--- a/spu_bubble/SPU销量汇总.xlsx
+++ b/spu_bubble/SPU销量汇总.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -47,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,12 +448,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>销售额 (USD)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>均价</t>
+          <t>均价 (USD)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -484,10 +487,10 @@
       <c r="E2" t="n">
         <v>27720</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="1" t="n">
         <v>1088778.87</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="1" t="n">
         <v>38.03</v>
       </c>
       <c r="H2" t="n">
@@ -517,10 +520,10 @@
       <c r="E3" t="n">
         <v>23064</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="1" t="n">
         <v>637708.26</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="1" t="n">
         <v>25.96</v>
       </c>
       <c r="H3" t="n">
@@ -550,10 +553,10 @@
       <c r="E4" t="n">
         <v>17667</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="1" t="n">
         <v>259688.94</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="1" t="n">
         <v>13.54</v>
       </c>
       <c r="H4" t="n">
@@ -583,10 +586,10 @@
       <c r="E5" t="n">
         <v>15852</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="1" t="n">
         <v>564917.28</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="1" t="n">
         <v>34.42</v>
       </c>
       <c r="H5" t="n">
@@ -616,10 +619,10 @@
       <c r="E6" t="n">
         <v>15098</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="1" t="n">
         <v>460290.08</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="1" t="n">
         <v>28.52</v>
       </c>
       <c r="H6" t="n">
@@ -649,10 +652,10 @@
       <c r="E7" t="n">
         <v>10882</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="1" t="n">
         <v>372153.99</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="1" t="n">
         <v>31.12</v>
       </c>
       <c r="H7" t="n">
@@ -682,10 +685,10 @@
       <c r="E8" t="n">
         <v>10532</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="1" t="n">
         <v>307786.98</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="1" t="n">
         <v>27.42</v>
       </c>
       <c r="H8" t="n">
@@ -715,10 +718,10 @@
       <c r="E9" t="n">
         <v>10524</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="1" t="n">
         <v>405535.55</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="1" t="n">
         <v>37.28</v>
       </c>
       <c r="H9" t="n">
@@ -748,10 +751,10 @@
       <c r="E10" t="n">
         <v>10324</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="1" t="n">
         <v>293088.03</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="H10" t="n">
@@ -781,10 +784,10 @@
       <c r="E11" t="n">
         <v>10281</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="1" t="n">
         <v>671906.15</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="1" t="n">
         <v>62.84</v>
       </c>
       <c r="H11" t="n">
@@ -814,10 +817,10 @@
       <c r="E12" t="n">
         <v>9738</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="1" t="n">
         <v>686630.97</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="1" t="n">
         <v>68.23999999999999</v>
       </c>
       <c r="H12" t="n">
@@ -847,10 +850,10 @@
       <c r="E13" t="n">
         <v>8724</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="1" t="n">
         <v>237604.78</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="1" t="n">
         <v>25.54</v>
       </c>
       <c r="H13" t="n">
@@ -880,10 +883,10 @@
       <c r="E14" t="n">
         <v>8070</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="1" t="n">
         <v>463345.41</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="1" t="n">
         <v>56.14</v>
       </c>
       <c r="H14" t="n">
@@ -913,10 +916,10 @@
       <c r="E15" t="n">
         <v>7958</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="1" t="n">
         <v>243455.87</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="1" t="n">
         <v>29.79</v>
       </c>
       <c r="H15" t="n">
@@ -946,10 +949,10 @@
       <c r="E16" t="n">
         <v>7418</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="1" t="n">
         <v>251537.82</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="1" t="n">
         <v>31.05</v>
       </c>
       <c r="H16" t="n">
@@ -979,10 +982,10 @@
       <c r="E17" t="n">
         <v>6047</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="1" t="n">
         <v>216427.2</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="1" t="n">
         <v>32.14</v>
       </c>
       <c r="H17" t="n">
@@ -1012,10 +1015,10 @@
       <c r="E18" t="n">
         <v>6567</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="1" t="n">
         <v>702457.54</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="1" t="n">
         <v>104.47</v>
       </c>
       <c r="H18" t="n">
@@ -1045,10 +1048,10 @@
       <c r="E19" t="n">
         <v>5930</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="1" t="n">
         <v>212457.25</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="1" t="n">
         <v>33.76</v>
       </c>
       <c r="H19" t="n">
@@ -1078,10 +1081,10 @@
       <c r="E20" t="n">
         <v>6080</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="1" t="n">
         <v>225859.22</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="1" t="n">
         <v>36.15</v>
       </c>
       <c r="H20" t="n">
@@ -1111,10 +1114,10 @@
       <c r="E21" t="n">
         <v>5982</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="1" t="n">
         <v>247167.35</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="1" t="n">
         <v>39.67</v>
       </c>
       <c r="H21" t="n">
@@ -1144,10 +1147,10 @@
       <c r="E22" t="n">
         <v>5656</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="1" t="n">
         <v>344787.18</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="1" t="n">
         <v>58.84</v>
       </c>
       <c r="H22" t="n">
@@ -1177,10 +1180,10 @@
       <c r="E23" t="n">
         <v>5606</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="1" t="n">
         <v>228076.66</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="1" t="n">
         <v>39.44</v>
       </c>
       <c r="H23" t="n">
@@ -1210,10 +1213,10 @@
       <c r="E24" t="n">
         <v>4531</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="1" t="n">
         <v>140962.39</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="1" t="n">
         <v>27.25</v>
       </c>
       <c r="H24" t="n">
@@ -1243,10 +1246,10 @@
       <c r="E25" t="n">
         <v>5019</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="1" t="n">
         <v>246442.37</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="1" t="n">
         <v>48.38</v>
       </c>
       <c r="H25" t="n">
@@ -1276,10 +1279,10 @@
       <c r="E26" t="n">
         <v>4329</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="1" t="n">
         <v>161778.26</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="1" t="n">
         <v>33.46</v>
       </c>
       <c r="H26" t="n">
@@ -1309,10 +1312,10 @@
       <c r="E27" t="n">
         <v>4603</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="1" t="n">
         <v>188039.46</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="1" t="n">
         <v>40.12</v>
       </c>
       <c r="H27" t="n">
@@ -1342,10 +1345,10 @@
       <c r="E28" t="n">
         <v>4557</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="1" t="n">
         <v>169139.3</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="1" t="n">
         <v>36.2</v>
       </c>
       <c r="H28" t="n">
@@ -1375,10 +1378,10 @@
       <c r="E29" t="n">
         <v>4230</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="1" t="n">
         <v>127645.2</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="1" t="n">
         <v>29.08</v>
       </c>
       <c r="H29" t="n">
@@ -1408,10 +1411,10 @@
       <c r="E30" t="n">
         <v>3859</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="1" t="n">
         <v>210253.4</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="1" t="n">
         <v>50.49</v>
       </c>
       <c r="H30" t="n">
@@ -1441,10 +1444,10 @@
       <c r="E31" t="n">
         <v>4026</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="1" t="n">
         <v>135524.54</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" s="1" t="n">
         <v>33.1</v>
       </c>
       <c r="H31" t="n">
@@ -1474,10 +1477,10 @@
       <c r="E32" t="n">
         <v>3801</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="1" t="n">
         <v>471507.93</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" s="1" t="n">
         <v>123.53</v>
       </c>
       <c r="H32" t="n">
@@ -1507,10 +1510,10 @@
       <c r="E33" t="n">
         <v>3734</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="1" t="n">
         <v>193347.5</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" s="1" t="n">
         <v>50.95</v>
       </c>
       <c r="H33" t="n">
@@ -1540,10 +1543,10 @@
       <c r="E34" t="n">
         <v>3495</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="1" t="n">
         <v>162814.95</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" s="1" t="n">
         <v>44.68</v>
       </c>
       <c r="H34" t="n">
@@ -1573,10 +1576,10 @@
       <c r="E35" t="n">
         <v>3366</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="1" t="n">
         <v>184320.86</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" s="1" t="n">
         <v>52.39</v>
       </c>
       <c r="H35" t="n">
@@ -1606,10 +1609,10 @@
       <c r="E36" t="n">
         <v>3236</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="1" t="n">
         <v>70459.05</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36" s="1" t="n">
         <v>20.07</v>
       </c>
       <c r="H36" t="n">
@@ -1639,10 +1642,10 @@
       <c r="E37" t="n">
         <v>3376</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="1" t="n">
         <v>158747.09</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" s="1" t="n">
         <v>46.43</v>
       </c>
       <c r="H37" t="n">
@@ -1672,10 +1675,10 @@
       <c r="E38" t="n">
         <v>3276</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="1" t="n">
         <v>213162.54</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" s="1" t="n">
         <v>64.36</v>
       </c>
       <c r="H38" t="n">
@@ -1705,10 +1708,10 @@
       <c r="E39" t="n">
         <v>3107</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="1" t="n">
         <v>354523.25</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" s="1" t="n">
         <v>112.4</v>
       </c>
       <c r="H39" t="n">
@@ -1738,10 +1741,10 @@
       <c r="E40" t="n">
         <v>3085</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="1" t="n">
         <v>219402.29</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" s="1" t="n">
         <v>70.43000000000001</v>
       </c>
       <c r="H40" t="n">
@@ -1771,10 +1774,10 @@
       <c r="E41" t="n">
         <v>2984</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="1" t="n">
         <v>194783.94</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41" s="1" t="n">
         <v>63.02</v>
       </c>
       <c r="H41" t="n">
@@ -1804,10 +1807,10 @@
       <c r="E42" t="n">
         <v>2900</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="1" t="n">
         <v>150713.58</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42" s="1" t="n">
         <v>51.67</v>
       </c>
       <c r="H42" t="n">
@@ -1837,10 +1840,10 @@
       <c r="E43" t="n">
         <v>2823</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="1" t="n">
         <v>343590.73</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" s="1" t="n">
         <v>117.87</v>
       </c>
       <c r="H43" t="n">
@@ -1870,10 +1873,10 @@
       <c r="E44" t="n">
         <v>2858</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="1" t="n">
         <v>135200.96</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="1" t="n">
         <v>46.38</v>
       </c>
       <c r="H44" t="n">
@@ -1903,10 +1906,10 @@
       <c r="E45" t="n">
         <v>2657</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="1" t="n">
         <v>77883.81</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" s="1" t="n">
         <v>27.18</v>
       </c>
       <c r="H45" t="n">
@@ -1936,10 +1939,10 @@
       <c r="E46" t="n">
         <v>2715</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="1" t="n">
         <v>290585.34</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46" s="1" t="n">
         <v>103.67</v>
       </c>
       <c r="H46" t="n">
@@ -1969,10 +1972,10 @@
       <c r="E47" t="n">
         <v>2704</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="1" t="n">
         <v>104484.88</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" s="1" t="n">
         <v>37.57</v>
       </c>
       <c r="H47" t="n">
@@ -2002,10 +2005,10 @@
       <c r="E48" t="n">
         <v>2626</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="1" t="n">
         <v>130714.75</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" s="1" t="n">
         <v>47.53</v>
       </c>
       <c r="H48" t="n">
@@ -2035,10 +2038,10 @@
       <c r="E49" t="n">
         <v>2485</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="1" t="n">
         <v>90459.33</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" s="1" t="n">
         <v>33.04</v>
       </c>
       <c r="H49" t="n">
@@ -2068,10 +2071,10 @@
       <c r="E50" t="n">
         <v>2461</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="1" t="n">
         <v>65965.06</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" s="1" t="n">
         <v>24.19</v>
       </c>
       <c r="H50" t="n">
@@ -2101,10 +2104,10 @@
       <c r="E51" t="n">
         <v>2637</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="1" t="n">
         <v>180834.09</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" s="1" t="n">
         <v>67.58</v>
       </c>
       <c r="H51" t="n">
@@ -2134,10 +2137,10 @@
       <c r="E52" t="n">
         <v>2627</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="1" t="n">
         <v>178941.19</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52" s="1" t="n">
         <v>67.78</v>
       </c>
       <c r="H52" t="n">
@@ -2167,10 +2170,10 @@
       <c r="E53" t="n">
         <v>2568</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="1" t="n">
         <v>103271.24</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" s="1" t="n">
         <v>39.34</v>
       </c>
       <c r="H53" t="n">
@@ -2200,10 +2203,10 @@
       <c r="E54" t="n">
         <v>2392</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="1" t="n">
         <v>46018.46000000001</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54" s="1" t="n">
         <v>18.07</v>
       </c>
       <c r="H54" t="n">
@@ -2233,10 +2236,10 @@
       <c r="E55" t="n">
         <v>2450</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="1" t="n">
         <v>68048.53</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55" s="1" t="n">
         <v>27.21</v>
       </c>
       <c r="H55" t="n">
@@ -2266,10 +2269,10 @@
       <c r="E56" t="n">
         <v>2448</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="1" t="n">
         <v>99750.82000000001</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" s="1" t="n">
         <v>40.06</v>
       </c>
       <c r="H56" t="n">
@@ -2299,10 +2302,10 @@
       <c r="E57" t="n">
         <v>2358</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="1" t="n">
         <v>93966.78</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" s="1" t="n">
         <v>37.87</v>
       </c>
       <c r="H57" t="n">
@@ -2332,10 +2335,10 @@
       <c r="E58" t="n">
         <v>2372</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="1" t="n">
         <v>95779.41</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" s="1" t="n">
         <v>39.08</v>
       </c>
       <c r="H58" t="n">
@@ -2365,10 +2368,10 @@
       <c r="E59" t="n">
         <v>2228</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="1" t="n">
         <v>105268</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" s="1" t="n">
         <v>43.09</v>
       </c>
       <c r="H59" t="n">
@@ -2398,10 +2401,10 @@
       <c r="E60" t="n">
         <v>2220</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="1" t="n">
         <v>159212.35</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60" s="1" t="n">
         <v>68.45</v>
       </c>
       <c r="H60" t="n">
@@ -2431,10 +2434,10 @@
       <c r="E61" t="n">
         <v>2150</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="1" t="n">
         <v>64786.87</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61" s="1" t="n">
         <v>28.27</v>
       </c>
       <c r="H61" t="n">
@@ -2464,10 +2467,10 @@
       <c r="E62" t="n">
         <v>2168</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="1" t="n">
         <v>161361.28</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62" s="1" t="n">
         <v>71.68000000000001</v>
       </c>
       <c r="H62" t="n">
@@ -2497,10 +2500,10 @@
       <c r="E63" t="n">
         <v>2051</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="1" t="n">
         <v>98600</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63" s="1" t="n">
         <v>46.1</v>
       </c>
       <c r="H63" t="n">
@@ -2530,10 +2533,10 @@
       <c r="E64" t="n">
         <v>2061</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="1" t="n">
         <v>93148.28</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64" s="1" t="n">
         <v>44.89</v>
       </c>
       <c r="H64" t="n">
@@ -2563,10 +2566,10 @@
       <c r="E65" t="n">
         <v>2028</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="1" t="n">
         <v>149312.17</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65" s="1" t="n">
         <v>72.41</v>
       </c>
       <c r="H65" t="n">
@@ -2596,10 +2599,10 @@
       <c r="E66" t="n">
         <v>2017</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="1" t="n">
         <v>113604.71</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66" s="1" t="n">
         <v>55.17</v>
       </c>
       <c r="H66" t="n">
@@ -2629,10 +2632,10 @@
       <c r="E67" t="n">
         <v>1982</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="1" t="n">
         <v>245551.04</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67" s="1" t="n">
         <v>119.49</v>
       </c>
       <c r="H67" t="n">
@@ -2662,10 +2665,10 @@
       <c r="E68" t="n">
         <v>1740</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="1" t="n">
         <v>39081.97</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68" s="1" t="n">
         <v>19.56</v>
       </c>
       <c r="H68" t="n">
@@ -2695,10 +2698,10 @@
       <c r="E69" t="n">
         <v>1872</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="1" t="n">
         <v>83175.47</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69" s="1" t="n">
         <v>43.66</v>
       </c>
       <c r="H69" t="n">
@@ -2728,10 +2731,10 @@
       <c r="E70" t="n">
         <v>1709</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="1" t="n">
         <v>94373.67999999999</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" s="1" t="n">
         <v>49.54</v>
       </c>
       <c r="H70" t="n">
@@ -2761,10 +2764,10 @@
       <c r="E71" t="n">
         <v>1856</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="1" t="n">
         <v>112790.2</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G71" s="1" t="n">
         <v>60.19</v>
       </c>
       <c r="H71" t="n">
@@ -2794,10 +2797,10 @@
       <c r="E72" t="n">
         <v>1731</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="1" t="n">
         <v>76264.97</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" s="1" t="n">
         <v>40.85</v>
       </c>
       <c r="H72" t="n">
@@ -2827,10 +2830,10 @@
       <c r="E73" t="n">
         <v>1830</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="1" t="n">
         <v>238733.98</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73" s="1" t="n">
         <v>129.4</v>
       </c>
       <c r="H73" t="n">
@@ -2860,10 +2863,10 @@
       <c r="E74" t="n">
         <v>1772</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="1" t="n">
         <v>130974.15</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74" s="1" t="n">
         <v>71.34</v>
       </c>
       <c r="H74" t="n">
@@ -2893,10 +2896,10 @@
       <c r="E75" t="n">
         <v>1796</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="1" t="n">
         <v>103406.7</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75" s="1" t="n">
         <v>56.51</v>
       </c>
       <c r="H75" t="n">
@@ -2926,10 +2929,10 @@
       <c r="E76" t="n">
         <v>1809</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" s="1" t="n">
         <v>165421.69</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G76" s="1" t="n">
         <v>91.23999999999999</v>
       </c>
       <c r="H76" t="n">
@@ -2959,10 +2962,10 @@
       <c r="E77" t="n">
         <v>1538</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="1" t="n">
         <v>43078.42000000001</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77" s="1" t="n">
         <v>23.93</v>
       </c>
       <c r="H77" t="n">
@@ -2992,10 +2995,10 @@
       <c r="E78" t="n">
         <v>1748</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" s="1" t="n">
         <v>247204.23</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G78" s="1" t="n">
         <v>140.06</v>
       </c>
       <c r="H78" t="n">
@@ -3025,10 +3028,10 @@
       <c r="E79" t="n">
         <v>1686</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" s="1" t="n">
         <v>112666.88</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79" s="1" t="n">
         <v>64.16</v>
       </c>
       <c r="H79" t="n">
@@ -3058,10 +3061,10 @@
       <c r="E80" t="n">
         <v>1740</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" s="1" t="n">
         <v>88271.86</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G80" s="1" t="n">
         <v>50.3</v>
       </c>
       <c r="H80" t="n">
@@ -3091,10 +3094,10 @@
       <c r="E81" t="n">
         <v>1671</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81" s="1" t="n">
         <v>182556.95</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G81" s="1" t="n">
         <v>106.2</v>
       </c>
       <c r="H81" t="n">
@@ -3124,10 +3127,10 @@
       <c r="E82" t="n">
         <v>1478</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82" s="1" t="n">
         <v>53065.29</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G82" s="1" t="n">
         <v>31</v>
       </c>
       <c r="H82" t="n">
@@ -3157,10 +3160,10 @@
       <c r="E83" t="n">
         <v>1487</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83" s="1" t="n">
         <v>55642.13</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G83" s="1" t="n">
         <v>33.22</v>
       </c>
       <c r="H83" t="n">
@@ -3190,10 +3193,10 @@
       <c r="E84" t="n">
         <v>1568</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84" s="1" t="n">
         <v>85608.88</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G84" s="1" t="n">
         <v>52.88</v>
       </c>
       <c r="H84" t="n">
@@ -3223,10 +3226,10 @@
       <c r="E85" t="n">
         <v>1582</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85" s="1" t="n">
         <v>150335.26</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G85" s="1" t="n">
         <v>93.48999999999999</v>
       </c>
       <c r="H85" t="n">
@@ -3256,10 +3259,10 @@
       <c r="E86" t="n">
         <v>1430</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" s="1" t="n">
         <v>88978.23</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86" s="1" t="n">
         <v>56.28</v>
       </c>
       <c r="H86" t="n">
@@ -3289,10 +3292,10 @@
       <c r="E87" t="n">
         <v>1338</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="1" t="n">
         <v>48879.32</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G87" s="1" t="n">
         <v>30.98</v>
       </c>
       <c r="H87" t="n">
@@ -3322,10 +3325,10 @@
       <c r="E88" t="n">
         <v>1524</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88" s="1" t="n">
         <v>151402.93</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G88" s="1" t="n">
         <v>96.87</v>
       </c>
       <c r="H88" t="n">
@@ -3355,10 +3358,10 @@
       <c r="E89" t="n">
         <v>1457</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89" s="1" t="n">
         <v>45744.29</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G89" s="1" t="n">
         <v>29.61</v>
       </c>
       <c r="H89" t="n">
@@ -3388,10 +3391,10 @@
       <c r="E90" t="n">
         <v>1483</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90" s="1" t="n">
         <v>132949.14</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G90" s="1" t="n">
         <v>89.11</v>
       </c>
       <c r="H90" t="n">
@@ -3421,10 +3424,10 @@
       <c r="E91" t="n">
         <v>1457</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91" s="1" t="n">
         <v>93617.65999999999</v>
       </c>
-      <c r="G91" t="n">
+      <c r="G91" s="1" t="n">
         <v>62.87</v>
       </c>
       <c r="H91" t="n">
@@ -3454,10 +3457,10 @@
       <c r="E92" t="n">
         <v>1382</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92" s="1" t="n">
         <v>34306.77</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G92" s="1" t="n">
         <v>23.18</v>
       </c>
       <c r="H92" t="n">
@@ -3487,10 +3490,10 @@
       <c r="E93" t="n">
         <v>1423</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" s="1" t="n">
         <v>204330.16</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G93" s="1" t="n">
         <v>140.92</v>
       </c>
       <c r="H93" t="n">
@@ -3520,10 +3523,10 @@
       <c r="E94" t="n">
         <v>1394</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94" s="1" t="n">
         <v>199003.08</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G94" s="1" t="n">
         <v>138.49</v>
       </c>
       <c r="H94" t="n">
@@ -3553,10 +3556,10 @@
       <c r="E95" t="n">
         <v>1422</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95" s="1" t="n">
         <v>76154.52</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G95" s="1" t="n">
         <v>53.22</v>
       </c>
       <c r="H95" t="n">
@@ -3586,10 +3589,10 @@
       <c r="E96" t="n">
         <v>1324</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96" s="1" t="n">
         <v>51661.64</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G96" s="1" t="n">
         <v>36.51</v>
       </c>
       <c r="H96" t="n">
@@ -3619,10 +3622,10 @@
       <c r="E97" t="n">
         <v>1288</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" s="1" t="n">
         <v>46666.17</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G97" s="1" t="n">
         <v>33.1</v>
       </c>
       <c r="H97" t="n">
@@ -3652,10 +3655,10 @@
       <c r="E98" t="n">
         <v>1309</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98" s="1" t="n">
         <v>39984.75</v>
       </c>
-      <c r="G98" t="n">
+      <c r="G98" s="1" t="n">
         <v>29.38</v>
       </c>
       <c r="H98" t="n">
@@ -3685,10 +3688,10 @@
       <c r="E99" t="n">
         <v>1340</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99" s="1" t="n">
         <v>165403.58</v>
       </c>
-      <c r="G99" t="n">
+      <c r="G99" s="1" t="n">
         <v>121.71</v>
       </c>
       <c r="H99" t="n">
@@ -3718,10 +3721,10 @@
       <c r="E100" t="n">
         <v>1338</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" s="1" t="n">
         <v>116602.07</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100" s="1" t="n">
         <v>86.12</v>
       </c>
       <c r="H100" t="n">
@@ -3751,10 +3754,10 @@
       <c r="E101" t="n">
         <v>1209</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101" s="1" t="n">
         <v>39785.41</v>
       </c>
-      <c r="G101" t="n">
+      <c r="G101" s="1" t="n">
         <v>29.51</v>
       </c>
       <c r="H101" t="n">
@@ -3784,10 +3787,10 @@
       <c r="E102" t="n">
         <v>1300</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102" s="1" t="n">
         <v>91840.53</v>
       </c>
-      <c r="G102" t="n">
+      <c r="G102" s="1" t="n">
         <v>68.38</v>
       </c>
       <c r="H102" t="n">
@@ -3817,10 +3820,10 @@
       <c r="E103" t="n">
         <v>1227</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103" s="1" t="n">
         <v>37519.12</v>
       </c>
-      <c r="G103" t="n">
+      <c r="G103" s="1" t="n">
         <v>27.98</v>
       </c>
       <c r="H103" t="n">
@@ -3850,10 +3853,10 @@
       <c r="E104" t="n">
         <v>1250</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104" s="1" t="n">
         <v>74282.73</v>
       </c>
-      <c r="G104" t="n">
+      <c r="G104" s="1" t="n">
         <v>55.98</v>
       </c>
       <c r="H104" t="n">
@@ -3883,10 +3886,10 @@
       <c r="E105" t="n">
         <v>1228</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105" s="1" t="n">
         <v>13761.02</v>
       </c>
-      <c r="G105" t="n">
+      <c r="G105" s="1" t="n">
         <v>10.46</v>
       </c>
       <c r="H105" t="n">
@@ -3916,10 +3919,10 @@
       <c r="E106" t="n">
         <v>1277</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106" s="1" t="n">
         <v>71404.56</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G106" s="1" t="n">
         <v>54.47</v>
       </c>
       <c r="H106" t="n">
@@ -3949,10 +3952,10 @@
       <c r="E107" t="n">
         <v>1244</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107" s="1" t="n">
         <v>54390.98</v>
       </c>
-      <c r="G107" t="n">
+      <c r="G107" s="1" t="n">
         <v>41.68</v>
       </c>
       <c r="H107" t="n">
@@ -3982,10 +3985,10 @@
       <c r="E108" t="n">
         <v>1286</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108" s="1" t="n">
         <v>158974.8</v>
       </c>
-      <c r="G108" t="n">
+      <c r="G108" s="1" t="n">
         <v>123.33</v>
       </c>
       <c r="H108" t="n">
@@ -4015,10 +4018,10 @@
       <c r="E109" t="n">
         <v>1250</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109" s="1" t="n">
         <v>136870.98</v>
       </c>
-      <c r="G109" t="n">
+      <c r="G109" s="1" t="n">
         <v>106.85</v>
       </c>
       <c r="H109" t="n">
@@ -4048,10 +4051,10 @@
       <c r="E110" t="n">
         <v>1217</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110" s="1" t="n">
         <v>82289.39999999999</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G110" s="1" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="H110" t="n">
@@ -4081,10 +4084,10 @@
       <c r="E111" t="n">
         <v>1261</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111" s="1" t="n">
         <v>85210.7</v>
       </c>
-      <c r="G111" t="n">
+      <c r="G111" s="1" t="n">
         <v>67.56999999999999</v>
       </c>
       <c r="H111" t="n">
@@ -4114,10 +4117,10 @@
       <c r="E112" t="n">
         <v>1215</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112" s="1" t="n">
         <v>109032.47</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G112" s="1" t="n">
         <v>88.5</v>
       </c>
       <c r="H112" t="n">
@@ -4147,10 +4150,10 @@
       <c r="E113" t="n">
         <v>1178</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113" s="1" t="n">
         <v>35847.61</v>
       </c>
-      <c r="G113" t="n">
+      <c r="G113" s="1" t="n">
         <v>29.19</v>
       </c>
       <c r="H113" t="n">
@@ -4180,10 +4183,10 @@
       <c r="E114" t="n">
         <v>1171</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" s="1" t="n">
         <v>63853.89999999999</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G114" s="1" t="n">
         <v>52.3</v>
       </c>
       <c r="H114" t="n">
@@ -4213,10 +4216,10 @@
       <c r="E115" t="n">
         <v>1156</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115" s="1" t="n">
         <v>42827.35</v>
       </c>
-      <c r="G115" t="n">
+      <c r="G115" s="1" t="n">
         <v>35.66</v>
       </c>
       <c r="H115" t="n">
@@ -4246,10 +4249,10 @@
       <c r="E116" t="n">
         <v>1149</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116" s="1" t="n">
         <v>81606.06</v>
       </c>
-      <c r="G116" t="n">
+      <c r="G116" s="1" t="n">
         <v>68.34999999999999</v>
       </c>
       <c r="H116" t="n">
@@ -4279,10 +4282,10 @@
       <c r="E117" t="n">
         <v>1166</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117" s="1" t="n">
         <v>72447.08</v>
       </c>
-      <c r="G117" t="n">
+      <c r="G117" s="1" t="n">
         <v>61.87</v>
       </c>
       <c r="H117" t="n">
@@ -4312,10 +4315,10 @@
       <c r="E118" t="n">
         <v>1145</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118" s="1" t="n">
         <v>143610.55</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G118" s="1" t="n">
         <v>124.77</v>
       </c>
       <c r="H118" t="n">
@@ -4345,10 +4348,10 @@
       <c r="E119" t="n">
         <v>1098</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119" s="1" t="n">
         <v>64016.98</v>
       </c>
-      <c r="G119" t="n">
+      <c r="G119" s="1" t="n">
         <v>55.81</v>
       </c>
       <c r="H119" t="n">
@@ -4378,10 +4381,10 @@
       <c r="E120" t="n">
         <v>1023</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120" s="1" t="n">
         <v>61422.66</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G120" s="1" t="n">
         <v>53.55</v>
       </c>
       <c r="H120" t="n">
@@ -4411,10 +4414,10 @@
       <c r="E121" t="n">
         <v>1084</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121" s="1" t="n">
         <v>73149.58</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G121" s="1" t="n">
         <v>63.94</v>
       </c>
       <c r="H121" t="n">
@@ -4444,10 +4447,10 @@
       <c r="E122" t="n">
         <v>1128</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122" s="1" t="n">
         <v>44425.17</v>
       </c>
-      <c r="G122" t="n">
+      <c r="G122" s="1" t="n">
         <v>39.24</v>
       </c>
       <c r="H122" t="n">
@@ -4477,10 +4480,10 @@
       <c r="E123" t="n">
         <v>1095</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123" s="1" t="n">
         <v>56519.53</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G123" s="1" t="n">
         <v>50.83</v>
       </c>
       <c r="H123" t="n">
@@ -4510,10 +4513,10 @@
       <c r="E124" t="n">
         <v>1088</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124" s="1" t="n">
         <v>140293.13</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G124" s="1" t="n">
         <v>126.73</v>
       </c>
       <c r="H124" t="n">
@@ -4543,10 +4546,10 @@
       <c r="E125" t="n">
         <v>1060</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125" s="1" t="n">
         <v>96357.43000000001</v>
       </c>
-      <c r="G125" t="n">
+      <c r="G125" s="1" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="H125" t="n">
@@ -4576,10 +4579,10 @@
       <c r="E126" t="n">
         <v>1029</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126" s="1" t="n">
         <v>51373</v>
       </c>
-      <c r="G126" t="n">
+      <c r="G126" s="1" t="n">
         <v>47.35</v>
       </c>
       <c r="H126" t="n">
@@ -4609,10 +4612,10 @@
       <c r="E127" t="n">
         <v>1070</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127" s="1" t="n">
         <v>59087.81</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G127" s="1" t="n">
         <v>54.76</v>
       </c>
       <c r="H127" t="n">
@@ -4642,10 +4645,10 @@
       <c r="E128" t="n">
         <v>952</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128" s="1" t="n">
         <v>17133.32</v>
       </c>
-      <c r="G128" t="n">
+      <c r="G128" s="1" t="n">
         <v>16.52</v>
       </c>
       <c r="H128" t="n">
@@ -4675,10 +4678,10 @@
       <c r="E129" t="n">
         <v>981</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129" s="1" t="n">
         <v>9671.900000000001</v>
       </c>
-      <c r="G129" t="n">
+      <c r="G129" s="1" t="n">
         <v>9.359999999999999</v>
       </c>
       <c r="H129" t="n">
@@ -4708,10 +4711,10 @@
       <c r="E130" t="n">
         <v>1017</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F130" s="1" t="n">
         <v>66152.66</v>
       </c>
-      <c r="G130" t="n">
+      <c r="G130" s="1" t="n">
         <v>64.23</v>
       </c>
       <c r="H130" t="n">
@@ -4741,10 +4744,10 @@
       <c r="E131" t="n">
         <v>940</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131" s="1" t="n">
         <v>45010.28999999999</v>
       </c>
-      <c r="G131" t="n">
+      <c r="G131" s="1" t="n">
         <v>44.08</v>
       </c>
       <c r="H131" t="n">
@@ -4774,10 +4777,10 @@
       <c r="E132" t="n">
         <v>1012</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F132" s="1" t="n">
         <v>53454.55</v>
       </c>
-      <c r="G132" t="n">
+      <c r="G132" s="1" t="n">
         <v>52.41</v>
       </c>
       <c r="H132" t="n">
@@ -4807,10 +4810,10 @@
       <c r="E133" t="n">
         <v>987</v>
       </c>
-      <c r="F133" t="n">
+      <c r="F133" s="1" t="n">
         <v>52177.87</v>
       </c>
-      <c r="G133" t="n">
+      <c r="G133" s="1" t="n">
         <v>51.46</v>
       </c>
       <c r="H133" t="n">
@@ -4840,10 +4843,10 @@
       <c r="E134" t="n">
         <v>1005</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134" s="1" t="n">
         <v>86946.42999999999</v>
       </c>
-      <c r="G134" t="n">
+      <c r="G134" s="1" t="n">
         <v>85.92</v>
       </c>
       <c r="H134" t="n">
@@ -4873,10 +4876,10 @@
       <c r="E135" t="n">
         <v>978</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F135" s="1" t="n">
         <v>40354.81</v>
       </c>
-      <c r="G135" t="n">
+      <c r="G135" s="1" t="n">
         <v>40.23</v>
       </c>
       <c r="H135" t="n">
@@ -4906,10 +4909,10 @@
       <c r="E136" t="n">
         <v>989</v>
       </c>
-      <c r="F136" t="n">
+      <c r="F136" s="1" t="n">
         <v>84214.42</v>
       </c>
-      <c r="G136" t="n">
+      <c r="G136" s="1" t="n">
         <v>84.81</v>
       </c>
       <c r="H136" t="n">
@@ -4939,10 +4942,10 @@
       <c r="E137" t="n">
         <v>948</v>
       </c>
-      <c r="F137" t="n">
+      <c r="F137" s="1" t="n">
         <v>110683.85</v>
       </c>
-      <c r="G137" t="n">
+      <c r="G137" s="1" t="n">
         <v>112.6</v>
       </c>
       <c r="H137" t="n">
@@ -4972,10 +4975,10 @@
       <c r="E138" t="n">
         <v>957</v>
       </c>
-      <c r="F138" t="n">
+      <c r="F138" s="1" t="n">
         <v>54533.46</v>
       </c>
-      <c r="G138" t="n">
+      <c r="G138" s="1" t="n">
         <v>55.93</v>
       </c>
       <c r="H138" t="n">
@@ -5005,10 +5008,10 @@
       <c r="E139" t="n">
         <v>851</v>
       </c>
-      <c r="F139" t="n">
+      <c r="F139" s="1" t="n">
         <v>56497.05</v>
       </c>
-      <c r="G139" t="n">
+      <c r="G139" s="1" t="n">
         <v>57.95</v>
       </c>
       <c r="H139" t="n">
@@ -5038,10 +5041,10 @@
       <c r="E140" t="n">
         <v>940</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F140" s="1" t="n">
         <v>62916.9</v>
       </c>
-      <c r="G140" t="n">
+      <c r="G140" s="1" t="n">
         <v>65.2</v>
       </c>
       <c r="H140" t="n">
@@ -5071,10 +5074,10 @@
       <c r="E141" t="n">
         <v>891</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F141" s="1" t="n">
         <v>10097.41</v>
       </c>
-      <c r="G141" t="n">
+      <c r="G141" s="1" t="n">
         <v>10.5</v>
       </c>
       <c r="H141" t="n">
@@ -5104,10 +5107,10 @@
       <c r="E142" t="n">
         <v>938</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142" s="1" t="n">
         <v>40936.6</v>
       </c>
-      <c r="G142" t="n">
+      <c r="G142" s="1" t="n">
         <v>42.87</v>
       </c>
       <c r="H142" t="n">
@@ -5137,10 +5140,10 @@
       <c r="E143" t="n">
         <v>918</v>
       </c>
-      <c r="F143" t="n">
+      <c r="F143" s="1" t="n">
         <v>20661.28</v>
       </c>
-      <c r="G143" t="n">
+      <c r="G143" s="1" t="n">
         <v>22.22</v>
       </c>
       <c r="H143" t="n">
@@ -5170,10 +5173,10 @@
       <c r="E144" t="n">
         <v>883</v>
       </c>
-      <c r="F144" t="n">
+      <c r="F144" s="1" t="n">
         <v>31334.35</v>
       </c>
-      <c r="G144" t="n">
+      <c r="G144" s="1" t="n">
         <v>35.01</v>
       </c>
       <c r="H144" t="n">
@@ -5203,10 +5206,10 @@
       <c r="E145" t="n">
         <v>883</v>
       </c>
-      <c r="F145" t="n">
+      <c r="F145" s="1" t="n">
         <v>46376.28</v>
       </c>
-      <c r="G145" t="n">
+      <c r="G145" s="1" t="n">
         <v>51.88</v>
       </c>
       <c r="H145" t="n">
@@ -5236,10 +5239,10 @@
       <c r="E146" t="n">
         <v>824</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F146" s="1" t="n">
         <v>38037.52</v>
       </c>
-      <c r="G146" t="n">
+      <c r="G146" s="1" t="n">
         <v>44.38</v>
       </c>
       <c r="H146" t="n">
@@ -5269,10 +5272,10 @@
       <c r="E147" t="n">
         <v>745</v>
       </c>
-      <c r="F147" t="n">
+      <c r="F147" s="1" t="n">
         <v>13901.18</v>
       </c>
-      <c r="G147" t="n">
+      <c r="G147" s="1" t="n">
         <v>16.24</v>
       </c>
       <c r="H147" t="n">
@@ -5302,10 +5305,10 @@
       <c r="E148" t="n">
         <v>836</v>
       </c>
-      <c r="F148" t="n">
+      <c r="F148" s="1" t="n">
         <v>60062.18</v>
       </c>
-      <c r="G148" t="n">
+      <c r="G148" s="1" t="n">
         <v>71.59</v>
       </c>
       <c r="H148" t="n">
@@ -5335,10 +5338,10 @@
       <c r="E149" t="n">
         <v>710</v>
       </c>
-      <c r="F149" t="n">
+      <c r="F149" s="1" t="n">
         <v>22043.95</v>
       </c>
-      <c r="G149" t="n">
+      <c r="G149" s="1" t="n">
         <v>26.4</v>
       </c>
       <c r="H149" t="n">
@@ -5368,10 +5371,10 @@
       <c r="E150" t="n">
         <v>823</v>
       </c>
-      <c r="F150" t="n">
+      <c r="F150" s="1" t="n">
         <v>75628.95999999999</v>
       </c>
-      <c r="G150" t="n">
+      <c r="G150" s="1" t="n">
         <v>91.56</v>
       </c>
       <c r="H150" t="n">
@@ -5401,10 +5404,10 @@
       <c r="E151" t="n">
         <v>774</v>
       </c>
-      <c r="F151" t="n">
+      <c r="F151" s="1" t="n">
         <v>67134.72</v>
       </c>
-      <c r="G151" t="n">
+      <c r="G151" s="1" t="n">
         <v>81.67</v>
       </c>
       <c r="H151" t="n">
@@ -5434,10 +5437,10 @@
       <c r="E152" t="n">
         <v>808</v>
       </c>
-      <c r="F152" t="n">
+      <c r="F152" s="1" t="n">
         <v>74958.03</v>
       </c>
-      <c r="G152" t="n">
+      <c r="G152" s="1" t="n">
         <v>92.54000000000001</v>
       </c>
       <c r="H152" t="n">
@@ -5467,10 +5470,10 @@
       <c r="E153" t="n">
         <v>793</v>
       </c>
-      <c r="F153" t="n">
+      <c r="F153" s="1" t="n">
         <v>68041.23999999999</v>
       </c>
-      <c r="G153" t="n">
+      <c r="G153" s="1" t="n">
         <v>84.63</v>
       </c>
       <c r="H153" t="n">
@@ -5500,10 +5503,10 @@
       <c r="E154" t="n">
         <v>745</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F154" s="1" t="n">
         <v>12874.72</v>
       </c>
-      <c r="G154" t="n">
+      <c r="G154" s="1" t="n">
         <v>16.11</v>
       </c>
       <c r="H154" t="n">
@@ -5533,10 +5536,10 @@
       <c r="E155" t="n">
         <v>755</v>
       </c>
-      <c r="F155" t="n">
+      <c r="F155" s="1" t="n">
         <v>53968.99</v>
       </c>
-      <c r="G155" t="n">
+      <c r="G155" s="1" t="n">
         <v>68.75</v>
       </c>
       <c r="H155" t="n">
@@ -5566,10 +5569,10 @@
       <c r="E156" t="n">
         <v>779</v>
       </c>
-      <c r="F156" t="n">
+      <c r="F156" s="1" t="n">
         <v>31352.62</v>
       </c>
-      <c r="G156" t="n">
+      <c r="G156" s="1" t="n">
         <v>40.09</v>
       </c>
       <c r="H156" t="n">
@@ -5599,10 +5602,10 @@
       <c r="E157" t="n">
         <v>762</v>
       </c>
-      <c r="F157" t="n">
+      <c r="F157" s="1" t="n">
         <v>52983.77</v>
       </c>
-      <c r="G157" t="n">
+      <c r="G157" s="1" t="n">
         <v>67.93000000000001</v>
       </c>
       <c r="H157" t="n">
@@ -5632,10 +5635,10 @@
       <c r="E158" t="n">
         <v>758</v>
       </c>
-      <c r="F158" t="n">
+      <c r="F158" s="1" t="n">
         <v>32466.89</v>
       </c>
-      <c r="G158" t="n">
+      <c r="G158" s="1" t="n">
         <v>42.61</v>
       </c>
       <c r="H158" t="n">
@@ -5665,10 +5668,10 @@
       <c r="E159" t="n">
         <v>748</v>
       </c>
-      <c r="F159" t="n">
+      <c r="F159" s="1" t="n">
         <v>48902.16</v>
       </c>
-      <c r="G159" t="n">
+      <c r="G159" s="1" t="n">
         <v>64.43000000000001</v>
       </c>
       <c r="H159" t="n">
@@ -5698,10 +5701,10 @@
       <c r="E160" t="n">
         <v>739</v>
       </c>
-      <c r="F160" t="n">
+      <c r="F160" s="1" t="n">
         <v>78745.25</v>
       </c>
-      <c r="G160" t="n">
+      <c r="G160" s="1" t="n">
         <v>104.44</v>
       </c>
       <c r="H160" t="n">
@@ -5731,10 +5734,10 @@
       <c r="E161" t="n">
         <v>738</v>
       </c>
-      <c r="F161" t="n">
+      <c r="F161" s="1" t="n">
         <v>63422.66</v>
       </c>
-      <c r="G161" t="n">
+      <c r="G161" s="1" t="n">
         <v>84.56</v>
       </c>
       <c r="H161" t="n">
@@ -5764,10 +5767,10 @@
       <c r="E162" t="n">
         <v>732</v>
       </c>
-      <c r="F162" t="n">
+      <c r="F162" s="1" t="n">
         <v>36490.14</v>
       </c>
-      <c r="G162" t="n">
+      <c r="G162" s="1" t="n">
         <v>49.24</v>
       </c>
       <c r="H162" t="n">
@@ -5797,10 +5800,10 @@
       <c r="E163" t="n">
         <v>715</v>
       </c>
-      <c r="F163" t="n">
+      <c r="F163" s="1" t="n">
         <v>41473.53</v>
       </c>
-      <c r="G163" t="n">
+      <c r="G163" s="1" t="n">
         <v>55.97</v>
       </c>
       <c r="H163" t="n">
@@ -5830,10 +5833,10 @@
       <c r="E164" t="n">
         <v>669</v>
       </c>
-      <c r="F164" t="n">
+      <c r="F164" s="1" t="n">
         <v>11679.03</v>
       </c>
-      <c r="G164" t="n">
+      <c r="G164" s="1" t="n">
         <v>15.87</v>
       </c>
       <c r="H164" t="n">
@@ -5863,10 +5866,10 @@
       <c r="E165" t="n">
         <v>700</v>
       </c>
-      <c r="F165" t="n">
+      <c r="F165" s="1" t="n">
         <v>64448.57999999999</v>
       </c>
-      <c r="G165" t="n">
+      <c r="G165" s="1" t="n">
         <v>88.65000000000001</v>
       </c>
       <c r="H165" t="n">
@@ -5896,10 +5899,10 @@
       <c r="E166" t="n">
         <v>695</v>
       </c>
-      <c r="F166" t="n">
+      <c r="F166" s="1" t="n">
         <v>94821.70999999999</v>
       </c>
-      <c r="G166" t="n">
+      <c r="G166" s="1" t="n">
         <v>130.97</v>
       </c>
       <c r="H166" t="n">
@@ -5929,10 +5932,10 @@
       <c r="E167" t="n">
         <v>712</v>
       </c>
-      <c r="F167" t="n">
+      <c r="F167" s="1" t="n">
         <v>50624.87</v>
       </c>
-      <c r="G167" t="n">
+      <c r="G167" s="1" t="n">
         <v>70.20999999999999</v>
       </c>
       <c r="H167" t="n">
@@ -5962,10 +5965,10 @@
       <c r="E168" t="n">
         <v>709</v>
       </c>
-      <c r="F168" t="n">
+      <c r="F168" s="1" t="n">
         <v>46234.03</v>
       </c>
-      <c r="G168" t="n">
+      <c r="G168" s="1" t="n">
         <v>64.3</v>
       </c>
       <c r="H168" t="n">
@@ -5995,10 +5998,10 @@
       <c r="E169" t="n">
         <v>654</v>
       </c>
-      <c r="F169" t="n">
+      <c r="F169" s="1" t="n">
         <v>26728.63</v>
       </c>
-      <c r="G169" t="n">
+      <c r="G169" s="1" t="n">
         <v>37.44</v>
       </c>
       <c r="H169" t="n">
@@ -6028,10 +6031,10 @@
       <c r="E170" t="n">
         <v>702</v>
       </c>
-      <c r="F170" t="n">
+      <c r="F170" s="1" t="n">
         <v>48834.86</v>
       </c>
-      <c r="G170" t="n">
+      <c r="G170" s="1" t="n">
         <v>68.98</v>
       </c>
       <c r="H170" t="n">
@@ -6061,10 +6064,10 @@
       <c r="E171" t="n">
         <v>685</v>
       </c>
-      <c r="F171" t="n">
+      <c r="F171" s="1" t="n">
         <v>62767.45</v>
       </c>
-      <c r="G171" t="n">
+      <c r="G171" s="1" t="n">
         <v>89.41</v>
       </c>
       <c r="H171" t="n">
@@ -6094,10 +6097,10 @@
       <c r="E172" t="n">
         <v>680</v>
       </c>
-      <c r="F172" t="n">
+      <c r="F172" s="1" t="n">
         <v>18135.6</v>
       </c>
-      <c r="G172" t="n">
+      <c r="G172" s="1" t="n">
         <v>25.87</v>
       </c>
       <c r="H172" t="n">
@@ -6127,10 +6130,10 @@
       <c r="E173" t="n">
         <v>699</v>
       </c>
-      <c r="F173" t="n">
+      <c r="F173" s="1" t="n">
         <v>61212.73</v>
       </c>
-      <c r="G173" t="n">
+      <c r="G173" s="1" t="n">
         <v>87.31999999999999</v>
       </c>
       <c r="H173" t="n">
@@ -6160,10 +6163,10 @@
       <c r="E174" t="n">
         <v>638</v>
       </c>
-      <c r="F174" t="n">
+      <c r="F174" s="1" t="n">
         <v>19426.02</v>
       </c>
-      <c r="G174" t="n">
+      <c r="G174" s="1" t="n">
         <v>28.11</v>
       </c>
       <c r="H174" t="n">
@@ -6193,10 +6196,10 @@
       <c r="E175" t="n">
         <v>669</v>
       </c>
-      <c r="F175" t="n">
+      <c r="F175" s="1" t="n">
         <v>46487.69</v>
       </c>
-      <c r="G175" t="n">
+      <c r="G175" s="1" t="n">
         <v>68.36</v>
       </c>
       <c r="H175" t="n">
@@ -6226,10 +6229,10 @@
       <c r="E176" t="n">
         <v>668</v>
       </c>
-      <c r="F176" t="n">
+      <c r="F176" s="1" t="n">
         <v>32073.78</v>
       </c>
-      <c r="G176" t="n">
+      <c r="G176" s="1" t="n">
         <v>47.45</v>
       </c>
       <c r="H176" t="n">
@@ -6259,10 +6262,10 @@
       <c r="E177" t="n">
         <v>667</v>
       </c>
-      <c r="F177" t="n">
+      <c r="F177" s="1" t="n">
         <v>46102.85</v>
       </c>
-      <c r="G177" t="n">
+      <c r="G177" s="1" t="n">
         <v>68.40000000000001</v>
       </c>
       <c r="H177" t="n">
@@ -6292,10 +6295,10 @@
       <c r="E178" t="n">
         <v>651</v>
       </c>
-      <c r="F178" t="n">
+      <c r="F178" s="1" t="n">
         <v>43935.93</v>
       </c>
-      <c r="G178" t="n">
+      <c r="G178" s="1" t="n">
         <v>65.67</v>
       </c>
       <c r="H178" t="n">
@@ -6325,10 +6328,10 @@
       <c r="E179" t="n">
         <v>650</v>
       </c>
-      <c r="F179" t="n">
+      <c r="F179" s="1" t="n">
         <v>33237.7</v>
       </c>
-      <c r="G179" t="n">
+      <c r="G179" s="1" t="n">
         <v>50.06</v>
       </c>
       <c r="H179" t="n">
@@ -6358,10 +6361,10 @@
       <c r="E180" t="n">
         <v>661</v>
       </c>
-      <c r="F180" t="n">
+      <c r="F180" s="1" t="n">
         <v>59665.49</v>
       </c>
-      <c r="G180" t="n">
+      <c r="G180" s="1" t="n">
         <v>90.13</v>
       </c>
       <c r="H180" t="n">
@@ -6391,10 +6394,10 @@
       <c r="E181" t="n">
         <v>597</v>
       </c>
-      <c r="F181" t="n">
+      <c r="F181" s="1" t="n">
         <v>51970.5</v>
       </c>
-      <c r="G181" t="n">
+      <c r="G181" s="1" t="n">
         <v>78.51000000000001</v>
       </c>
       <c r="H181" t="n">
@@ -6424,10 +6427,10 @@
       <c r="E182" t="n">
         <v>631</v>
       </c>
-      <c r="F182" t="n">
+      <c r="F182" s="1" t="n">
         <v>41977.4</v>
       </c>
-      <c r="G182" t="n">
+      <c r="G182" s="1" t="n">
         <v>64.98</v>
       </c>
       <c r="H182" t="n">
@@ -6457,10 +6460,10 @@
       <c r="E183" t="n">
         <v>595</v>
       </c>
-      <c r="F183" t="n">
+      <c r="F183" s="1" t="n">
         <v>11339.04</v>
       </c>
-      <c r="G183" t="n">
+      <c r="G183" s="1" t="n">
         <v>17.58</v>
       </c>
       <c r="H183" t="n">
@@ -6490,10 +6493,10 @@
       <c r="E184" t="n">
         <v>629</v>
       </c>
-      <c r="F184" t="n">
+      <c r="F184" s="1" t="n">
         <v>134393.58</v>
       </c>
-      <c r="G184" t="n">
+      <c r="G184" s="1" t="n">
         <v>212.31</v>
       </c>
       <c r="H184" t="n">
@@ -6523,10 +6526,10 @@
       <c r="E185" t="n">
         <v>567</v>
       </c>
-      <c r="F185" t="n">
+      <c r="F185" s="1" t="n">
         <v>47120.12</v>
       </c>
-      <c r="G185" t="n">
+      <c r="G185" s="1" t="n">
         <v>76.12</v>
       </c>
       <c r="H185" t="n">
@@ -6556,10 +6559,10 @@
       <c r="E186" t="n">
         <v>552</v>
       </c>
-      <c r="F186" t="n">
+      <c r="F186" s="1" t="n">
         <v>11208.3</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G186" s="1" t="n">
         <v>18.14</v>
       </c>
       <c r="H186" t="n">
@@ -6589,10 +6592,10 @@
       <c r="E187" t="n">
         <v>605</v>
       </c>
-      <c r="F187" t="n">
+      <c r="F187" s="1" t="n">
         <v>37388.83</v>
       </c>
-      <c r="G187" t="n">
+      <c r="G187" s="1" t="n">
         <v>60.5</v>
       </c>
       <c r="H187" t="n">
@@ -6622,10 +6625,10 @@
       <c r="E188" t="n">
         <v>606</v>
       </c>
-      <c r="F188" t="n">
+      <c r="F188" s="1" t="n">
         <v>51330.27</v>
       </c>
-      <c r="G188" t="n">
+      <c r="G188" s="1" t="n">
         <v>83.19</v>
       </c>
       <c r="H188" t="n">
@@ -6655,10 +6658,10 @@
       <c r="E189" t="n">
         <v>590</v>
       </c>
-      <c r="F189" t="n">
+      <c r="F189" s="1" t="n">
         <v>44804.63</v>
       </c>
-      <c r="G189" t="n">
+      <c r="G189" s="1" t="n">
         <v>73.45</v>
       </c>
       <c r="H189" t="n">
@@ -6688,10 +6691,10 @@
       <c r="E190" t="n">
         <v>603</v>
       </c>
-      <c r="F190" t="n">
+      <c r="F190" s="1" t="n">
         <v>45600.56</v>
       </c>
-      <c r="G190" t="n">
+      <c r="G190" s="1" t="n">
         <v>74.88</v>
       </c>
       <c r="H190" t="n">
@@ -6721,10 +6724,10 @@
       <c r="E191" t="n">
         <v>603</v>
       </c>
-      <c r="F191" t="n">
+      <c r="F191" s="1" t="n">
         <v>96270.8</v>
       </c>
-      <c r="G191" t="n">
+      <c r="G191" s="1" t="n">
         <v>158.86</v>
       </c>
       <c r="H191" t="n">
@@ -6754,10 +6757,10 @@
       <c r="E192" t="n">
         <v>598</v>
       </c>
-      <c r="F192" t="n">
+      <c r="F192" s="1" t="n">
         <v>32034.56</v>
       </c>
-      <c r="G192" t="n">
+      <c r="G192" s="1" t="n">
         <v>53.3</v>
       </c>
       <c r="H192" t="n">
@@ -6787,10 +6790,10 @@
       <c r="E193" t="n">
         <v>567</v>
       </c>
-      <c r="F193" t="n">
+      <c r="F193" s="1" t="n">
         <v>34564</v>
       </c>
-      <c r="G193" t="n">
+      <c r="G193" s="1" t="n">
         <v>57.51</v>
       </c>
       <c r="H193" t="n">
@@ -6820,10 +6823,10 @@
       <c r="E194" t="n">
         <v>561</v>
       </c>
-      <c r="F194" t="n">
+      <c r="F194" s="1" t="n">
         <v>15483.94</v>
       </c>
-      <c r="G194" t="n">
+      <c r="G194" s="1" t="n">
         <v>25.94</v>
       </c>
       <c r="H194" t="n">
@@ -6853,10 +6856,10 @@
       <c r="E195" t="n">
         <v>586</v>
       </c>
-      <c r="F195" t="n">
+      <c r="F195" s="1" t="n">
         <v>51052.09</v>
       </c>
-      <c r="G195" t="n">
+      <c r="G195" s="1" t="n">
         <v>86.38</v>
       </c>
       <c r="H195" t="n">
@@ -6886,10 +6889,10 @@
       <c r="E196" t="n">
         <v>557</v>
       </c>
-      <c r="F196" t="n">
+      <c r="F196" s="1" t="n">
         <v>26926.97</v>
       </c>
-      <c r="G196" t="n">
+      <c r="G196" s="1" t="n">
         <v>46.03</v>
       </c>
       <c r="H196" t="n">
@@ -6919,10 +6922,10 @@
       <c r="E197" t="n">
         <v>528</v>
       </c>
-      <c r="F197" t="n">
+      <c r="F197" s="1" t="n">
         <v>13220.35</v>
       </c>
-      <c r="G197" t="n">
+      <c r="G197" s="1" t="n">
         <v>22.68</v>
       </c>
       <c r="H197" t="n">
@@ -6952,10 +6955,10 @@
       <c r="E198" t="n">
         <v>542</v>
       </c>
-      <c r="F198" t="n">
+      <c r="F198" s="1" t="n">
         <v>34421.83</v>
       </c>
-      <c r="G198" t="n">
+      <c r="G198" s="1" t="n">
         <v>59.14</v>
       </c>
       <c r="H198" t="n">
@@ -6985,10 +6988,10 @@
       <c r="E199" t="n">
         <v>563</v>
       </c>
-      <c r="F199" t="n">
+      <c r="F199" s="1" t="n">
         <v>25792.43</v>
       </c>
-      <c r="G199" t="n">
+      <c r="G199" s="1" t="n">
         <v>45.49</v>
       </c>
       <c r="H199" t="n">
@@ -7018,10 +7021,10 @@
       <c r="E200" t="n">
         <v>545</v>
       </c>
-      <c r="F200" t="n">
+      <c r="F200" s="1" t="n">
         <v>20054.19</v>
       </c>
-      <c r="G200" t="n">
+      <c r="G200" s="1" t="n">
         <v>35.49</v>
       </c>
       <c r="H200" t="n">
@@ -7051,10 +7054,10 @@
       <c r="E201" t="n">
         <v>531</v>
       </c>
-      <c r="F201" t="n">
+      <c r="F201" s="1" t="n">
         <v>36410.24</v>
       </c>
-      <c r="G201" t="n">
+      <c r="G201" s="1" t="n">
         <v>66.08</v>
       </c>
       <c r="H201" t="n">
@@ -7084,10 +7087,10 @@
       <c r="E202" t="n">
         <v>531</v>
       </c>
-      <c r="F202" t="n">
+      <c r="F202" s="1" t="n">
         <v>60706.78999999999</v>
       </c>
-      <c r="G202" t="n">
+      <c r="G202" s="1" t="n">
         <v>110.58</v>
       </c>
       <c r="H202" t="n">
@@ -7117,10 +7120,10 @@
       <c r="E203" t="n">
         <v>535</v>
       </c>
-      <c r="F203" t="n">
+      <c r="F203" s="1" t="n">
         <v>74215.35000000001</v>
       </c>
-      <c r="G203" t="n">
+      <c r="G203" s="1" t="n">
         <v>137.69</v>
       </c>
       <c r="H203" t="n">
@@ -7150,10 +7153,10 @@
       <c r="E204" t="n">
         <v>496</v>
       </c>
-      <c r="F204" t="n">
+      <c r="F204" s="1" t="n">
         <v>13337.23</v>
       </c>
-      <c r="G204" t="n">
+      <c r="G204" s="1" t="n">
         <v>24.79</v>
       </c>
       <c r="H204" t="n">
@@ -7183,10 +7186,10 @@
       <c r="E205" t="n">
         <v>526</v>
       </c>
-      <c r="F205" t="n">
+      <c r="F205" s="1" t="n">
         <v>35028.2</v>
       </c>
-      <c r="G205" t="n">
+      <c r="G205" s="1" t="n">
         <v>65.47</v>
       </c>
       <c r="H205" t="n">
@@ -7216,10 +7219,10 @@
       <c r="E206" t="n">
         <v>519</v>
       </c>
-      <c r="F206" t="n">
+      <c r="F206" s="1" t="n">
         <v>57672.3</v>
       </c>
-      <c r="G206" t="n">
+      <c r="G206" s="1" t="n">
         <v>108.41</v>
       </c>
       <c r="H206" t="n">
@@ -7249,10 +7252,10 @@
       <c r="E207" t="n">
         <v>500</v>
       </c>
-      <c r="F207" t="n">
+      <c r="F207" s="1" t="n">
         <v>33613.94</v>
       </c>
-      <c r="G207" t="n">
+      <c r="G207" s="1" t="n">
         <v>63.42</v>
       </c>
       <c r="H207" t="n">
@@ -7282,10 +7285,10 @@
       <c r="E208" t="n">
         <v>487</v>
       </c>
-      <c r="F208" t="n">
+      <c r="F208" s="1" t="n">
         <v>28006.65</v>
       </c>
-      <c r="G208" t="n">
+      <c r="G208" s="1" t="n">
         <v>53.14</v>
       </c>
       <c r="H208" t="n">
@@ -7315,10 +7318,10 @@
       <c r="E209" t="n">
         <v>520</v>
       </c>
-      <c r="F209" t="n">
+      <c r="F209" s="1" t="n">
         <v>17316.19</v>
       </c>
-      <c r="G209" t="n">
+      <c r="G209" s="1" t="n">
         <v>32.86</v>
       </c>
       <c r="H209" t="n">
@@ -7348,10 +7351,10 @@
       <c r="E210" t="n">
         <v>485</v>
       </c>
-      <c r="F210" t="n">
+      <c r="F210" s="1" t="n">
         <v>23260.8</v>
       </c>
-      <c r="G210" t="n">
+      <c r="G210" s="1" t="n">
         <v>44.65</v>
       </c>
       <c r="H210" t="n">
@@ -7381,10 +7384,10 @@
       <c r="E211" t="n">
         <v>520</v>
       </c>
-      <c r="F211" t="n">
+      <c r="F211" s="1" t="n">
         <v>65148.25</v>
       </c>
-      <c r="G211" t="n">
+      <c r="G211" s="1" t="n">
         <v>125.04</v>
       </c>
       <c r="H211" t="n">
@@ -7414,10 +7417,10 @@
       <c r="E212" t="n">
         <v>515</v>
       </c>
-      <c r="F212" t="n">
+      <c r="F212" s="1" t="n">
         <v>35804.05</v>
       </c>
-      <c r="G212" t="n">
+      <c r="G212" s="1" t="n">
         <v>68.72</v>
       </c>
       <c r="H212" t="n">
@@ -7447,10 +7450,10 @@
       <c r="E213" t="n">
         <v>477</v>
       </c>
-      <c r="F213" t="n">
+      <c r="F213" s="1" t="n">
         <v>14901.76</v>
       </c>
-      <c r="G213" t="n">
+      <c r="G213" s="1" t="n">
         <v>28.71</v>
       </c>
       <c r="H213" t="n">
@@ -7480,10 +7483,10 @@
       <c r="E214" t="n">
         <v>515</v>
       </c>
-      <c r="F214" t="n">
+      <c r="F214" s="1" t="n">
         <v>51131.53000000001</v>
       </c>
-      <c r="G214" t="n">
+      <c r="G214" s="1" t="n">
         <v>98.70999999999999</v>
       </c>
       <c r="H214" t="n">
@@ -7513,10 +7516,10 @@
       <c r="E215" t="n">
         <v>509</v>
       </c>
-      <c r="F215" t="n">
+      <c r="F215" s="1" t="n">
         <v>59565.27</v>
       </c>
-      <c r="G215" t="n">
+      <c r="G215" s="1" t="n">
         <v>115.21</v>
       </c>
       <c r="H215" t="n">
@@ -7546,10 +7549,10 @@
       <c r="E216" t="n">
         <v>503</v>
       </c>
-      <c r="F216" t="n">
+      <c r="F216" s="1" t="n">
         <v>23655.7</v>
       </c>
-      <c r="G216" t="n">
+      <c r="G216" s="1" t="n">
         <v>45.93</v>
       </c>
       <c r="H216" t="n">
@@ -7579,10 +7582,10 @@
       <c r="E217" t="n">
         <v>510</v>
       </c>
-      <c r="F217" t="n">
+      <c r="F217" s="1" t="n">
         <v>29464.18</v>
       </c>
-      <c r="G217" t="n">
+      <c r="G217" s="1" t="n">
         <v>57.44</v>
       </c>
       <c r="H217" t="n">
@@ -7612,10 +7615,10 @@
       <c r="E218" t="n">
         <v>505</v>
       </c>
-      <c r="F218" t="n">
+      <c r="F218" s="1" t="n">
         <v>43294.53</v>
       </c>
-      <c r="G218" t="n">
+      <c r="G218" s="1" t="n">
         <v>84.89</v>
       </c>
       <c r="H218" t="n">
@@ -7645,10 +7648,10 @@
       <c r="E219" t="n">
         <v>503</v>
       </c>
-      <c r="F219" t="n">
+      <c r="F219" s="1" t="n">
         <v>35973.44</v>
       </c>
-      <c r="G219" t="n">
+      <c r="G219" s="1" t="n">
         <v>70.67</v>
       </c>
       <c r="H219" t="n">
@@ -7678,10 +7681,10 @@
       <c r="E220" t="n">
         <v>480</v>
       </c>
-      <c r="F220" t="n">
+      <c r="F220" s="1" t="n">
         <v>17974.83</v>
       </c>
-      <c r="G220" t="n">
+      <c r="G220" s="1" t="n">
         <v>35.45</v>
       </c>
       <c r="H220" t="n">
@@ -7711,10 +7714,10 @@
       <c r="E221" t="n">
         <v>504</v>
       </c>
-      <c r="F221" t="n">
+      <c r="F221" s="1" t="n">
         <v>23251.11</v>
       </c>
-      <c r="G221" t="n">
+      <c r="G221" s="1" t="n">
         <v>45.95</v>
       </c>
       <c r="H221" t="n">
@@ -7744,10 +7747,10 @@
       <c r="E222" t="n">
         <v>490</v>
       </c>
-      <c r="F222" t="n">
+      <c r="F222" s="1" t="n">
         <v>30793.57</v>
       </c>
-      <c r="G222" t="n">
+      <c r="G222" s="1" t="n">
         <v>61.1</v>
       </c>
       <c r="H222" t="n">
@@ -7777,10 +7780,10 @@
       <c r="E223" t="n">
         <v>496</v>
       </c>
-      <c r="F223" t="n">
+      <c r="F223" s="1" t="n">
         <v>23795.6</v>
       </c>
-      <c r="G223" t="n">
+      <c r="G223" s="1" t="n">
         <v>47.4</v>
       </c>
       <c r="H223" t="n">
@@ -7810,10 +7813,10 @@
       <c r="E224" t="n">
         <v>495</v>
       </c>
-      <c r="F224" t="n">
+      <c r="F224" s="1" t="n">
         <v>39764.67</v>
       </c>
-      <c r="G224" t="n">
+      <c r="G224" s="1" t="n">
         <v>79.53</v>
       </c>
       <c r="H224" t="n">
@@ -7843,10 +7846,10 @@
       <c r="E225" t="n">
         <v>482</v>
       </c>
-      <c r="F225" t="n">
+      <c r="F225" s="1" t="n">
         <v>31148.2</v>
       </c>
-      <c r="G225" t="n">
+      <c r="G225" s="1" t="n">
         <v>62.67</v>
       </c>
       <c r="H225" t="n">
@@ -7876,10 +7879,10 @@
       <c r="E226" t="n">
         <v>486</v>
       </c>
-      <c r="F226" t="n">
+      <c r="F226" s="1" t="n">
         <v>23258.04</v>
       </c>
-      <c r="G226" t="n">
+      <c r="G226" s="1" t="n">
         <v>46.8</v>
       </c>
       <c r="H226" t="n">
@@ -7909,10 +7912,10 @@
       <c r="E227" t="n">
         <v>399</v>
       </c>
-      <c r="F227" t="n">
+      <c r="F227" s="1" t="n">
         <v>23252.7</v>
       </c>
-      <c r="G227" t="n">
+      <c r="G227" s="1" t="n">
         <v>46.98</v>
       </c>
       <c r="H227" t="n">
@@ -7942,10 +7945,10 @@
       <c r="E228" t="n">
         <v>437</v>
       </c>
-      <c r="F228" t="n">
+      <c r="F228" s="1" t="n">
         <v>12720.53</v>
       </c>
-      <c r="G228" t="n">
+      <c r="G228" s="1" t="n">
         <v>25.7</v>
       </c>
       <c r="H228" t="n">
@@ -7975,10 +7978,10 @@
       <c r="E229" t="n">
         <v>429</v>
       </c>
-      <c r="F229" t="n">
+      <c r="F229" s="1" t="n">
         <v>23077.74</v>
       </c>
-      <c r="G229" t="n">
+      <c r="G229" s="1" t="n">
         <v>46.81</v>
       </c>
       <c r="H229" t="n">
@@ -8008,10 +8011,10 @@
       <c r="E230" t="n">
         <v>480</v>
       </c>
-      <c r="F230" t="n">
+      <c r="F230" s="1" t="n">
         <v>24102.55</v>
       </c>
-      <c r="G230" t="n">
+      <c r="G230" s="1" t="n">
         <v>48.99</v>
       </c>
       <c r="H230" t="n">
@@ -8041,10 +8044,10 @@
       <c r="E231" t="n">
         <v>467</v>
       </c>
-      <c r="F231" t="n">
+      <c r="F231" s="1" t="n">
         <v>47361.39</v>
       </c>
-      <c r="G231" t="n">
+      <c r="G231" s="1" t="n">
         <v>96.26000000000001</v>
       </c>
       <c r="H231" t="n">
@@ -8074,10 +8077,10 @@
       <c r="E232" t="n">
         <v>486</v>
       </c>
-      <c r="F232" t="n">
+      <c r="F232" s="1" t="n">
         <v>27426.78</v>
       </c>
-      <c r="G232" t="n">
+      <c r="G232" s="1" t="n">
         <v>55.86</v>
       </c>
       <c r="H232" t="n">
@@ -8107,10 +8110,10 @@
       <c r="E233" t="n">
         <v>473</v>
       </c>
-      <c r="F233" t="n">
+      <c r="F233" s="1" t="n">
         <v>42918.01</v>
       </c>
-      <c r="G233" t="n">
+      <c r="G233" s="1" t="n">
         <v>87.41</v>
       </c>
       <c r="H233" t="n">
@@ -8140,10 +8143,10 @@
       <c r="E234" t="n">
         <v>483</v>
       </c>
-      <c r="F234" t="n">
+      <c r="F234" s="1" t="n">
         <v>33091.01</v>
       </c>
-      <c r="G234" t="n">
+      <c r="G234" s="1" t="n">
         <v>67.53</v>
       </c>
       <c r="H234" t="n">
@@ -8173,10 +8176,10 @@
       <c r="E235" t="n">
         <v>463</v>
       </c>
-      <c r="F235" t="n">
+      <c r="F235" s="1" t="n">
         <v>31502.54</v>
       </c>
-      <c r="G235" t="n">
+      <c r="G235" s="1" t="n">
         <v>64.55</v>
       </c>
       <c r="H235" t="n">
@@ -8206,10 +8209,10 @@
       <c r="E236" t="n">
         <v>438</v>
       </c>
-      <c r="F236" t="n">
+      <c r="F236" s="1" t="n">
         <v>12255.24</v>
       </c>
-      <c r="G236" t="n">
+      <c r="G236" s="1" t="n">
         <v>25.11</v>
       </c>
       <c r="H236" t="n">
@@ -8239,10 +8242,10 @@
       <c r="E237" t="n">
         <v>484</v>
       </c>
-      <c r="F237" t="n">
+      <c r="F237" s="1" t="n">
         <v>26014.9</v>
       </c>
-      <c r="G237" t="n">
+      <c r="G237" s="1" t="n">
         <v>53.42</v>
       </c>
       <c r="H237" t="n">
@@ -8272,10 +8275,10 @@
       <c r="E238" t="n">
         <v>454</v>
       </c>
-      <c r="F238" t="n">
+      <c r="F238" s="1" t="n">
         <v>24024.08</v>
       </c>
-      <c r="G238" t="n">
+      <c r="G238" s="1" t="n">
         <v>49.74</v>
       </c>
       <c r="H238" t="n">
@@ -8305,10 +8308,10 @@
       <c r="E239" t="n">
         <v>470</v>
       </c>
-      <c r="F239" t="n">
+      <c r="F239" s="1" t="n">
         <v>50636.45</v>
       </c>
-      <c r="G239" t="n">
+      <c r="G239" s="1" t="n">
         <v>105.27</v>
       </c>
       <c r="H239" t="n">
@@ -8338,10 +8341,10 @@
       <c r="E240" t="n">
         <v>478</v>
       </c>
-      <c r="F240" t="n">
+      <c r="F240" s="1" t="n">
         <v>44420.08</v>
       </c>
-      <c r="G240" t="n">
+      <c r="G240" s="1" t="n">
         <v>92.34999999999999</v>
       </c>
       <c r="H240" t="n">
@@ -8371,10 +8374,10 @@
       <c r="E241" t="n">
         <v>480</v>
       </c>
-      <c r="F241" t="n">
+      <c r="F241" s="1" t="n">
         <v>28586.6</v>
       </c>
-      <c r="G241" t="n">
+      <c r="G241" s="1" t="n">
         <v>59.56</v>
       </c>
       <c r="H241" t="n">
@@ -8404,10 +8407,10 @@
       <c r="E242" t="n">
         <v>460</v>
       </c>
-      <c r="F242" t="n">
+      <c r="F242" s="1" t="n">
         <v>33862.65</v>
       </c>
-      <c r="G242" t="n">
+      <c r="G242" s="1" t="n">
         <v>70.84</v>
       </c>
       <c r="H242" t="n">
@@ -8437,10 +8440,10 @@
       <c r="E243" t="n">
         <v>469</v>
       </c>
-      <c r="F243" t="n">
+      <c r="F243" s="1" t="n">
         <v>55229.35</v>
       </c>
-      <c r="G243" t="n">
+      <c r="G243" s="1" t="n">
         <v>115.78</v>
       </c>
       <c r="H243" t="n">
@@ -8470,10 +8473,10 @@
       <c r="E244" t="n">
         <v>410</v>
       </c>
-      <c r="F244" t="n">
+      <c r="F244" s="1" t="n">
         <v>7177.96</v>
       </c>
-      <c r="G244" t="n">
+      <c r="G244" s="1" t="n">
         <v>15.24</v>
       </c>
       <c r="H244" t="n">
@@ -8503,10 +8506,10 @@
       <c r="E245" t="n">
         <v>461</v>
       </c>
-      <c r="F245" t="n">
+      <c r="F245" s="1" t="n">
         <v>28999.37</v>
       </c>
-      <c r="G245" t="n">
+      <c r="G245" s="1" t="n">
         <v>62.36</v>
       </c>
       <c r="H245" t="n">
@@ -8536,10 +8539,10 @@
       <c r="E246" t="n">
         <v>463</v>
       </c>
-      <c r="F246" t="n">
+      <c r="F246" s="1" t="n">
         <v>18440.83</v>
       </c>
-      <c r="G246" t="n">
+      <c r="G246" s="1" t="n">
         <v>39.74</v>
       </c>
       <c r="H246" t="n">
@@ -8569,10 +8572,10 @@
       <c r="E247" t="n">
         <v>454</v>
       </c>
-      <c r="F247" t="n">
+      <c r="F247" s="1" t="n">
         <v>12635.32</v>
       </c>
-      <c r="G247" t="n">
+      <c r="G247" s="1" t="n">
         <v>27.35</v>
       </c>
       <c r="H247" t="n">
@@ -8602,10 +8605,10 @@
       <c r="E248" t="n">
         <v>447</v>
       </c>
-      <c r="F248" t="n">
+      <c r="F248" s="1" t="n">
         <v>27367.99</v>
       </c>
-      <c r="G248" t="n">
+      <c r="G248" s="1" t="n">
         <v>59.37</v>
       </c>
       <c r="H248" t="n">
@@ -8635,10 +8638,10 @@
       <c r="E249" t="n">
         <v>447</v>
       </c>
-      <c r="F249" t="n">
+      <c r="F249" s="1" t="n">
         <v>34975.56</v>
       </c>
-      <c r="G249" t="n">
+      <c r="G249" s="1" t="n">
         <v>76.2</v>
       </c>
       <c r="H249" t="n">
@@ -8668,10 +8671,10 @@
       <c r="E250" t="n">
         <v>444</v>
       </c>
-      <c r="F250" t="n">
+      <c r="F250" s="1" t="n">
         <v>18723.81</v>
       </c>
-      <c r="G250" t="n">
+      <c r="G250" s="1" t="n">
         <v>41.24</v>
       </c>
       <c r="H250" t="n">
@@ -8701,10 +8704,10 @@
       <c r="E251" t="n">
         <v>450</v>
       </c>
-      <c r="F251" t="n">
+      <c r="F251" s="1" t="n">
         <v>21577.17</v>
       </c>
-      <c r="G251" t="n">
+      <c r="G251" s="1" t="n">
         <v>47.63</v>
       </c>
       <c r="H251" t="n">
@@ -8734,10 +8737,10 @@
       <c r="E252" t="n">
         <v>449</v>
       </c>
-      <c r="F252" t="n">
+      <c r="F252" s="1" t="n">
         <v>20455.37</v>
       </c>
-      <c r="G252" t="n">
+      <c r="G252" s="1" t="n">
         <v>45.26</v>
       </c>
       <c r="H252" t="n">
@@ -8767,10 +8770,10 @@
       <c r="E253" t="n">
         <v>441</v>
       </c>
-      <c r="F253" t="n">
+      <c r="F253" s="1" t="n">
         <v>29885.26</v>
       </c>
-      <c r="G253" t="n">
+      <c r="G253" s="1" t="n">
         <v>66.41</v>
       </c>
       <c r="H253" t="n">
@@ -8800,10 +8803,10 @@
       <c r="E254" t="n">
         <v>396</v>
       </c>
-      <c r="F254" t="n">
+      <c r="F254" s="1" t="n">
         <v>22925.5</v>
       </c>
-      <c r="G254" t="n">
+      <c r="G254" s="1" t="n">
         <v>51.17</v>
       </c>
       <c r="H254" t="n">
@@ -8833,10 +8836,10 @@
       <c r="E255" t="n">
         <v>390</v>
       </c>
-      <c r="F255" t="n">
+      <c r="F255" s="1" t="n">
         <v>19542.72</v>
       </c>
-      <c r="G255" t="n">
+      <c r="G255" s="1" t="n">
         <v>44.72</v>
       </c>
       <c r="H255" t="n">
@@ -8866,10 +8869,10 @@
       <c r="E256" t="n">
         <v>429</v>
       </c>
-      <c r="F256" t="n">
+      <c r="F256" s="1" t="n">
         <v>47983.11</v>
       </c>
-      <c r="G256" t="n">
+      <c r="G256" s="1" t="n">
         <v>110.56</v>
       </c>
       <c r="H256" t="n">
@@ -8899,10 +8902,10 @@
       <c r="E257" t="n">
         <v>424</v>
       </c>
-      <c r="F257" t="n">
+      <c r="F257" s="1" t="n">
         <v>28044.97</v>
       </c>
-      <c r="G257" t="n">
+      <c r="G257" s="1" t="n">
         <v>64.77</v>
       </c>
       <c r="H257" t="n">
@@ -8932,10 +8935,10 @@
       <c r="E258" t="n">
         <v>420</v>
       </c>
-      <c r="F258" t="n">
+      <c r="F258" s="1" t="n">
         <v>18479.74</v>
       </c>
-      <c r="G258" t="n">
+      <c r="G258" s="1" t="n">
         <v>43.89</v>
       </c>
       <c r="H258" t="n">
@@ -8965,10 +8968,10 @@
       <c r="E259" t="n">
         <v>415</v>
       </c>
-      <c r="F259" t="n">
+      <c r="F259" s="1" t="n">
         <v>22933.66</v>
       </c>
-      <c r="G259" t="n">
+      <c r="G259" s="1" t="n">
         <v>54.6</v>
       </c>
       <c r="H259" t="n">
@@ -8998,10 +9001,10 @@
       <c r="E260" t="n">
         <v>357</v>
       </c>
-      <c r="F260" t="n">
+      <c r="F260" s="1" t="n">
         <v>6390.15</v>
       </c>
-      <c r="G260" t="n">
+      <c r="G260" s="1" t="n">
         <v>15.36</v>
       </c>
       <c r="H260" t="n">
@@ -9031,10 +9034,10 @@
       <c r="E261" t="n">
         <v>384</v>
       </c>
-      <c r="F261" t="n">
+      <c r="F261" s="1" t="n">
         <v>26813.76</v>
       </c>
-      <c r="G261" t="n">
+      <c r="G261" s="1" t="n">
         <v>65.23999999999999</v>
       </c>
       <c r="H261" t="n">
@@ -9064,10 +9067,10 @@
       <c r="E262" t="n">
         <v>406</v>
       </c>
-      <c r="F262" t="n">
+      <c r="F262" s="1" t="n">
         <v>23188.32</v>
       </c>
-      <c r="G262" t="n">
+      <c r="G262" s="1" t="n">
         <v>56.7</v>
       </c>
       <c r="H262" t="n">
@@ -9097,10 +9100,10 @@
       <c r="E263" t="n">
         <v>399</v>
       </c>
-      <c r="F263" t="n">
+      <c r="F263" s="1" t="n">
         <v>35662.77</v>
       </c>
-      <c r="G263" t="n">
+      <c r="G263" s="1" t="n">
         <v>88.48999999999999</v>
       </c>
       <c r="H263" t="n">
@@ -9130,10 +9133,10 @@
       <c r="E264" t="n">
         <v>398</v>
       </c>
-      <c r="F264" t="n">
+      <c r="F264" s="1" t="n">
         <v>52291.94</v>
       </c>
-      <c r="G264" t="n">
+      <c r="G264" s="1" t="n">
         <v>130.73</v>
       </c>
       <c r="H264" t="n">
@@ -9163,10 +9166,10 @@
       <c r="E265" t="n">
         <v>371</v>
       </c>
-      <c r="F265" t="n">
+      <c r="F265" s="1" t="n">
         <v>22792.73</v>
       </c>
-      <c r="G265" t="n">
+      <c r="G265" s="1" t="n">
         <v>57.27</v>
       </c>
       <c r="H265" t="n">
@@ -9196,10 +9199,10 @@
       <c r="E266" t="n">
         <v>394</v>
       </c>
-      <c r="F266" t="n">
+      <c r="F266" s="1" t="n">
         <v>31629.35</v>
       </c>
-      <c r="G266" t="n">
+      <c r="G266" s="1" t="n">
         <v>80.28</v>
       </c>
       <c r="H266" t="n">
@@ -9229,10 +9232,10 @@
       <c r="E267" t="n">
         <v>386</v>
       </c>
-      <c r="F267" t="n">
+      <c r="F267" s="1" t="n">
         <v>18341.57</v>
       </c>
-      <c r="G267" t="n">
+      <c r="G267" s="1" t="n">
         <v>46.67</v>
       </c>
       <c r="H267" t="n">
@@ -9262,10 +9265,10 @@
       <c r="E268" t="n">
         <v>380</v>
       </c>
-      <c r="F268" t="n">
+      <c r="F268" s="1" t="n">
         <v>51068.13</v>
       </c>
-      <c r="G268" t="n">
+      <c r="G268" s="1" t="n">
         <v>131.28</v>
       </c>
       <c r="H268" t="n">
@@ -9295,10 +9298,10 @@
       <c r="E269" t="n">
         <v>389</v>
       </c>
-      <c r="F269" t="n">
+      <c r="F269" s="1" t="n">
         <v>25011.84</v>
       </c>
-      <c r="G269" t="n">
+      <c r="G269" s="1" t="n">
         <v>64.3</v>
       </c>
       <c r="H269" t="n">
@@ -9328,10 +9331,10 @@
       <c r="E270" t="n">
         <v>346</v>
       </c>
-      <c r="F270" t="n">
+      <c r="F270" s="1" t="n">
         <v>12242.66</v>
       </c>
-      <c r="G270" t="n">
+      <c r="G270" s="1" t="n">
         <v>31.47</v>
       </c>
       <c r="H270" t="n">
@@ -9361,10 +9364,10 @@
       <c r="E271" t="n">
         <v>345</v>
       </c>
-      <c r="F271" t="n">
+      <c r="F271" s="1" t="n">
         <v>7831.5</v>
       </c>
-      <c r="G271" t="n">
+      <c r="G271" s="1" t="n">
         <v>20.29</v>
       </c>
       <c r="H271" t="n">
@@ -9394,10 +9397,10 @@
       <c r="E272" t="n">
         <v>355</v>
       </c>
-      <c r="F272" t="n">
+      <c r="F272" s="1" t="n">
         <v>17227.56</v>
       </c>
-      <c r="G272" t="n">
+      <c r="G272" s="1" t="n">
         <v>44.75</v>
       </c>
       <c r="H272" t="n">
@@ -9427,10 +9430,10 @@
       <c r="E273" t="n">
         <v>373</v>
       </c>
-      <c r="F273" t="n">
+      <c r="F273" s="1" t="n">
         <v>26286.49</v>
       </c>
-      <c r="G273" t="n">
+      <c r="G273" s="1" t="n">
         <v>68.63</v>
       </c>
       <c r="H273" t="n">
@@ -9460,10 +9463,10 @@
       <c r="E274" t="n">
         <v>375</v>
       </c>
-      <c r="F274" t="n">
+      <c r="F274" s="1" t="n">
         <v>17181.41</v>
       </c>
-      <c r="G274" t="n">
+      <c r="G274" s="1" t="n">
         <v>44.86</v>
       </c>
       <c r="H274" t="n">
@@ -9493,10 +9496,10 @@
       <c r="E275" t="n">
         <v>381</v>
       </c>
-      <c r="F275" t="n">
+      <c r="F275" s="1" t="n">
         <v>40639.82</v>
       </c>
-      <c r="G275" t="n">
+      <c r="G275" s="1" t="n">
         <v>106.67</v>
       </c>
       <c r="H275" t="n">
@@ -9526,10 +9529,10 @@
       <c r="E276" t="n">
         <v>363</v>
       </c>
-      <c r="F276" t="n">
+      <c r="F276" s="1" t="n">
         <v>20559.58</v>
       </c>
-      <c r="G276" t="n">
+      <c r="G276" s="1" t="n">
         <v>54.25</v>
       </c>
       <c r="H276" t="n">
@@ -9559,10 +9562,10 @@
       <c r="E277" t="n">
         <v>364</v>
       </c>
-      <c r="F277" t="n">
+      <c r="F277" s="1" t="n">
         <v>27779.63</v>
       </c>
-      <c r="G277" t="n">
+      <c r="G277" s="1" t="n">
         <v>73.48999999999999</v>
       </c>
       <c r="H277" t="n">
@@ -9592,10 +9595,10 @@
       <c r="E278" t="n">
         <v>370</v>
       </c>
-      <c r="F278" t="n">
+      <c r="F278" s="1" t="n">
         <v>16756.7</v>
       </c>
-      <c r="G278" t="n">
+      <c r="G278" s="1" t="n">
         <v>44.92</v>
       </c>
       <c r="H278" t="n">
@@ -9625,10 +9628,10 @@
       <c r="E279" t="n">
         <v>364</v>
       </c>
-      <c r="F279" t="n">
+      <c r="F279" s="1" t="n">
         <v>32155.82</v>
       </c>
-      <c r="G279" t="n">
+      <c r="G279" s="1" t="n">
         <v>86.44</v>
       </c>
       <c r="H279" t="n">
@@ -9658,10 +9661,10 @@
       <c r="E280" t="n">
         <v>370</v>
       </c>
-      <c r="F280" t="n">
+      <c r="F280" s="1" t="n">
         <v>42970.32</v>
       </c>
-      <c r="G280" t="n">
+      <c r="G280" s="1" t="n">
         <v>115.82</v>
       </c>
       <c r="H280" t="n">
@@ -9691,10 +9694,10 @@
       <c r="E281" t="n">
         <v>345</v>
       </c>
-      <c r="F281" t="n">
+      <c r="F281" s="1" t="n">
         <v>5469.8</v>
       </c>
-      <c r="G281" t="n">
+      <c r="G281" s="1" t="n">
         <v>14.78</v>
       </c>
       <c r="H281" t="n">
@@ -9724,10 +9727,10 @@
       <c r="E282" t="n">
         <v>366</v>
       </c>
-      <c r="F282" t="n">
+      <c r="F282" s="1" t="n">
         <v>40134.65</v>
       </c>
-      <c r="G282" t="n">
+      <c r="G282" s="1" t="n">
         <v>108.77</v>
       </c>
       <c r="H282" t="n">
@@ -9757,10 +9760,10 @@
       <c r="E283" t="n">
         <v>360</v>
       </c>
-      <c r="F283" t="n">
+      <c r="F283" s="1" t="n">
         <v>23787.41</v>
       </c>
-      <c r="G283" t="n">
+      <c r="G283" s="1" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="H283" t="n">
@@ -9790,10 +9793,10 @@
       <c r="E284" t="n">
         <v>360</v>
       </c>
-      <c r="F284" t="n">
+      <c r="F284" s="1" t="n">
         <v>32069.73</v>
       </c>
-      <c r="G284" t="n">
+      <c r="G284" s="1" t="n">
         <v>88.34999999999999</v>
       </c>
       <c r="H284" t="n">
@@ -9823,10 +9826,10 @@
       <c r="E285" t="n">
         <v>359</v>
       </c>
-      <c r="F285" t="n">
+      <c r="F285" s="1" t="n">
         <v>40829.15</v>
       </c>
-      <c r="G285" t="n">
+      <c r="G285" s="1" t="n">
         <v>112.79</v>
       </c>
       <c r="H285" t="n">
@@ -9856,10 +9859,10 @@
       <c r="E286" t="n">
         <v>326</v>
       </c>
-      <c r="F286" t="n">
+      <c r="F286" s="1" t="n">
         <v>18085.08</v>
       </c>
-      <c r="G286" t="n">
+      <c r="G286" s="1" t="n">
         <v>49.96</v>
       </c>
       <c r="H286" t="n">
@@ -9889,10 +9892,10 @@
       <c r="E287" t="n">
         <v>350</v>
       </c>
-      <c r="F287" t="n">
+      <c r="F287" s="1" t="n">
         <v>29264.36</v>
       </c>
-      <c r="G287" t="n">
+      <c r="G287" s="1" t="n">
         <v>81.06</v>
       </c>
       <c r="H287" t="n">
@@ -9922,10 +9925,10 @@
       <c r="E288" t="n">
         <v>327</v>
       </c>
-      <c r="F288" t="n">
+      <c r="F288" s="1" t="n">
         <v>5126.01</v>
       </c>
-      <c r="G288" t="n">
+      <c r="G288" s="1" t="n">
         <v>14.36</v>
       </c>
       <c r="H288" t="n">
@@ -9955,10 +9958,10 @@
       <c r="E289" t="n">
         <v>349</v>
       </c>
-      <c r="F289" t="n">
+      <c r="F289" s="1" t="n">
         <v>20024.73</v>
       </c>
-      <c r="G289" t="n">
+      <c r="G289" s="1" t="n">
         <v>56.09</v>
       </c>
       <c r="H289" t="n">
@@ -9988,10 +9991,10 @@
       <c r="E290" t="n">
         <v>351</v>
       </c>
-      <c r="F290" t="n">
+      <c r="F290" s="1" t="n">
         <v>12720</v>
       </c>
-      <c r="G290" t="n">
+      <c r="G290" s="1" t="n">
         <v>35.93</v>
       </c>
       <c r="H290" t="n">
@@ -10021,10 +10024,10 @@
       <c r="E291" t="n">
         <v>350</v>
       </c>
-      <c r="F291" t="n">
+      <c r="F291" s="1" t="n">
         <v>23123.58</v>
       </c>
-      <c r="G291" t="n">
+      <c r="G291" s="1" t="n">
         <v>65.69</v>
       </c>
       <c r="H291" t="n">
@@ -10054,10 +10057,10 @@
       <c r="E292" t="n">
         <v>309</v>
       </c>
-      <c r="F292" t="n">
+      <c r="F292" s="1" t="n">
         <v>5162.16</v>
       </c>
-      <c r="G292" t="n">
+      <c r="G292" s="1" t="n">
         <v>14.71</v>
       </c>
       <c r="H292" t="n">
@@ -10087,10 +10090,10 @@
       <c r="E293" t="n">
         <v>345</v>
       </c>
-      <c r="F293" t="n">
+      <c r="F293" s="1" t="n">
         <v>17478.25</v>
       </c>
-      <c r="G293" t="n">
+      <c r="G293" s="1" t="n">
         <v>50.22</v>
       </c>
       <c r="H293" t="n">
@@ -10120,10 +10123,10 @@
       <c r="E294" t="n">
         <v>306</v>
       </c>
-      <c r="F294" t="n">
+      <c r="F294" s="1" t="n">
         <v>44526.8</v>
       </c>
-      <c r="G294" t="n">
+      <c r="G294" s="1" t="n">
         <v>128.32</v>
       </c>
       <c r="H294" t="n">
@@ -10153,10 +10156,10 @@
       <c r="E295" t="n">
         <v>334</v>
       </c>
-      <c r="F295" t="n">
+      <c r="F295" s="1" t="n">
         <v>16883.31</v>
       </c>
-      <c r="G295" t="n">
+      <c r="G295" s="1" t="n">
         <v>49.95</v>
       </c>
       <c r="H295" t="n">
@@ -10186,10 +10189,10 @@
       <c r="E296" t="n">
         <v>336</v>
       </c>
-      <c r="F296" t="n">
+      <c r="F296" s="1" t="n">
         <v>38859.61</v>
       </c>
-      <c r="G296" t="n">
+      <c r="G296" s="1" t="n">
         <v>115.31</v>
       </c>
       <c r="H296" t="n">
@@ -10219,10 +10222,10 @@
       <c r="E297" t="n">
         <v>328</v>
       </c>
-      <c r="F297" t="n">
+      <c r="F297" s="1" t="n">
         <v>20493.99</v>
       </c>
-      <c r="G297" t="n">
+      <c r="G297" s="1" t="n">
         <v>60.99</v>
       </c>
       <c r="H297" t="n">
@@ -10252,10 +10255,10 @@
       <c r="E298" t="n">
         <v>322</v>
       </c>
-      <c r="F298" t="n">
+      <c r="F298" s="1" t="n">
         <v>14623.21</v>
       </c>
-      <c r="G298" t="n">
+      <c r="G298" s="1" t="n">
         <v>43.52</v>
       </c>
       <c r="H298" t="n">
@@ -10285,10 +10288,10 @@
       <c r="E299" t="n">
         <v>318</v>
       </c>
-      <c r="F299" t="n">
+      <c r="F299" s="1" t="n">
         <v>14990.86</v>
       </c>
-      <c r="G299" t="n">
+      <c r="G299" s="1" t="n">
         <v>45.02</v>
       </c>
       <c r="H299" t="n">
@@ -10318,10 +10321,10 @@
       <c r="E300" t="n">
         <v>323</v>
       </c>
-      <c r="F300" t="n">
+      <c r="F300" s="1" t="n">
         <v>12966.67</v>
       </c>
-      <c r="G300" t="n">
+      <c r="G300" s="1" t="n">
         <v>39.41</v>
       </c>
       <c r="H300" t="n">
@@ -10351,10 +10354,10 @@
       <c r="E301" t="n">
         <v>323</v>
       </c>
-      <c r="F301" t="n">
+      <c r="F301" s="1" t="n">
         <v>13159.6</v>
       </c>
-      <c r="G301" t="n">
+      <c r="G301" s="1" t="n">
         <v>40.12</v>
       </c>
       <c r="H301" t="n">
@@ -10384,10 +10387,10 @@
       <c r="E302" t="n">
         <v>325</v>
       </c>
-      <c r="F302" t="n">
+      <c r="F302" s="1" t="n">
         <v>25685.65</v>
       </c>
-      <c r="G302" t="n">
+      <c r="G302" s="1" t="n">
         <v>78.31</v>
       </c>
       <c r="H302" t="n">
@@ -10417,10 +10420,10 @@
       <c r="E303" t="n">
         <v>320</v>
       </c>
-      <c r="F303" t="n">
+      <c r="F303" s="1" t="n">
         <v>24602.51</v>
       </c>
-      <c r="G303" t="n">
+      <c r="G303" s="1" t="n">
         <v>75.7</v>
       </c>
       <c r="H303" t="n">
@@ -10450,10 +10453,10 @@
       <c r="E304" t="n">
         <v>305</v>
       </c>
-      <c r="F304" t="n">
+      <c r="F304" s="1" t="n">
         <v>13482.35</v>
       </c>
-      <c r="G304" t="n">
+      <c r="G304" s="1" t="n">
         <v>41.74</v>
       </c>
       <c r="H304" t="n">
@@ -10483,10 +10486,10 @@
       <c r="E305" t="n">
         <v>319</v>
       </c>
-      <c r="F305" t="n">
+      <c r="F305" s="1" t="n">
         <v>23701.46</v>
       </c>
-      <c r="G305" t="n">
+      <c r="G305" s="1" t="n">
         <v>73.61</v>
       </c>
       <c r="H305" t="n">
@@ -10516,10 +10519,10 @@
       <c r="E306" t="n">
         <v>321</v>
       </c>
-      <c r="F306" t="n">
+      <c r="F306" s="1" t="n">
         <v>14738.96</v>
       </c>
-      <c r="G306" t="n">
+      <c r="G306" s="1" t="n">
         <v>45.92</v>
       </c>
       <c r="H306" t="n">
@@ -10549,10 +10552,10 @@
       <c r="E307" t="n">
         <v>290</v>
       </c>
-      <c r="F307" t="n">
+      <c r="F307" s="1" t="n">
         <v>25046.62</v>
       </c>
-      <c r="G307" t="n">
+      <c r="G307" s="1" t="n">
         <v>78.27</v>
       </c>
       <c r="H307" t="n">
@@ -10582,10 +10585,10 @@
       <c r="E308" t="n">
         <v>267</v>
       </c>
-      <c r="F308" t="n">
+      <c r="F308" s="1" t="n">
         <v>15661.82</v>
       </c>
-      <c r="G308" t="n">
+      <c r="G308" s="1" t="n">
         <v>48.94</v>
       </c>
       <c r="H308" t="n">
@@ -10615,10 +10618,10 @@
       <c r="E309" t="n">
         <v>309</v>
       </c>
-      <c r="F309" t="n">
+      <c r="F309" s="1" t="n">
         <v>21089.55</v>
       </c>
-      <c r="G309" t="n">
+      <c r="G309" s="1" t="n">
         <v>66.11</v>
       </c>
       <c r="H309" t="n">
@@ -10648,10 +10651,10 @@
       <c r="E310" t="n">
         <v>316</v>
       </c>
-      <c r="F310" t="n">
+      <c r="F310" s="1" t="n">
         <v>18048.64</v>
       </c>
-      <c r="G310" t="n">
+      <c r="G310" s="1" t="n">
         <v>56.94</v>
       </c>
       <c r="H310" t="n">
@@ -10681,10 +10684,10 @@
       <c r="E311" t="n">
         <v>314</v>
       </c>
-      <c r="F311" t="n">
+      <c r="F311" s="1" t="n">
         <v>21228.77</v>
       </c>
-      <c r="G311" t="n">
+      <c r="G311" s="1" t="n">
         <v>66.97</v>
       </c>
       <c r="H311" t="n">
@@ -10714,10 +10717,10 @@
       <c r="E312" t="n">
         <v>309</v>
       </c>
-      <c r="F312" t="n">
+      <c r="F312" s="1" t="n">
         <v>23621.01</v>
       </c>
-      <c r="G312" t="n">
+      <c r="G312" s="1" t="n">
         <v>76.2</v>
       </c>
       <c r="H312" t="n">
@@ -10747,10 +10750,10 @@
       <c r="E313" t="n">
         <v>304</v>
       </c>
-      <c r="F313" t="n">
+      <c r="F313" s="1" t="n">
         <v>26157.99</v>
       </c>
-      <c r="G313" t="n">
+      <c r="G313" s="1" t="n">
         <v>85.76000000000001</v>
       </c>
       <c r="H313" t="n">
@@ -10780,10 +10783,10 @@
       <c r="E314" t="n">
         <v>299</v>
       </c>
-      <c r="F314" t="n">
+      <c r="F314" s="1" t="n">
         <v>36069.47</v>
       </c>
-      <c r="G314" t="n">
+      <c r="G314" s="1" t="n">
         <v>119.44</v>
       </c>
       <c r="H314" t="n">
@@ -10813,10 +10816,10 @@
       <c r="E315" t="n">
         <v>292</v>
       </c>
-      <c r="F315" t="n">
+      <c r="F315" s="1" t="n">
         <v>26896.27</v>
       </c>
-      <c r="G315" t="n">
+      <c r="G315" s="1" t="n">
         <v>90.26000000000001</v>
       </c>
       <c r="H315" t="n">
@@ -10846,10 +10849,10 @@
       <c r="E316" t="n">
         <v>296</v>
       </c>
-      <c r="F316" t="n">
+      <c r="F316" s="1" t="n">
         <v>23005.33</v>
       </c>
-      <c r="G316" t="n">
+      <c r="G316" s="1" t="n">
         <v>77.72</v>
       </c>
       <c r="H316" t="n">
@@ -10879,10 +10882,10 @@
       <c r="E317" t="n">
         <v>293</v>
       </c>
-      <c r="F317" t="n">
+      <c r="F317" s="1" t="n">
         <v>34267.36</v>
       </c>
-      <c r="G317" t="n">
+      <c r="G317" s="1" t="n">
         <v>115.77</v>
       </c>
       <c r="H317" t="n">
@@ -10912,10 +10915,10 @@
       <c r="E318" t="n">
         <v>295</v>
       </c>
-      <c r="F318" t="n">
+      <c r="F318" s="1" t="n">
         <v>22266.18</v>
       </c>
-      <c r="G318" t="n">
+      <c r="G318" s="1" t="n">
         <v>75.48</v>
       </c>
       <c r="H318" t="n">
@@ -10945,10 +10948,10 @@
       <c r="E319" t="n">
         <v>291</v>
       </c>
-      <c r="F319" t="n">
+      <c r="F319" s="1" t="n">
         <v>54472.37</v>
       </c>
-      <c r="G319" t="n">
+      <c r="G319" s="1" t="n">
         <v>186.55</v>
       </c>
       <c r="H319" t="n">
@@ -10978,10 +10981,10 @@
       <c r="E320" t="n">
         <v>287</v>
       </c>
-      <c r="F320" t="n">
+      <c r="F320" s="1" t="n">
         <v>26127.59</v>
       </c>
-      <c r="G320" t="n">
+      <c r="G320" s="1" t="n">
         <v>90.41</v>
       </c>
       <c r="H320" t="n">
@@ -11011,10 +11014,10 @@
       <c r="E321" t="n">
         <v>275</v>
       </c>
-      <c r="F321" t="n">
+      <c r="F321" s="1" t="n">
         <v>7899.14</v>
       </c>
-      <c r="G321" t="n">
+      <c r="G321" s="1" t="n">
         <v>27.43</v>
       </c>
       <c r="H321" t="n">
@@ -11044,10 +11047,10 @@
       <c r="E322" t="n">
         <v>287</v>
       </c>
-      <c r="F322" t="n">
+      <c r="F322" s="1" t="n">
         <v>25911.09</v>
       </c>
-      <c r="G322" t="n">
+      <c r="G322" s="1" t="n">
         <v>89.97</v>
       </c>
       <c r="H322" t="n">
@@ -11077,10 +11080,10 @@
       <c r="E323" t="n">
         <v>260</v>
       </c>
-      <c r="F323" t="n">
+      <c r="F323" s="1" t="n">
         <v>8582.58</v>
       </c>
-      <c r="G323" t="n">
+      <c r="G323" s="1" t="n">
         <v>30.43</v>
       </c>
       <c r="H323" t="n">
@@ -11110,10 +11113,10 @@
       <c r="E324" t="n">
         <v>277</v>
       </c>
-      <c r="F324" t="n">
+      <c r="F324" s="1" t="n">
         <v>21007.23</v>
       </c>
-      <c r="G324" t="n">
+      <c r="G324" s="1" t="n">
         <v>75.29000000000001</v>
       </c>
       <c r="H324" t="n">
@@ -11143,10 +11146,10 @@
       <c r="E325" t="n">
         <v>261</v>
       </c>
-      <c r="F325" t="n">
+      <c r="F325" s="1" t="n">
         <v>29021.2</v>
       </c>
-      <c r="G325" t="n">
+      <c r="G325" s="1" t="n">
         <v>105.92</v>
       </c>
       <c r="H325" t="n">
@@ -11176,10 +11179,10 @@
       <c r="E326" t="n">
         <v>272</v>
       </c>
-      <c r="F326" t="n">
+      <c r="F326" s="1" t="n">
         <v>33015.01</v>
       </c>
-      <c r="G326" t="n">
+      <c r="G326" s="1" t="n">
         <v>120.49</v>
       </c>
       <c r="H326" t="n">
@@ -11209,10 +11212,10 @@
       <c r="E327" t="n">
         <v>238</v>
       </c>
-      <c r="F327" t="n">
+      <c r="F327" s="1" t="n">
         <v>4678.38</v>
       </c>
-      <c r="G327" t="n">
+      <c r="G327" s="1" t="n">
         <v>17.14</v>
       </c>
       <c r="H327" t="n">
@@ -11242,10 +11245,10 @@
       <c r="E328" t="n">
         <v>271</v>
       </c>
-      <c r="F328" t="n">
+      <c r="F328" s="1" t="n">
         <v>30781.11</v>
       </c>
-      <c r="G328" t="n">
+      <c r="G328" s="1" t="n">
         <v>113.17</v>
       </c>
       <c r="H328" t="n">
@@ -11275,10 +11278,10 @@
       <c r="E329" t="n">
         <v>249</v>
       </c>
-      <c r="F329" t="n">
+      <c r="F329" s="1" t="n">
         <v>6153.6</v>
       </c>
-      <c r="G329" t="n">
+      <c r="G329" s="1" t="n">
         <v>22.62</v>
       </c>
       <c r="H329" t="n">
@@ -11308,10 +11311,10 @@
       <c r="E330" t="n">
         <v>261</v>
       </c>
-      <c r="F330" t="n">
+      <c r="F330" s="1" t="n">
         <v>27097.29</v>
       </c>
-      <c r="G330" t="n">
+      <c r="G330" s="1" t="n">
         <v>99.98999999999999</v>
       </c>
       <c r="H330" t="n">
@@ -11341,10 +11344,10 @@
       <c r="E331" t="n">
         <v>245</v>
       </c>
-      <c r="F331" t="n">
+      <c r="F331" s="1" t="n">
         <v>6278.7</v>
       </c>
-      <c r="G331" t="n">
+      <c r="G331" s="1" t="n">
         <v>23.43</v>
       </c>
       <c r="H331" t="n">
@@ -11374,10 +11377,10 @@
       <c r="E332" t="n">
         <v>263</v>
       </c>
-      <c r="F332" t="n">
+      <c r="F332" s="1" t="n">
         <v>13175.94</v>
       </c>
-      <c r="G332" t="n">
+      <c r="G332" s="1" t="n">
         <v>49.35</v>
       </c>
       <c r="H332" t="n">
@@ -11407,10 +11410,10 @@
       <c r="E333" t="n">
         <v>262</v>
       </c>
-      <c r="F333" t="n">
+      <c r="F333" s="1" t="n">
         <v>13473.83</v>
       </c>
-      <c r="G333" t="n">
+      <c r="G333" s="1" t="n">
         <v>50.65</v>
       </c>
       <c r="H333" t="n">
@@ -11440,10 +11443,10 @@
       <c r="E334" t="n">
         <v>254</v>
       </c>
-      <c r="F334" t="n">
+      <c r="F334" s="1" t="n">
         <v>13655.26</v>
       </c>
-      <c r="G334" t="n">
+      <c r="G334" s="1" t="n">
         <v>51.72</v>
       </c>
       <c r="H334" t="n">
@@ -11473,10 +11476,10 @@
       <c r="E335" t="n">
         <v>234</v>
       </c>
-      <c r="F335" t="n">
+      <c r="F335" s="1" t="n">
         <v>4932.13</v>
       </c>
-      <c r="G335" t="n">
+      <c r="G335" s="1" t="n">
         <v>19.04</v>
       </c>
       <c r="H335" t="n">
@@ -11506,10 +11509,10 @@
       <c r="E336" t="n">
         <v>252</v>
       </c>
-      <c r="F336" t="n">
+      <c r="F336" s="1" t="n">
         <v>8807.359999999999</v>
       </c>
-      <c r="G336" t="n">
+      <c r="G336" s="1" t="n">
         <v>34.14</v>
       </c>
       <c r="H336" t="n">
@@ -11539,10 +11542,10 @@
       <c r="E337" t="n">
         <v>256</v>
       </c>
-      <c r="F337" t="n">
+      <c r="F337" s="1" t="n">
         <v>20405.58</v>
       </c>
-      <c r="G337" t="n">
+      <c r="G337" s="1" t="n">
         <v>79.70999999999999</v>
       </c>
       <c r="H337" t="n">
@@ -11572,10 +11575,10 @@
       <c r="E338" t="n">
         <v>252</v>
       </c>
-      <c r="F338" t="n">
+      <c r="F338" s="1" t="n">
         <v>20466.21</v>
       </c>
-      <c r="G338" t="n">
+      <c r="G338" s="1" t="n">
         <v>79.95</v>
       </c>
       <c r="H338" t="n">
@@ -11605,10 +11608,10 @@
       <c r="E339" t="n">
         <v>250</v>
       </c>
-      <c r="F339" t="n">
+      <c r="F339" s="1" t="n">
         <v>8797.039999999999</v>
       </c>
-      <c r="G339" t="n">
+      <c r="G339" s="1" t="n">
         <v>34.36</v>
       </c>
       <c r="H339" t="n">
@@ -11638,10 +11641,10 @@
       <c r="E340" t="n">
         <v>250</v>
       </c>
-      <c r="F340" t="n">
+      <c r="F340" s="1" t="n">
         <v>33976.60000000001</v>
       </c>
-      <c r="G340" t="n">
+      <c r="G340" s="1" t="n">
         <v>133.24</v>
       </c>
       <c r="H340" t="n">
@@ -11671,10 +11674,10 @@
       <c r="E341" t="n">
         <v>222</v>
       </c>
-      <c r="F341" t="n">
+      <c r="F341" s="1" t="n">
         <v>7501.46</v>
       </c>
-      <c r="G341" t="n">
+      <c r="G341" s="1" t="n">
         <v>29.42</v>
       </c>
       <c r="H341" t="n">
@@ -11704,10 +11707,10 @@
       <c r="E342" t="n">
         <v>254</v>
       </c>
-      <c r="F342" t="n">
+      <c r="F342" s="1" t="n">
         <v>16562.33</v>
       </c>
-      <c r="G342" t="n">
+      <c r="G342" s="1" t="n">
         <v>65.20999999999999</v>
       </c>
       <c r="H342" t="n">
@@ -11737,10 +11740,10 @@
       <c r="E343" t="n">
         <v>219</v>
       </c>
-      <c r="F343" t="n">
+      <c r="F343" s="1" t="n">
         <v>20370.18</v>
       </c>
-      <c r="G343" t="n">
+      <c r="G343" s="1" t="n">
         <v>80.51000000000001</v>
       </c>
       <c r="H343" t="n">
@@ -11770,10 +11773,10 @@
       <c r="E344" t="n">
         <v>226</v>
       </c>
-      <c r="F344" t="n">
+      <c r="F344" s="1" t="n">
         <v>5880.79</v>
       </c>
-      <c r="G344" t="n">
+      <c r="G344" s="1" t="n">
         <v>23.71</v>
       </c>
       <c r="H344" t="n">
@@ -11803,10 +11806,10 @@
       <c r="E345" t="n">
         <v>241</v>
       </c>
-      <c r="F345" t="n">
+      <c r="F345" s="1" t="n">
         <v>4006.79</v>
       </c>
-      <c r="G345" t="n">
+      <c r="G345" s="1" t="n">
         <v>16.35</v>
       </c>
       <c r="H345" t="n">
@@ -11836,10 +11839,10 @@
       <c r="E346" t="n">
         <v>237</v>
       </c>
-      <c r="F346" t="n">
+      <c r="F346" s="1" t="n">
         <v>12662.24</v>
       </c>
-      <c r="G346" t="n">
+      <c r="G346" s="1" t="n">
         <v>51.68</v>
       </c>
       <c r="H346" t="n">
@@ -11869,10 +11872,10 @@
       <c r="E347" t="n">
         <v>237</v>
       </c>
-      <c r="F347" t="n">
+      <c r="F347" s="1" t="n">
         <v>3430.13</v>
       </c>
-      <c r="G347" t="n">
+      <c r="G347" s="1" t="n">
         <v>14</v>
       </c>
       <c r="H347" t="n">
@@ -11902,10 +11905,10 @@
       <c r="E348" t="n">
         <v>227</v>
       </c>
-      <c r="F348" t="n">
+      <c r="F348" s="1" t="n">
         <v>13564.41</v>
       </c>
-      <c r="G348" t="n">
+      <c r="G348" s="1" t="n">
         <v>56.05</v>
       </c>
       <c r="H348" t="n">
@@ -11935,10 +11938,10 @@
       <c r="E349" t="n">
         <v>234</v>
       </c>
-      <c r="F349" t="n">
+      <c r="F349" s="1" t="n">
         <v>33620.05</v>
       </c>
-      <c r="G349" t="n">
+      <c r="G349" s="1" t="n">
         <v>140.67</v>
       </c>
       <c r="H349" t="n">
@@ -11968,10 +11971,10 @@
       <c r="E350" t="n">
         <v>237</v>
       </c>
-      <c r="F350" t="n">
+      <c r="F350" s="1" t="n">
         <v>14443.32</v>
       </c>
-      <c r="G350" t="n">
+      <c r="G350" s="1" t="n">
         <v>60.43</v>
       </c>
       <c r="H350" t="n">
@@ -12001,10 +12004,10 @@
       <c r="E351" t="n">
         <v>235</v>
       </c>
-      <c r="F351" t="n">
+      <c r="F351" s="1" t="n">
         <v>22090.11</v>
       </c>
-      <c r="G351" t="n">
+      <c r="G351" s="1" t="n">
         <v>93.59999999999999</v>
       </c>
       <c r="H351" t="n">
@@ -12034,10 +12037,10 @@
       <c r="E352" t="n">
         <v>234</v>
       </c>
-      <c r="F352" t="n">
+      <c r="F352" s="1" t="n">
         <v>16938.85</v>
       </c>
-      <c r="G352" t="n">
+      <c r="G352" s="1" t="n">
         <v>72.08</v>
       </c>
       <c r="H352" t="n">
@@ -12067,10 +12070,10 @@
       <c r="E353" t="n">
         <v>233</v>
       </c>
-      <c r="F353" t="n">
+      <c r="F353" s="1" t="n">
         <v>22816.33</v>
       </c>
-      <c r="G353" t="n">
+      <c r="G353" s="1" t="n">
         <v>97.51000000000001</v>
       </c>
       <c r="H353" t="n">
@@ -12100,10 +12103,10 @@
       <c r="E354" t="n">
         <v>228</v>
       </c>
-      <c r="F354" t="n">
+      <c r="F354" s="1" t="n">
         <v>9279.880000000001</v>
       </c>
-      <c r="G354" t="n">
+      <c r="G354" s="1" t="n">
         <v>39.83</v>
       </c>
       <c r="H354" t="n">
@@ -12133,10 +12136,10 @@
       <c r="E355" t="n">
         <v>216</v>
       </c>
-      <c r="F355" t="n">
+      <c r="F355" s="1" t="n">
         <v>10824.16</v>
       </c>
-      <c r="G355" t="n">
+      <c r="G355" s="1" t="n">
         <v>46.66</v>
       </c>
       <c r="H355" t="n">
@@ -12166,10 +12169,10 @@
       <c r="E356" t="n">
         <v>205</v>
       </c>
-      <c r="F356" t="n">
+      <c r="F356" s="1" t="n">
         <v>8103.37</v>
       </c>
-      <c r="G356" t="n">
+      <c r="G356" s="1" t="n">
         <v>35.08</v>
       </c>
       <c r="H356" t="n">
@@ -12199,10 +12202,10 @@
       <c r="E357" t="n">
         <v>230</v>
       </c>
-      <c r="F357" t="n">
+      <c r="F357" s="1" t="n">
         <v>18285.88</v>
       </c>
-      <c r="G357" t="n">
+      <c r="G357" s="1" t="n">
         <v>79.5</v>
       </c>
       <c r="H357" t="n">
@@ -12232,10 +12235,10 @@
       <c r="E358" t="n">
         <v>226</v>
       </c>
-      <c r="F358" t="n">
+      <c r="F358" s="1" t="n">
         <v>16886.03</v>
       </c>
-      <c r="G358" t="n">
+      <c r="G358" s="1" t="n">
         <v>73.73999999999999</v>
       </c>
       <c r="H358" t="n">
@@ -12265,10 +12268,10 @@
       <c r="E359" t="n">
         <v>215</v>
       </c>
-      <c r="F359" t="n">
+      <c r="F359" s="1" t="n">
         <v>8007.27</v>
       </c>
-      <c r="G359" t="n">
+      <c r="G359" s="1" t="n">
         <v>35.59</v>
       </c>
       <c r="H359" t="n">
@@ -12298,10 +12301,10 @@
       <c r="E360" t="n">
         <v>221</v>
       </c>
-      <c r="F360" t="n">
+      <c r="F360" s="1" t="n">
         <v>31320.84</v>
       </c>
-      <c r="G360" t="n">
+      <c r="G360" s="1" t="n">
         <v>140.45</v>
       </c>
       <c r="H360" t="n">
@@ -12331,10 +12334,10 @@
       <c r="E361" t="n">
         <v>216</v>
       </c>
-      <c r="F361" t="n">
+      <c r="F361" s="1" t="n">
         <v>20991.33</v>
       </c>
-      <c r="G361" t="n">
+      <c r="G361" s="1" t="n">
         <v>94.13</v>
       </c>
       <c r="H361" t="n">
@@ -12364,10 +12367,10 @@
       <c r="E362" t="n">
         <v>212</v>
       </c>
-      <c r="F362" t="n">
+      <c r="F362" s="1" t="n">
         <v>19412.89</v>
       </c>
-      <c r="G362" t="n">
+      <c r="G362" s="1" t="n">
         <v>91.14</v>
       </c>
       <c r="H362" t="n">
@@ -12397,10 +12400,10 @@
       <c r="E363" t="n">
         <v>210</v>
       </c>
-      <c r="F363" t="n">
+      <c r="F363" s="1" t="n">
         <v>10201.91</v>
       </c>
-      <c r="G363" t="n">
+      <c r="G363" s="1" t="n">
         <v>48.12</v>
       </c>
       <c r="H363" t="n">
@@ -12430,10 +12433,10 @@
       <c r="E364" t="n">
         <v>207</v>
       </c>
-      <c r="F364" t="n">
+      <c r="F364" s="1" t="n">
         <v>4111.26</v>
       </c>
-      <c r="G364" t="n">
+      <c r="G364" s="1" t="n">
         <v>19.48</v>
       </c>
       <c r="H364" t="n">
@@ -12463,10 +12466,10 @@
       <c r="E365" t="n">
         <v>205</v>
       </c>
-      <c r="F365" t="n">
+      <c r="F365" s="1" t="n">
         <v>12436.93</v>
       </c>
-      <c r="G365" t="n">
+      <c r="G365" s="1" t="n">
         <v>60.08</v>
       </c>
       <c r="H365" t="n">
@@ -12496,10 +12499,10 @@
       <c r="E366" t="n">
         <v>202</v>
       </c>
-      <c r="F366" t="n">
+      <c r="F366" s="1" t="n">
         <v>12072.95</v>
       </c>
-      <c r="G366" t="n">
+      <c r="G366" s="1" t="n">
         <v>58.61</v>
       </c>
       <c r="H366" t="n">
@@ -12529,10 +12532,10 @@
       <c r="E367" t="n">
         <v>199</v>
       </c>
-      <c r="F367" t="n">
+      <c r="F367" s="1" t="n">
         <v>9707.77</v>
       </c>
-      <c r="G367" t="n">
+      <c r="G367" s="1" t="n">
         <v>47.59</v>
       </c>
       <c r="H367" t="n">
@@ -12562,10 +12565,10 @@
       <c r="E368" t="n">
         <v>163</v>
       </c>
-      <c r="F368" t="n">
+      <c r="F368" s="1" t="n">
         <v>5645.15</v>
       </c>
-      <c r="G368" t="n">
+      <c r="G368" s="1" t="n">
         <v>27.95</v>
       </c>
       <c r="H368" t="n">
@@ -12595,10 +12598,10 @@
       <c r="E369" t="n">
         <v>175</v>
       </c>
-      <c r="F369" t="n">
+      <c r="F369" s="1" t="n">
         <v>5829.27</v>
       </c>
-      <c r="G369" t="n">
+      <c r="G369" s="1" t="n">
         <v>29.15</v>
       </c>
       <c r="H369" t="n">
@@ -12628,10 +12631,10 @@
       <c r="E370" t="n">
         <v>199</v>
       </c>
-      <c r="F370" t="n">
+      <c r="F370" s="1" t="n">
         <v>17623.64</v>
       </c>
-      <c r="G370" t="n">
+      <c r="G370" s="1" t="n">
         <v>88.56</v>
       </c>
       <c r="H370" t="n">
@@ -12661,10 +12664,10 @@
       <c r="E371" t="n">
         <v>198</v>
       </c>
-      <c r="F371" t="n">
+      <c r="F371" s="1" t="n">
         <v>29827.04</v>
       </c>
-      <c r="G371" t="n">
+      <c r="G371" s="1" t="n">
         <v>150.64</v>
       </c>
       <c r="H371" t="n">
@@ -12694,10 +12697,10 @@
       <c r="E372" t="n">
         <v>192</v>
       </c>
-      <c r="F372" t="n">
+      <c r="F372" s="1" t="n">
         <v>15473.5</v>
       </c>
-      <c r="G372" t="n">
+      <c r="G372" s="1" t="n">
         <v>78.15000000000001</v>
       </c>
       <c r="H372" t="n">
@@ -12727,10 +12730,10 @@
       <c r="E373" t="n">
         <v>194</v>
       </c>
-      <c r="F373" t="n">
+      <c r="F373" s="1" t="n">
         <v>12089.52</v>
       </c>
-      <c r="G373" t="n">
+      <c r="G373" s="1" t="n">
         <v>61.37</v>
       </c>
       <c r="H373" t="n">
@@ -12760,10 +12763,10 @@
       <c r="E374" t="n">
         <v>197</v>
       </c>
-      <c r="F374" t="n">
+      <c r="F374" s="1" t="n">
         <v>21058.73</v>
       </c>
-      <c r="G374" t="n">
+      <c r="G374" s="1" t="n">
         <v>106.9</v>
       </c>
       <c r="H374" t="n">
@@ -12793,10 +12796,10 @@
       <c r="E375" t="n">
         <v>195</v>
       </c>
-      <c r="F375" t="n">
+      <c r="F375" s="1" t="n">
         <v>18742.6</v>
       </c>
-      <c r="G375" t="n">
+      <c r="G375" s="1" t="n">
         <v>95.14</v>
       </c>
       <c r="H375" t="n">
@@ -12826,10 +12829,10 @@
       <c r="E376" t="n">
         <v>194</v>
       </c>
-      <c r="F376" t="n">
+      <c r="F376" s="1" t="n">
         <v>12399.75</v>
       </c>
-      <c r="G376" t="n">
+      <c r="G376" s="1" t="n">
         <v>63.59</v>
       </c>
       <c r="H376" t="n">
@@ -12859,10 +12862,10 @@
       <c r="E377" t="n">
         <v>194</v>
       </c>
-      <c r="F377" t="n">
+      <c r="F377" s="1" t="n">
         <v>22355.6</v>
       </c>
-      <c r="G377" t="n">
+      <c r="G377" s="1" t="n">
         <v>115.24</v>
       </c>
       <c r="H377" t="n">
@@ -12892,10 +12895,10 @@
       <c r="E378" t="n">
         <v>168</v>
       </c>
-      <c r="F378" t="n">
+      <c r="F378" s="1" t="n">
         <v>3494.55</v>
       </c>
-      <c r="G378" t="n">
+      <c r="G378" s="1" t="n">
         <v>18.01</v>
       </c>
       <c r="H378" t="n">
@@ -12925,10 +12928,10 @@
       <c r="E379" t="n">
         <v>182</v>
       </c>
-      <c r="F379" t="n">
+      <c r="F379" s="1" t="n">
         <v>7549.28</v>
       </c>
-      <c r="G379" t="n">
+      <c r="G379" s="1" t="n">
         <v>39.12</v>
       </c>
       <c r="H379" t="n">
@@ -12958,10 +12961,10 @@
       <c r="E380" t="n">
         <v>190</v>
       </c>
-      <c r="F380" t="n">
+      <c r="F380" s="1" t="n">
         <v>9622.370000000001</v>
       </c>
-      <c r="G380" t="n">
+      <c r="G380" s="1" t="n">
         <v>49.86</v>
       </c>
       <c r="H380" t="n">
@@ -12991,10 +12994,10 @@
       <c r="E381" t="n">
         <v>192</v>
       </c>
-      <c r="F381" t="n">
+      <c r="F381" s="1" t="n">
         <v>17109.66</v>
       </c>
-      <c r="G381" t="n">
+      <c r="G381" s="1" t="n">
         <v>89.11</v>
       </c>
       <c r="H381" t="n">
@@ -13024,10 +13027,10 @@
       <c r="E382" t="n">
         <v>188</v>
       </c>
-      <c r="F382" t="n">
+      <c r="F382" s="1" t="n">
         <v>10447.75</v>
       </c>
-      <c r="G382" t="n">
+      <c r="G382" s="1" t="n">
         <v>54.7</v>
       </c>
       <c r="H382" t="n">
@@ -13057,10 +13060,10 @@
       <c r="E383" t="n">
         <v>184</v>
       </c>
-      <c r="F383" t="n">
+      <c r="F383" s="1" t="n">
         <v>12666.62</v>
       </c>
-      <c r="G383" t="n">
+      <c r="G383" s="1" t="n">
         <v>67.38</v>
       </c>
       <c r="H383" t="n">
@@ -13090,10 +13093,10 @@
       <c r="E384" t="n">
         <v>188</v>
       </c>
-      <c r="F384" t="n">
+      <c r="F384" s="1" t="n">
         <v>18579.63</v>
       </c>
-      <c r="G384" t="n">
+      <c r="G384" s="1" t="n">
         <v>98.83</v>
       </c>
       <c r="H384" t="n">
@@ -13123,10 +13126,10 @@
       <c r="E385" t="n">
         <v>185</v>
       </c>
-      <c r="F385" t="n">
+      <c r="F385" s="1" t="n">
         <v>16982.32</v>
       </c>
-      <c r="G385" t="n">
+      <c r="G385" s="1" t="n">
         <v>90.33</v>
       </c>
       <c r="H385" t="n">
@@ -13156,10 +13159,10 @@
       <c r="E386" t="n">
         <v>183</v>
       </c>
-      <c r="F386" t="n">
+      <c r="F386" s="1" t="n">
         <v>13484.19</v>
       </c>
-      <c r="G386" t="n">
+      <c r="G386" s="1" t="n">
         <v>72.89</v>
       </c>
       <c r="H386" t="n">
@@ -13189,10 +13192,10 @@
       <c r="E387" t="n">
         <v>176</v>
       </c>
-      <c r="F387" t="n">
+      <c r="F387" s="1" t="n">
         <v>23512.28</v>
       </c>
-      <c r="G387" t="n">
+      <c r="G387" s="1" t="n">
         <v>130.62</v>
       </c>
       <c r="H387" t="n">
@@ -13222,10 +13225,10 @@
       <c r="E388" t="n">
         <v>154</v>
       </c>
-      <c r="F388" t="n">
+      <c r="F388" s="1" t="n">
         <v>5205.44</v>
       </c>
-      <c r="G388" t="n">
+      <c r="G388" s="1" t="n">
         <v>29.08</v>
       </c>
       <c r="H388" t="n">
@@ -13255,10 +13258,10 @@
       <c r="E389" t="n">
         <v>167</v>
       </c>
-      <c r="F389" t="n">
+      <c r="F389" s="1" t="n">
         <v>14780.46</v>
       </c>
-      <c r="G389" t="n">
+      <c r="G389" s="1" t="n">
         <v>82.56999999999999</v>
       </c>
       <c r="H389" t="n">
@@ -13288,10 +13291,10 @@
       <c r="E390" t="n">
         <v>166</v>
       </c>
-      <c r="F390" t="n">
+      <c r="F390" s="1" t="n">
         <v>8030.15</v>
       </c>
-      <c r="G390" t="n">
+      <c r="G390" s="1" t="n">
         <v>44.86</v>
       </c>
       <c r="H390" t="n">
@@ -13321,10 +13324,10 @@
       <c r="E391" t="n">
         <v>154</v>
       </c>
-      <c r="F391" t="n">
+      <c r="F391" s="1" t="n">
         <v>2894.35</v>
       </c>
-      <c r="G391" t="n">
+      <c r="G391" s="1" t="n">
         <v>16.45</v>
       </c>
       <c r="H391" t="n">
@@ -13354,10 +13357,10 @@
       <c r="E392" t="n">
         <v>146</v>
       </c>
-      <c r="F392" t="n">
+      <c r="F392" s="1" t="n">
         <v>1535.36</v>
       </c>
-      <c r="G392" t="n">
+      <c r="G392" s="1" t="n">
         <v>8.93</v>
       </c>
       <c r="H392" t="n">
@@ -13387,10 +13390,10 @@
       <c r="E393" t="n">
         <v>169</v>
       </c>
-      <c r="F393" t="n">
+      <c r="F393" s="1" t="n">
         <v>9042.949999999999</v>
       </c>
-      <c r="G393" t="n">
+      <c r="G393" s="1" t="n">
         <v>52.88</v>
       </c>
       <c r="H393" t="n">
@@ -13420,10 +13423,10 @@
       <c r="E394" t="n">
         <v>148</v>
       </c>
-      <c r="F394" t="n">
+      <c r="F394" s="1" t="n">
         <v>4811.48</v>
       </c>
-      <c r="G394" t="n">
+      <c r="G394" s="1" t="n">
         <v>28.64</v>
       </c>
       <c r="H394" t="n">
@@ -13453,10 +13456,10 @@
       <c r="E395" t="n">
         <v>156</v>
       </c>
-      <c r="F395" t="n">
+      <c r="F395" s="1" t="n">
         <v>7964.35</v>
       </c>
-      <c r="G395" t="n">
+      <c r="G395" s="1" t="n">
         <v>47.69</v>
       </c>
       <c r="H395" t="n">
@@ -13486,10 +13489,10 @@
       <c r="E396" t="n">
         <v>164</v>
       </c>
-      <c r="F396" t="n">
+      <c r="F396" s="1" t="n">
         <v>9819.889999999999</v>
       </c>
-      <c r="G396" t="n">
+      <c r="G396" s="1" t="n">
         <v>59.88</v>
       </c>
       <c r="H396" t="n">
@@ -13519,10 +13522,10 @@
       <c r="E397" t="n">
         <v>163</v>
       </c>
-      <c r="F397" t="n">
+      <c r="F397" s="1" t="n">
         <v>12481.87</v>
       </c>
-      <c r="G397" t="n">
+      <c r="G397" s="1" t="n">
         <v>76.58</v>
       </c>
       <c r="H397" t="n">
@@ -13552,10 +13555,10 @@
       <c r="E398" t="n">
         <v>160</v>
       </c>
-      <c r="F398" t="n">
+      <c r="F398" s="1" t="n">
         <v>12270.37</v>
       </c>
-      <c r="G398" t="n">
+      <c r="G398" s="1" t="n">
         <v>75.28</v>
       </c>
       <c r="H398" t="n">
@@ -13585,10 +13588,10 @@
       <c r="E399" t="n">
         <v>160</v>
       </c>
-      <c r="F399" t="n">
+      <c r="F399" s="1" t="n">
         <v>19223.82</v>
       </c>
-      <c r="G399" t="n">
+      <c r="G399" s="1" t="n">
         <v>119.4</v>
       </c>
       <c r="H399" t="n">
@@ -13618,10 +13621,10 @@
       <c r="E400" t="n">
         <v>159</v>
       </c>
-      <c r="F400" t="n">
+      <c r="F400" s="1" t="n">
         <v>9188.85</v>
       </c>
-      <c r="G400" t="n">
+      <c r="G400" s="1" t="n">
         <v>57.43</v>
       </c>
       <c r="H400" t="n">
@@ -13651,10 +13654,10 @@
       <c r="E401" t="n">
         <v>157</v>
       </c>
-      <c r="F401" t="n">
+      <c r="F401" s="1" t="n">
         <v>10481.42</v>
       </c>
-      <c r="G401" t="n">
+      <c r="G401" s="1" t="n">
         <v>65.92</v>
       </c>
       <c r="H401" t="n">
@@ -13684,10 +13687,10 @@
       <c r="E402" t="n">
         <v>159</v>
       </c>
-      <c r="F402" t="n">
+      <c r="F402" s="1" t="n">
         <v>16280.64</v>
       </c>
-      <c r="G402" t="n">
+      <c r="G402" s="1" t="n">
         <v>102.39</v>
       </c>
       <c r="H402" t="n">
@@ -13717,10 +13720,10 @@
       <c r="E403" t="n">
         <v>153</v>
       </c>
-      <c r="F403" t="n">
+      <c r="F403" s="1" t="n">
         <v>9355.84</v>
       </c>
-      <c r="G403" t="n">
+      <c r="G403" s="1" t="n">
         <v>59.21</v>
       </c>
       <c r="H403" t="n">
@@ -13750,10 +13753,10 @@
       <c r="E404" t="n">
         <v>120</v>
       </c>
-      <c r="F404" t="n">
+      <c r="F404" s="1" t="n">
         <v>3254.37</v>
       </c>
-      <c r="G404" t="n">
+      <c r="G404" s="1" t="n">
         <v>20.73</v>
       </c>
       <c r="H404" t="n">
@@ -13783,10 +13786,10 @@
       <c r="E405" t="n">
         <v>156</v>
       </c>
-      <c r="F405" t="n">
+      <c r="F405" s="1" t="n">
         <v>6725.55</v>
       </c>
-      <c r="G405" t="n">
+      <c r="G405" s="1" t="n">
         <v>43.11</v>
       </c>
       <c r="H405" t="n">
@@ -13816,10 +13819,10 @@
       <c r="E406" t="n">
         <v>142</v>
       </c>
-      <c r="F406" t="n">
+      <c r="F406" s="1" t="n">
         <v>2876.32</v>
       </c>
-      <c r="G406" t="n">
+      <c r="G406" s="1" t="n">
         <v>18.92</v>
       </c>
       <c r="H406" t="n">
@@ -13849,10 +13852,10 @@
       <c r="E407" t="n">
         <v>151</v>
       </c>
-      <c r="F407" t="n">
+      <c r="F407" s="1" t="n">
         <v>11939.05</v>
       </c>
-      <c r="G407" t="n">
+      <c r="G407" s="1" t="n">
         <v>79.06999999999999</v>
       </c>
       <c r="H407" t="n">
@@ -13882,10 +13885,10 @@
       <c r="E408" t="n">
         <v>146</v>
       </c>
-      <c r="F408" t="n">
+      <c r="F408" s="1" t="n">
         <v>11383.07</v>
       </c>
-      <c r="G408" t="n">
+      <c r="G408" s="1" t="n">
         <v>75.89</v>
       </c>
       <c r="H408" t="n">
@@ -13915,10 +13918,10 @@
       <c r="E409" t="n">
         <v>127</v>
       </c>
-      <c r="F409" t="n">
+      <c r="F409" s="1" t="n">
         <v>12876.26</v>
       </c>
-      <c r="G409" t="n">
+      <c r="G409" s="1" t="n">
         <v>86.42</v>
       </c>
       <c r="H409" t="n">
@@ -13948,10 +13951,10 @@
       <c r="E410" t="n">
         <v>147</v>
       </c>
-      <c r="F410" t="n">
+      <c r="F410" s="1" t="n">
         <v>18848.55</v>
       </c>
-      <c r="G410" t="n">
+      <c r="G410" s="1" t="n">
         <v>126.5</v>
       </c>
       <c r="H410" t="n">
@@ -13981,10 +13984,10 @@
       <c r="E411" t="n">
         <v>141</v>
       </c>
-      <c r="F411" t="n">
+      <c r="F411" s="1" t="n">
         <v>2449.97</v>
       </c>
-      <c r="G411" t="n">
+      <c r="G411" s="1" t="n">
         <v>16.44</v>
       </c>
       <c r="H411" t="n">
@@ -14014,10 +14017,10 @@
       <c r="E412" t="n">
         <v>146</v>
       </c>
-      <c r="F412" t="n">
+      <c r="F412" s="1" t="n">
         <v>13432.41</v>
       </c>
-      <c r="G412" t="n">
+      <c r="G412" s="1" t="n">
         <v>90.15000000000001</v>
       </c>
       <c r="H412" t="n">
@@ -14047,10 +14050,10 @@
       <c r="E413" t="n">
         <v>149</v>
       </c>
-      <c r="F413" t="n">
+      <c r="F413" s="1" t="n">
         <v>6863.41</v>
       </c>
-      <c r="G413" t="n">
+      <c r="G413" s="1" t="n">
         <v>46.06</v>
       </c>
       <c r="H413" t="n">
@@ -14080,10 +14083,10 @@
       <c r="E414" t="n">
         <v>148</v>
       </c>
-      <c r="F414" t="n">
+      <c r="F414" s="1" t="n">
         <v>14290.91</v>
       </c>
-      <c r="G414" t="n">
+      <c r="G414" s="1" t="n">
         <v>96.56</v>
       </c>
       <c r="H414" t="n">
@@ -14113,10 +14116,10 @@
       <c r="E415" t="n">
         <v>136</v>
       </c>
-      <c r="F415" t="n">
+      <c r="F415" s="1" t="n">
         <v>2969.74</v>
       </c>
-      <c r="G415" t="n">
+      <c r="G415" s="1" t="n">
         <v>20.34</v>
       </c>
       <c r="H415" t="n">
@@ -14146,10 +14149,10 @@
       <c r="E416" t="n">
         <v>146</v>
       </c>
-      <c r="F416" t="n">
+      <c r="F416" s="1" t="n">
         <v>14557.16</v>
       </c>
-      <c r="G416" t="n">
+      <c r="G416" s="1" t="n">
         <v>99.70999999999999</v>
       </c>
       <c r="H416" t="n">
@@ -14179,10 +14182,10 @@
       <c r="E417" t="n">
         <v>145</v>
       </c>
-      <c r="F417" t="n">
+      <c r="F417" s="1" t="n">
         <v>9958.049999999999</v>
       </c>
-      <c r="G417" t="n">
+      <c r="G417" s="1" t="n">
         <v>68.68000000000001</v>
       </c>
       <c r="H417" t="n">
@@ -14212,10 +14215,10 @@
       <c r="E418" t="n">
         <v>143</v>
       </c>
-      <c r="F418" t="n">
+      <c r="F418" s="1" t="n">
         <v>12946.43</v>
       </c>
-      <c r="G418" t="n">
+      <c r="G418" s="1" t="n">
         <v>90.53</v>
       </c>
       <c r="H418" t="n">
@@ -14245,10 +14248,10 @@
       <c r="E419" t="n">
         <v>139</v>
       </c>
-      <c r="F419" t="n">
+      <c r="F419" s="1" t="n">
         <v>7319.26</v>
       </c>
-      <c r="G419" t="n">
+      <c r="G419" s="1" t="n">
         <v>51.54</v>
       </c>
       <c r="H419" t="n">
@@ -14278,10 +14281,10 @@
       <c r="E420" t="n">
         <v>137</v>
       </c>
-      <c r="F420" t="n">
+      <c r="F420" s="1" t="n">
         <v>2943.96</v>
       </c>
-      <c r="G420" t="n">
+      <c r="G420" s="1" t="n">
         <v>21.03</v>
       </c>
       <c r="H420" t="n">
@@ -14311,10 +14314,10 @@
       <c r="E421" t="n">
         <v>122</v>
       </c>
-      <c r="F421" t="n">
+      <c r="F421" s="1" t="n">
         <v>2682.61</v>
       </c>
-      <c r="G421" t="n">
+      <c r="G421" s="1" t="n">
         <v>19.16</v>
       </c>
       <c r="H421" t="n">
@@ -14344,10 +14347,10 @@
       <c r="E422" t="n">
         <v>120</v>
       </c>
-      <c r="F422" t="n">
+      <c r="F422" s="1" t="n">
         <v>8441.630000000001</v>
       </c>
-      <c r="G422" t="n">
+      <c r="G422" s="1" t="n">
         <v>61.17</v>
       </c>
       <c r="H422" t="n">
@@ -14377,10 +14380,10 @@
       <c r="E423" t="n">
         <v>138</v>
       </c>
-      <c r="F423" t="n">
+      <c r="F423" s="1" t="n">
         <v>5078.17</v>
       </c>
-      <c r="G423" t="n">
+      <c r="G423" s="1" t="n">
         <v>36.8</v>
       </c>
       <c r="H423" t="n">
@@ -14410,10 +14413,10 @@
       <c r="E424" t="n">
         <v>136</v>
       </c>
-      <c r="F424" t="n">
+      <c r="F424" s="1" t="n">
         <v>6840.639999999999</v>
       </c>
-      <c r="G424" t="n">
+      <c r="G424" s="1" t="n">
         <v>50.3</v>
       </c>
       <c r="H424" t="n">
@@ -14443,10 +14446,10 @@
       <c r="E425" t="n">
         <v>116</v>
       </c>
-      <c r="F425" t="n">
+      <c r="F425" s="1" t="n">
         <v>3466.7</v>
       </c>
-      <c r="G425" t="n">
+      <c r="G425" s="1" t="n">
         <v>25.49</v>
       </c>
       <c r="H425" t="n">
@@ -14476,10 +14479,10 @@
       <c r="E426" t="n">
         <v>135</v>
       </c>
-      <c r="F426" t="n">
+      <c r="F426" s="1" t="n">
         <v>14236.77</v>
       </c>
-      <c r="G426" t="n">
+      <c r="G426" s="1" t="n">
         <v>105.46</v>
       </c>
       <c r="H426" t="n">
@@ -14509,10 +14512,10 @@
       <c r="E427" t="n">
         <v>131</v>
       </c>
-      <c r="F427" t="n">
+      <c r="F427" s="1" t="n">
         <v>2725.84</v>
       </c>
-      <c r="G427" t="n">
+      <c r="G427" s="1" t="n">
         <v>20.81</v>
       </c>
       <c r="H427" t="n">
@@ -14542,10 +14545,10 @@
       <c r="E428" t="n">
         <v>130</v>
       </c>
-      <c r="F428" t="n">
+      <c r="F428" s="1" t="n">
         <v>7304.95</v>
       </c>
-      <c r="G428" t="n">
+      <c r="G428" s="1" t="n">
         <v>55.76</v>
       </c>
       <c r="H428" t="n">
@@ -14575,10 +14578,10 @@
       <c r="E429" t="n">
         <v>127</v>
       </c>
-      <c r="F429" t="n">
+      <c r="F429" s="1" t="n">
         <v>9126.9</v>
       </c>
-      <c r="G429" t="n">
+      <c r="G429" s="1" t="n">
         <v>70.20999999999999</v>
       </c>
       <c r="H429" t="n">
@@ -14608,10 +14611,10 @@
       <c r="E430" t="n">
         <v>113</v>
       </c>
-      <c r="F430" t="n">
+      <c r="F430" s="1" t="n">
         <v>8655.75</v>
       </c>
-      <c r="G430" t="n">
+      <c r="G430" s="1" t="n">
         <v>67.62</v>
       </c>
       <c r="H430" t="n">
@@ -14641,10 +14644,10 @@
       <c r="E431" t="n">
         <v>128</v>
       </c>
-      <c r="F431" t="n">
+      <c r="F431" s="1" t="n">
         <v>122778.72</v>
       </c>
-      <c r="G431" t="n">
+      <c r="G431" s="1" t="n">
         <v>959.21</v>
       </c>
       <c r="H431" t="n">
@@ -14674,10 +14677,10 @@
       <c r="E432" t="n">
         <v>124</v>
       </c>
-      <c r="F432" t="n">
+      <c r="F432" s="1" t="n">
         <v>10456.42</v>
       </c>
-      <c r="G432" t="n">
+      <c r="G432" s="1" t="n">
         <v>82.98999999999999</v>
       </c>
       <c r="H432" t="n">
@@ -14707,10 +14710,10 @@
       <c r="E433" t="n">
         <v>126</v>
       </c>
-      <c r="F433" t="n">
+      <c r="F433" s="1" t="n">
         <v>9134.75</v>
       </c>
-      <c r="G433" t="n">
+      <c r="G433" s="1" t="n">
         <v>72.5</v>
       </c>
       <c r="H433" t="n">
@@ -14740,10 +14743,10 @@
       <c r="E434" t="n">
         <v>112</v>
       </c>
-      <c r="F434" t="n">
+      <c r="F434" s="1" t="n">
         <v>2596.98</v>
       </c>
-      <c r="G434" t="n">
+      <c r="G434" s="1" t="n">
         <v>20.61</v>
       </c>
       <c r="H434" t="n">
@@ -14773,10 +14776,10 @@
       <c r="E435" t="n">
         <v>122</v>
       </c>
-      <c r="F435" t="n">
+      <c r="F435" s="1" t="n">
         <v>16339.46</v>
       </c>
-      <c r="G435" t="n">
+      <c r="G435" s="1" t="n">
         <v>133.93</v>
       </c>
       <c r="H435" t="n">
@@ -14806,10 +14809,10 @@
       <c r="E436" t="n">
         <v>116</v>
       </c>
-      <c r="F436" t="n">
+      <c r="F436" s="1" t="n">
         <v>7085.12</v>
       </c>
-      <c r="G436" t="n">
+      <c r="G436" s="1" t="n">
         <v>59.54</v>
       </c>
       <c r="H436" t="n">
@@ -14839,10 +14842,10 @@
       <c r="E437" t="n">
         <v>116</v>
       </c>
-      <c r="F437" t="n">
+      <c r="F437" s="1" t="n">
         <v>10297.03</v>
       </c>
-      <c r="G437" t="n">
+      <c r="G437" s="1" t="n">
         <v>87.26000000000001</v>
       </c>
       <c r="H437" t="n">
@@ -14872,10 +14875,10 @@
       <c r="E438" t="n">
         <v>105</v>
       </c>
-      <c r="F438" t="n">
+      <c r="F438" s="1" t="n">
         <v>1738.09</v>
       </c>
-      <c r="G438" t="n">
+      <c r="G438" s="1" t="n">
         <v>14.86</v>
       </c>
       <c r="H438" t="n">
@@ -14905,10 +14908,10 @@
       <c r="E439" t="n">
         <v>114</v>
       </c>
-      <c r="F439" t="n">
+      <c r="F439" s="1" t="n">
         <v>15732.12</v>
       </c>
-      <c r="G439" t="n">
+      <c r="G439" s="1" t="n">
         <v>136.8</v>
       </c>
       <c r="H439" t="n">
@@ -14938,10 +14941,10 @@
       <c r="E440" t="n">
         <v>114</v>
       </c>
-      <c r="F440" t="n">
+      <c r="F440" s="1" t="n">
         <v>8708.85</v>
       </c>
-      <c r="G440" t="n">
+      <c r="G440" s="1" t="n">
         <v>75.73</v>
       </c>
       <c r="H440" t="n">
@@ -14971,10 +14974,10 @@
       <c r="E441" t="n">
         <v>112</v>
       </c>
-      <c r="F441" t="n">
+      <c r="F441" s="1" t="n">
         <v>2565.12</v>
       </c>
-      <c r="G441" t="n">
+      <c r="G441" s="1" t="n">
         <v>22.5</v>
       </c>
       <c r="H441" t="n">
@@ -15004,10 +15007,10 @@
       <c r="E442" t="n">
         <v>99</v>
       </c>
-      <c r="F442" t="n">
+      <c r="F442" s="1" t="n">
         <v>5075.82</v>
       </c>
-      <c r="G442" t="n">
+      <c r="G442" s="1" t="n">
         <v>45.32</v>
       </c>
       <c r="H442" t="n">
@@ -15037,10 +15040,10 @@
       <c r="E443" t="n">
         <v>106</v>
       </c>
-      <c r="F443" t="n">
+      <c r="F443" s="1" t="n">
         <v>3208.61</v>
       </c>
-      <c r="G443" t="n">
+      <c r="G443" s="1" t="n">
         <v>29.71</v>
       </c>
       <c r="H443" t="n">
@@ -15070,10 +15073,10 @@
       <c r="E444" t="n">
         <v>108</v>
       </c>
-      <c r="F444" t="n">
+      <c r="F444" s="1" t="n">
         <v>12588.93</v>
       </c>
-      <c r="G444" t="n">
+      <c r="G444" s="1" t="n">
         <v>116.56</v>
       </c>
       <c r="H444" t="n">
@@ -15103,10 +15106,10 @@
       <c r="E445" t="n">
         <v>105</v>
       </c>
-      <c r="F445" t="n">
+      <c r="F445" s="1" t="n">
         <v>9156.940000000001</v>
       </c>
-      <c r="G445" t="n">
+      <c r="G445" s="1" t="n">
         <v>85.58</v>
       </c>
       <c r="H445" t="n">
@@ -15136,10 +15139,10 @@
       <c r="E446" t="n">
         <v>106</v>
       </c>
-      <c r="F446" t="n">
+      <c r="F446" s="1" t="n">
         <v>6252.67</v>
       </c>
-      <c r="G446" t="n">
+      <c r="G446" s="1" t="n">
         <v>58.99</v>
       </c>
       <c r="H446" t="n">
@@ -15169,10 +15172,10 @@
       <c r="E447" t="n">
         <v>105</v>
       </c>
-      <c r="F447" t="n">
+      <c r="F447" s="1" t="n">
         <v>6771.37</v>
       </c>
-      <c r="G447" t="n">
+      <c r="G447" s="1" t="n">
         <v>64.48999999999999</v>
       </c>
       <c r="H447" t="n">
@@ -15202,10 +15205,10 @@
       <c r="E448" t="n">
         <v>104</v>
       </c>
-      <c r="F448" t="n">
+      <c r="F448" s="1" t="n">
         <v>17631.55</v>
       </c>
-      <c r="G448" t="n">
+      <c r="G448" s="1" t="n">
         <v>169.53</v>
       </c>
       <c r="H448" t="n">
@@ -15235,10 +15238,10 @@
       <c r="E449" t="n">
         <v>102</v>
       </c>
-      <c r="F449" t="n">
+      <c r="F449" s="1" t="n">
         <v>6250.97</v>
       </c>
-      <c r="G449" t="n">
+      <c r="G449" s="1" t="n">
         <v>60.11</v>
       </c>
       <c r="H449" t="n">
@@ -15268,10 +15271,10 @@
       <c r="E450" t="n">
         <v>99</v>
       </c>
-      <c r="F450" t="n">
+      <c r="F450" s="1" t="n">
         <v>10541.28</v>
       </c>
-      <c r="G450" t="n">
+      <c r="G450" s="1" t="n">
         <v>101.36</v>
       </c>
       <c r="H450" t="n">
@@ -15301,10 +15304,10 @@
       <c r="E451" t="n">
         <v>99</v>
       </c>
-      <c r="F451" t="n">
+      <c r="F451" s="1" t="n">
         <v>9625.17</v>
       </c>
-      <c r="G451" t="n">
+      <c r="G451" s="1" t="n">
         <v>94.36</v>
       </c>
       <c r="H451" t="n">
@@ -15334,10 +15337,10 @@
       <c r="E452" t="n">
         <v>96</v>
       </c>
-      <c r="F452" t="n">
+      <c r="F452" s="1" t="n">
         <v>2338.51</v>
       </c>
-      <c r="G452" t="n">
+      <c r="G452" s="1" t="n">
         <v>23.15</v>
       </c>
       <c r="H452" t="n">
@@ -15367,10 +15370,10 @@
       <c r="E453" t="n">
         <v>88</v>
       </c>
-      <c r="F453" t="n">
+      <c r="F453" s="1" t="n">
         <v>2885.55</v>
       </c>
-      <c r="G453" t="n">
+      <c r="G453" s="1" t="n">
         <v>28.86</v>
       </c>
       <c r="H453" t="n">
@@ -15400,10 +15403,10 @@
       <c r="E454" t="n">
         <v>95</v>
       </c>
-      <c r="F454" t="n">
+      <c r="F454" s="1" t="n">
         <v>13186.15</v>
       </c>
-      <c r="G454" t="n">
+      <c r="G454" s="1" t="n">
         <v>135.94</v>
       </c>
       <c r="H454" t="n">
@@ -15433,10 +15436,10 @@
       <c r="E455" t="n">
         <v>87</v>
       </c>
-      <c r="F455" t="n">
+      <c r="F455" s="1" t="n">
         <v>3016.84</v>
       </c>
-      <c r="G455" t="n">
+      <c r="G455" s="1" t="n">
         <v>31.43</v>
       </c>
       <c r="H455" t="n">
@@ -15466,10 +15469,10 @@
       <c r="E456" t="n">
         <v>96</v>
       </c>
-      <c r="F456" t="n">
+      <c r="F456" s="1" t="n">
         <v>10359.09</v>
       </c>
-      <c r="G456" t="n">
+      <c r="G456" s="1" t="n">
         <v>107.91</v>
       </c>
       <c r="H456" t="n">
@@ -15499,10 +15502,10 @@
       <c r="E457" t="n">
         <v>95</v>
       </c>
-      <c r="F457" t="n">
+      <c r="F457" s="1" t="n">
         <v>11499.05</v>
       </c>
-      <c r="G457" t="n">
+      <c r="G457" s="1" t="n">
         <v>119.78</v>
       </c>
       <c r="H457" t="n">
@@ -15532,10 +15535,10 @@
       <c r="E458" t="n">
         <v>81</v>
       </c>
-      <c r="F458" t="n">
+      <c r="F458" s="1" t="n">
         <v>2850.76</v>
       </c>
-      <c r="G458" t="n">
+      <c r="G458" s="1" t="n">
         <v>30.33</v>
       </c>
       <c r="H458" t="n">
@@ -15565,10 +15568,10 @@
       <c r="E459" t="n">
         <v>90</v>
       </c>
-      <c r="F459" t="n">
+      <c r="F459" s="1" t="n">
         <v>5438.650000000001</v>
       </c>
-      <c r="G459" t="n">
+      <c r="G459" s="1" t="n">
         <v>59.12</v>
       </c>
       <c r="H459" t="n">
@@ -15598,10 +15601,10 @@
       <c r="E460" t="n">
         <v>91</v>
       </c>
-      <c r="F460" t="n">
+      <c r="F460" s="1" t="n">
         <v>6022.3</v>
       </c>
-      <c r="G460" t="n">
+      <c r="G460" s="1" t="n">
         <v>66.18000000000001</v>
       </c>
       <c r="H460" t="n">
@@ -15631,10 +15634,10 @@
       <c r="E461" t="n">
         <v>91</v>
       </c>
-      <c r="F461" t="n">
+      <c r="F461" s="1" t="n">
         <v>9559.640000000001</v>
       </c>
-      <c r="G461" t="n">
+      <c r="G461" s="1" t="n">
         <v>105.05</v>
       </c>
       <c r="H461" t="n">
@@ -15664,10 +15667,10 @@
       <c r="E462" t="n">
         <v>90</v>
       </c>
-      <c r="F462" t="n">
+      <c r="F462" s="1" t="n">
         <v>8645.450000000001</v>
       </c>
-      <c r="G462" t="n">
+      <c r="G462" s="1" t="n">
         <v>96.06</v>
       </c>
       <c r="H462" t="n">
@@ -15697,10 +15700,10 @@
       <c r="E463" t="n">
         <v>88</v>
       </c>
-      <c r="F463" t="n">
+      <c r="F463" s="1" t="n">
         <v>3650.21</v>
       </c>
-      <c r="G463" t="n">
+      <c r="G463" s="1" t="n">
         <v>41.48</v>
       </c>
       <c r="H463" t="n">
@@ -15730,10 +15733,10 @@
       <c r="E464" t="n">
         <v>87</v>
       </c>
-      <c r="F464" t="n">
+      <c r="F464" s="1" t="n">
         <v>3049.41</v>
       </c>
-      <c r="G464" t="n">
+      <c r="G464" s="1" t="n">
         <v>35.05</v>
       </c>
       <c r="H464" t="n">
@@ -15763,10 +15766,10 @@
       <c r="E465" t="n">
         <v>87</v>
       </c>
-      <c r="F465" t="n">
+      <c r="F465" s="1" t="n">
         <v>3586.28</v>
       </c>
-      <c r="G465" t="n">
+      <c r="G465" s="1" t="n">
         <v>41.22</v>
       </c>
       <c r="H465" t="n">
@@ -15796,10 +15799,10 @@
       <c r="E466" t="n">
         <v>82</v>
       </c>
-      <c r="F466" t="n">
+      <c r="F466" s="1" t="n">
         <v>3999.1</v>
       </c>
-      <c r="G466" t="n">
+      <c r="G466" s="1" t="n">
         <v>45.97</v>
       </c>
       <c r="H466" t="n">
@@ -15829,10 +15832,10 @@
       <c r="E467" t="n">
         <v>84</v>
       </c>
-      <c r="F467" t="n">
+      <c r="F467" s="1" t="n">
         <v>4455.04</v>
       </c>
-      <c r="G467" t="n">
+      <c r="G467" s="1" t="n">
         <v>51.21</v>
       </c>
       <c r="H467" t="n">
@@ -15862,10 +15865,10 @@
       <c r="E468" t="n">
         <v>86</v>
       </c>
-      <c r="F468" t="n">
+      <c r="F468" s="1" t="n">
         <v>7411.33</v>
       </c>
-      <c r="G468" t="n">
+      <c r="G468" s="1" t="n">
         <v>85.19</v>
       </c>
       <c r="H468" t="n">
@@ -15895,10 +15898,10 @@
       <c r="E469" t="n">
         <v>63</v>
       </c>
-      <c r="F469" t="n">
+      <c r="F469" s="1" t="n">
         <v>1375.72</v>
       </c>
-      <c r="G469" t="n">
+      <c r="G469" s="1" t="n">
         <v>16</v>
       </c>
       <c r="H469" t="n">
@@ -15928,10 +15931,10 @@
       <c r="E470" t="n">
         <v>86</v>
       </c>
-      <c r="F470" t="n">
+      <c r="F470" s="1" t="n">
         <v>7471.940000000001</v>
       </c>
-      <c r="G470" t="n">
+      <c r="G470" s="1" t="n">
         <v>86.88</v>
       </c>
       <c r="H470" t="n">
@@ -15961,10 +15964,10 @@
       <c r="E471" t="n">
         <v>86</v>
       </c>
-      <c r="F471" t="n">
+      <c r="F471" s="1" t="n">
         <v>11031.15</v>
       </c>
-      <c r="G471" t="n">
+      <c r="G471" s="1" t="n">
         <v>128.27</v>
       </c>
       <c r="H471" t="n">
@@ -15994,10 +15997,10 @@
       <c r="E472" t="n">
         <v>83</v>
       </c>
-      <c r="F472" t="n">
+      <c r="F472" s="1" t="n">
         <v>6459.83</v>
       </c>
-      <c r="G472" t="n">
+      <c r="G472" s="1" t="n">
         <v>76</v>
       </c>
       <c r="H472" t="n">
@@ -16027,10 +16030,10 @@
       <c r="E473" t="n">
         <v>84</v>
       </c>
-      <c r="F473" t="n">
+      <c r="F473" s="1" t="n">
         <v>5150.54</v>
       </c>
-      <c r="G473" t="n">
+      <c r="G473" s="1" t="n">
         <v>61.32</v>
       </c>
       <c r="H473" t="n">
@@ -16060,10 +16063,10 @@
       <c r="E474" t="n">
         <v>65</v>
       </c>
-      <c r="F474" t="n">
+      <c r="F474" s="1" t="n">
         <v>1390.46</v>
       </c>
-      <c r="G474" t="n">
+      <c r="G474" s="1" t="n">
         <v>16.75</v>
       </c>
       <c r="H474" t="n">
@@ -16093,10 +16096,10 @@
       <c r="E475" t="n">
         <v>83</v>
       </c>
-      <c r="F475" t="n">
+      <c r="F475" s="1" t="n">
         <v>5346.63</v>
       </c>
-      <c r="G475" t="n">
+      <c r="G475" s="1" t="n">
         <v>64.42</v>
       </c>
       <c r="H475" t="n">
@@ -16126,10 +16129,10 @@
       <c r="E476" t="n">
         <v>80</v>
       </c>
-      <c r="F476" t="n">
+      <c r="F476" s="1" t="n">
         <v>3988.58</v>
       </c>
-      <c r="G476" t="n">
+      <c r="G476" s="1" t="n">
         <v>48.64</v>
       </c>
       <c r="H476" t="n">
@@ -16159,10 +16162,10 @@
       <c r="E477" t="n">
         <v>79</v>
       </c>
-      <c r="F477" t="n">
+      <c r="F477" s="1" t="n">
         <v>4885.19</v>
       </c>
-      <c r="G477" t="n">
+      <c r="G477" s="1" t="n">
         <v>60.31</v>
       </c>
       <c r="H477" t="n">
@@ -16192,10 +16195,10 @@
       <c r="E478" t="n">
         <v>78</v>
       </c>
-      <c r="F478" t="n">
+      <c r="F478" s="1" t="n">
         <v>3467.78</v>
       </c>
-      <c r="G478" t="n">
+      <c r="G478" s="1" t="n">
         <v>43.35</v>
       </c>
       <c r="H478" t="n">
@@ -16225,10 +16228,10 @@
       <c r="E479" t="n">
         <v>77</v>
       </c>
-      <c r="F479" t="n">
+      <c r="F479" s="1" t="n">
         <v>1667.1</v>
       </c>
-      <c r="G479" t="n">
+      <c r="G479" s="1" t="n">
         <v>21.1</v>
       </c>
       <c r="H479" t="n">
@@ -16258,10 +16261,10 @@
       <c r="E480" t="n">
         <v>79</v>
       </c>
-      <c r="F480" t="n">
+      <c r="F480" s="1" t="n">
         <v>7595.51</v>
       </c>
-      <c r="G480" t="n">
+      <c r="G480" s="1" t="n">
         <v>96.15000000000001</v>
       </c>
       <c r="H480" t="n">
@@ -16291,10 +16294,10 @@
       <c r="E481" t="n">
         <v>75</v>
       </c>
-      <c r="F481" t="n">
+      <c r="F481" s="1" t="n">
         <v>2422.36</v>
       </c>
-      <c r="G481" t="n">
+      <c r="G481" s="1" t="n">
         <v>31.06</v>
       </c>
       <c r="H481" t="n">
@@ -16324,10 +16327,10 @@
       <c r="E482" t="n">
         <v>65</v>
       </c>
-      <c r="F482" t="n">
+      <c r="F482" s="1" t="n">
         <v>5511.599999999999</v>
       </c>
-      <c r="G482" t="n">
+      <c r="G482" s="1" t="n">
         <v>70.66</v>
       </c>
       <c r="H482" t="n">
@@ -16357,10 +16360,10 @@
       <c r="E483" t="n">
         <v>77</v>
       </c>
-      <c r="F483" t="n">
+      <c r="F483" s="1" t="n">
         <v>7439.289999999999</v>
       </c>
-      <c r="G483" t="n">
+      <c r="G483" s="1" t="n">
         <v>96.61</v>
       </c>
       <c r="H483" t="n">
@@ -16390,10 +16393,10 @@
       <c r="E484" t="n">
         <v>71</v>
       </c>
-      <c r="F484" t="n">
+      <c r="F484" s="1" t="n">
         <v>9088.84</v>
       </c>
-      <c r="G484" t="n">
+      <c r="G484" s="1" t="n">
         <v>119.59</v>
       </c>
       <c r="H484" t="n">
@@ -16423,10 +16426,10 @@
       <c r="E485" t="n">
         <v>59</v>
       </c>
-      <c r="F485" t="n">
+      <c r="F485" s="1" t="n">
         <v>1595.95</v>
       </c>
-      <c r="G485" t="n">
+      <c r="G485" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H485" t="n">
@@ -16456,10 +16459,10 @@
       <c r="E486" t="n">
         <v>75</v>
       </c>
-      <c r="F486" t="n">
+      <c r="F486" s="1" t="n">
         <v>3990.35</v>
       </c>
-      <c r="G486" t="n">
+      <c r="G486" s="1" t="n">
         <v>53.2</v>
       </c>
       <c r="H486" t="n">
@@ -16489,10 +16492,10 @@
       <c r="E487" t="n">
         <v>66</v>
       </c>
-      <c r="F487" t="n">
+      <c r="F487" s="1" t="n">
         <v>1151.95</v>
       </c>
-      <c r="G487" t="n">
+      <c r="G487" s="1" t="n">
         <v>15.57</v>
       </c>
       <c r="H487" t="n">
@@ -16522,10 +16525,10 @@
       <c r="E488" t="n">
         <v>67</v>
       </c>
-      <c r="F488" t="n">
+      <c r="F488" s="1" t="n">
         <v>6834.27</v>
       </c>
-      <c r="G488" t="n">
+      <c r="G488" s="1" t="n">
         <v>99.05</v>
       </c>
       <c r="H488" t="n">
@@ -16555,10 +16558,10 @@
       <c r="E489" t="n">
         <v>67</v>
       </c>
-      <c r="F489" t="n">
+      <c r="F489" s="1" t="n">
         <v>3042.8</v>
       </c>
-      <c r="G489" t="n">
+      <c r="G489" s="1" t="n">
         <v>45.41</v>
       </c>
       <c r="H489" t="n">
@@ -16588,10 +16591,10 @@
       <c r="E490" t="n">
         <v>64</v>
       </c>
-      <c r="F490" t="n">
+      <c r="F490" s="1" t="n">
         <v>1225.6</v>
       </c>
-      <c r="G490" t="n">
+      <c r="G490" s="1" t="n">
         <v>19.15</v>
       </c>
       <c r="H490" t="n">
@@ -16621,10 +16624,10 @@
       <c r="E491" t="n">
         <v>64</v>
       </c>
-      <c r="F491" t="n">
+      <c r="F491" s="1" t="n">
         <v>7057.87</v>
       </c>
-      <c r="G491" t="n">
+      <c r="G491" s="1" t="n">
         <v>110.28</v>
       </c>
       <c r="H491" t="n">
@@ -16654,10 +16657,10 @@
       <c r="E492" t="n">
         <v>56</v>
       </c>
-      <c r="F492" t="n">
+      <c r="F492" s="1" t="n">
         <v>4761.82</v>
       </c>
-      <c r="G492" t="n">
+      <c r="G492" s="1" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="H492" t="n">
@@ -16687,10 +16690,10 @@
       <c r="E493" t="n">
         <v>56</v>
       </c>
-      <c r="F493" t="n">
+      <c r="F493" s="1" t="n">
         <v>5803.17</v>
       </c>
-      <c r="G493" t="n">
+      <c r="G493" s="1" t="n">
         <v>92.11</v>
       </c>
       <c r="H493" t="n">
@@ -16720,10 +16723,10 @@
       <c r="E494" t="n">
         <v>60</v>
       </c>
-      <c r="F494" t="n">
+      <c r="F494" s="1" t="n">
         <v>4515.39</v>
       </c>
-      <c r="G494" t="n">
+      <c r="G494" s="1" t="n">
         <v>72.83</v>
       </c>
       <c r="H494" t="n">
@@ -16753,10 +16756,10 @@
       <c r="E495" t="n">
         <v>57</v>
       </c>
-      <c r="F495" t="n">
+      <c r="F495" s="1" t="n">
         <v>14470.4</v>
       </c>
-      <c r="G495" t="n">
+      <c r="G495" s="1" t="n">
         <v>241.17</v>
       </c>
       <c r="H495" t="n">
@@ -16786,10 +16789,10 @@
       <c r="E496" t="n">
         <v>49</v>
       </c>
-      <c r="F496" t="n">
+      <c r="F496" s="1" t="n">
         <v>531.65</v>
       </c>
-      <c r="G496" t="n">
+      <c r="G496" s="1" t="n">
         <v>8.859999999999999</v>
       </c>
       <c r="H496" t="n">
@@ -16819,10 +16822,10 @@
       <c r="E497" t="n">
         <v>47</v>
       </c>
-      <c r="F497" t="n">
+      <c r="F497" s="1" t="n">
         <v>2913.09</v>
       </c>
-      <c r="G497" t="n">
+      <c r="G497" s="1" t="n">
         <v>50.23</v>
       </c>
       <c r="H497" t="n">
@@ -16852,10 +16855,10 @@
       <c r="E498" t="n">
         <v>58</v>
       </c>
-      <c r="F498" t="n">
+      <c r="F498" s="1" t="n">
         <v>6589.76</v>
       </c>
-      <c r="G498" t="n">
+      <c r="G498" s="1" t="n">
         <v>113.62</v>
       </c>
       <c r="H498" t="n">
@@ -16885,10 +16888,10 @@
       <c r="E499" t="n">
         <v>57</v>
       </c>
-      <c r="F499" t="n">
+      <c r="F499" s="1" t="n">
         <v>7274.39</v>
       </c>
-      <c r="G499" t="n">
+      <c r="G499" s="1" t="n">
         <v>127.62</v>
       </c>
       <c r="H499" t="n">
@@ -16918,10 +16921,10 @@
       <c r="E500" t="n">
         <v>56</v>
       </c>
-      <c r="F500" t="n">
+      <c r="F500" s="1" t="n">
         <v>4587.71</v>
       </c>
-      <c r="G500" t="n">
+      <c r="G500" s="1" t="n">
         <v>80.48999999999999</v>
       </c>
       <c r="H500" t="n">
@@ -16951,10 +16954,10 @@
       <c r="E501" t="n">
         <v>54</v>
       </c>
-      <c r="F501" t="n">
+      <c r="F501" s="1" t="n">
         <v>2186.55</v>
       </c>
-      <c r="G501" t="n">
+      <c r="G501" s="1" t="n">
         <v>39.05</v>
       </c>
       <c r="H501" t="n">
@@ -16984,10 +16987,10 @@
       <c r="E502" t="n">
         <v>56</v>
       </c>
-      <c r="F502" t="n">
+      <c r="F502" s="1" t="n">
         <v>8161.17</v>
       </c>
-      <c r="G502" t="n">
+      <c r="G502" s="1" t="n">
         <v>145.74</v>
       </c>
       <c r="H502" t="n">
@@ -17017,10 +17020,10 @@
       <c r="E503" t="n">
         <v>54</v>
       </c>
-      <c r="F503" t="n">
+      <c r="F503" s="1" t="n">
         <v>8678.370000000001</v>
       </c>
-      <c r="G503" t="n">
+      <c r="G503" s="1" t="n">
         <v>160.71</v>
       </c>
       <c r="H503" t="n">
@@ -17050,10 +17053,10 @@
       <c r="E504" t="n">
         <v>50</v>
       </c>
-      <c r="F504" t="n">
+      <c r="F504" s="1" t="n">
         <v>1300.17</v>
       </c>
-      <c r="G504" t="n">
+      <c r="G504" s="1" t="n">
         <v>24.08</v>
       </c>
       <c r="H504" t="n">
@@ -17083,10 +17086,10 @@
       <c r="E505" t="n">
         <v>42</v>
       </c>
-      <c r="F505" t="n">
+      <c r="F505" s="1" t="n">
         <v>807.73</v>
       </c>
-      <c r="G505" t="n">
+      <c r="G505" s="1" t="n">
         <v>15.24</v>
       </c>
       <c r="H505" t="n">
@@ -17116,10 +17119,10 @@
       <c r="E506" t="n">
         <v>51</v>
       </c>
-      <c r="F506" t="n">
+      <c r="F506" s="1" t="n">
         <v>11418.99</v>
       </c>
-      <c r="G506" t="n">
+      <c r="G506" s="1" t="n">
         <v>223.9</v>
       </c>
       <c r="H506" t="n">
@@ -17149,10 +17152,10 @@
       <c r="E507" t="n">
         <v>40</v>
       </c>
-      <c r="F507" t="n">
+      <c r="F507" s="1" t="n">
         <v>6449.82</v>
       </c>
-      <c r="G507" t="n">
+      <c r="G507" s="1" t="n">
         <v>129</v>
       </c>
       <c r="H507" t="n">
@@ -17182,10 +17185,10 @@
       <c r="E508" t="n">
         <v>49</v>
       </c>
-      <c r="F508" t="n">
+      <c r="F508" s="1" t="n">
         <v>2820.08</v>
       </c>
-      <c r="G508" t="n">
+      <c r="G508" s="1" t="n">
         <v>57.55</v>
       </c>
       <c r="H508" t="n">
@@ -17215,10 +17218,10 @@
       <c r="E509" t="n">
         <v>38</v>
       </c>
-      <c r="F509" t="n">
+      <c r="F509" s="1" t="n">
         <v>479.52</v>
       </c>
-      <c r="G509" t="n">
+      <c r="G509" s="1" t="n">
         <v>9.99</v>
       </c>
       <c r="H509" t="n">
@@ -17248,10 +17251,10 @@
       <c r="E510" t="n">
         <v>47</v>
       </c>
-      <c r="F510" t="n">
+      <c r="F510" s="1" t="n">
         <v>4472.51</v>
       </c>
-      <c r="G510" t="n">
+      <c r="G510" s="1" t="n">
         <v>95.16</v>
       </c>
       <c r="H510" t="n">
@@ -17281,10 +17284,10 @@
       <c r="E511" t="n">
         <v>39</v>
       </c>
-      <c r="F511" t="n">
+      <c r="F511" s="1" t="n">
         <v>1186.05</v>
       </c>
-      <c r="G511" t="n">
+      <c r="G511" s="1" t="n">
         <v>25.24</v>
       </c>
       <c r="H511" t="n">
@@ -17314,10 +17317,10 @@
       <c r="E512" t="n">
         <v>40</v>
       </c>
-      <c r="F512" t="n">
+      <c r="F512" s="1" t="n">
         <v>2194.55</v>
       </c>
-      <c r="G512" t="n">
+      <c r="G512" s="1" t="n">
         <v>47.71</v>
       </c>
       <c r="H512" t="n">
@@ -17347,10 +17350,10 @@
       <c r="E513" t="n">
         <v>46</v>
       </c>
-      <c r="F513" t="n">
+      <c r="F513" s="1" t="n">
         <v>1987.3</v>
       </c>
-      <c r="G513" t="n">
+      <c r="G513" s="1" t="n">
         <v>43.2</v>
       </c>
       <c r="H513" t="n">
@@ -17380,10 +17383,10 @@
       <c r="E514" t="n">
         <v>45</v>
       </c>
-      <c r="F514" t="n">
+      <c r="F514" s="1" t="n">
         <v>2542.55</v>
       </c>
-      <c r="G514" t="n">
+      <c r="G514" s="1" t="n">
         <v>56.5</v>
       </c>
       <c r="H514" t="n">
@@ -17413,10 +17416,10 @@
       <c r="E515" t="n">
         <v>45</v>
       </c>
-      <c r="F515" t="n">
+      <c r="F515" s="1" t="n">
         <v>3114.55</v>
       </c>
-      <c r="G515" t="n">
+      <c r="G515" s="1" t="n">
         <v>69.20999999999999</v>
       </c>
       <c r="H515" t="n">
@@ -17446,10 +17449,10 @@
       <c r="E516" t="n">
         <v>45</v>
       </c>
-      <c r="F516" t="n">
+      <c r="F516" s="1" t="n">
         <v>1242.24</v>
       </c>
-      <c r="G516" t="n">
+      <c r="G516" s="1" t="n">
         <v>27.61</v>
       </c>
       <c r="H516" t="n">
@@ -17479,10 +17482,10 @@
       <c r="E517" t="n">
         <v>40</v>
       </c>
-      <c r="F517" t="n">
+      <c r="F517" s="1" t="n">
         <v>1804.4</v>
       </c>
-      <c r="G517" t="n">
+      <c r="G517" s="1" t="n">
         <v>42.96</v>
       </c>
       <c r="H517" t="n">
@@ -17512,10 +17515,10 @@
       <c r="E518" t="n">
         <v>42</v>
       </c>
-      <c r="F518" t="n">
+      <c r="F518" s="1" t="n">
         <v>3359.58</v>
       </c>
-      <c r="G518" t="n">
+      <c r="G518" s="1" t="n">
         <v>79.98999999999999</v>
       </c>
       <c r="H518" t="n">
@@ -17545,10 +17548,10 @@
       <c r="E519" t="n">
         <v>38</v>
       </c>
-      <c r="F519" t="n">
+      <c r="F519" s="1" t="n">
         <v>3744.76</v>
       </c>
-      <c r="G519" t="n">
+      <c r="G519" s="1" t="n">
         <v>89.16</v>
       </c>
       <c r="H519" t="n">
@@ -17578,10 +17581,10 @@
       <c r="E520" t="n">
         <v>39</v>
       </c>
-      <c r="F520" t="n">
+      <c r="F520" s="1" t="n">
         <v>3482.53</v>
       </c>
-      <c r="G520" t="n">
+      <c r="G520" s="1" t="n">
         <v>82.92</v>
       </c>
       <c r="H520" t="n">
@@ -17611,10 +17614,10 @@
       <c r="E521" t="n">
         <v>39</v>
       </c>
-      <c r="F521" t="n">
+      <c r="F521" s="1" t="n">
         <v>3167.6</v>
       </c>
-      <c r="G521" t="n">
+      <c r="G521" s="1" t="n">
         <v>77.26000000000001</v>
       </c>
       <c r="H521" t="n">
@@ -17644,10 +17647,10 @@
       <c r="E522" t="n">
         <v>40</v>
       </c>
-      <c r="F522" t="n">
+      <c r="F522" s="1" t="n">
         <v>4992.25</v>
       </c>
-      <c r="G522" t="n">
+      <c r="G522" s="1" t="n">
         <v>124.81</v>
       </c>
       <c r="H522" t="n">
@@ -17677,10 +17680,10 @@
       <c r="E523" t="n">
         <v>39</v>
       </c>
-      <c r="F523" t="n">
+      <c r="F523" s="1" t="n">
         <v>1785.57</v>
       </c>
-      <c r="G523" t="n">
+      <c r="G523" s="1" t="n">
         <v>45.78</v>
       </c>
       <c r="H523" t="n">
@@ -17710,10 +17713,10 @@
       <c r="E524" t="n">
         <v>38</v>
       </c>
-      <c r="F524" t="n">
+      <c r="F524" s="1" t="n">
         <v>2324.91</v>
       </c>
-      <c r="G524" t="n">
+      <c r="G524" s="1" t="n">
         <v>59.61</v>
       </c>
       <c r="H524" t="n">
@@ -17743,10 +17746,10 @@
       <c r="E525" t="n">
         <v>38</v>
       </c>
-      <c r="F525" t="n">
+      <c r="F525" s="1" t="n">
         <v>1996.07</v>
       </c>
-      <c r="G525" t="n">
+      <c r="G525" s="1" t="n">
         <v>51.18</v>
       </c>
       <c r="H525" t="n">
@@ -17776,10 +17779,10 @@
       <c r="E526" t="n">
         <v>39</v>
       </c>
-      <c r="F526" t="n">
+      <c r="F526" s="1" t="n">
         <v>2320.31</v>
       </c>
-      <c r="G526" t="n">
+      <c r="G526" s="1" t="n">
         <v>59.5</v>
       </c>
       <c r="H526" t="n">
@@ -17809,10 +17812,10 @@
       <c r="E527" t="n">
         <v>33</v>
       </c>
-      <c r="F527" t="n">
+      <c r="F527" s="1" t="n">
         <v>1005.98</v>
       </c>
-      <c r="G527" t="n">
+      <c r="G527" s="1" t="n">
         <v>27.19</v>
       </c>
       <c r="H527" t="n">
@@ -17842,10 +17845,10 @@
       <c r="E528" t="n">
         <v>35</v>
       </c>
-      <c r="F528" t="n">
+      <c r="F528" s="1" t="n">
         <v>837.24</v>
       </c>
-      <c r="G528" t="n">
+      <c r="G528" s="1" t="n">
         <v>22.63</v>
       </c>
       <c r="H528" t="n">
@@ -17875,10 +17878,10 @@
       <c r="E529" t="n">
         <v>37</v>
       </c>
-      <c r="F529" t="n">
+      <c r="F529" s="1" t="n">
         <v>2931.25</v>
       </c>
-      <c r="G529" t="n">
+      <c r="G529" s="1" t="n">
         <v>79.22</v>
       </c>
       <c r="H529" t="n">
@@ -17908,10 +17911,10 @@
       <c r="E530" t="n">
         <v>36</v>
       </c>
-      <c r="F530" t="n">
+      <c r="F530" s="1" t="n">
         <v>1291.64</v>
       </c>
-      <c r="G530" t="n">
+      <c r="G530" s="1" t="n">
         <v>35.88</v>
       </c>
       <c r="H530" t="n">
@@ -17941,10 +17944,10 @@
       <c r="E531" t="n">
         <v>35</v>
       </c>
-      <c r="F531" t="n">
+      <c r="F531" s="1" t="n">
         <v>1758.43</v>
       </c>
-      <c r="G531" t="n">
+      <c r="G531" s="1" t="n">
         <v>50.24</v>
       </c>
       <c r="H531" t="n">
@@ -17974,10 +17977,10 @@
       <c r="E532" t="n">
         <v>34</v>
       </c>
-      <c r="F532" t="n">
+      <c r="F532" s="1" t="n">
         <v>585.4599999999999</v>
       </c>
-      <c r="G532" t="n">
+      <c r="G532" s="1" t="n">
         <v>17.22</v>
       </c>
       <c r="H532" t="n">
@@ -18007,10 +18010,10 @@
       <c r="E533" t="n">
         <v>33</v>
       </c>
-      <c r="F533" t="n">
+      <c r="F533" s="1" t="n">
         <v>1850.53</v>
       </c>
-      <c r="G533" t="n">
+      <c r="G533" s="1" t="n">
         <v>56.08</v>
       </c>
       <c r="H533" t="n">
@@ -18040,10 +18043,10 @@
       <c r="E534" t="n">
         <v>24</v>
       </c>
-      <c r="F534" t="n">
+      <c r="F534" s="1" t="n">
         <v>2658.67</v>
       </c>
-      <c r="G534" t="n">
+      <c r="G534" s="1" t="n">
         <v>80.56999999999999</v>
       </c>
       <c r="H534" t="n">
@@ -18073,10 +18076,10 @@
       <c r="E535" t="n">
         <v>32</v>
       </c>
-      <c r="F535" t="n">
+      <c r="F535" s="1" t="n">
         <v>29959.68</v>
       </c>
-      <c r="G535" t="n">
+      <c r="G535" s="1" t="n">
         <v>936.24</v>
       </c>
       <c r="H535" t="n">
@@ -18106,10 +18109,10 @@
       <c r="E536" t="n">
         <v>30</v>
       </c>
-      <c r="F536" t="n">
+      <c r="F536" s="1" t="n">
         <v>4202.66</v>
       </c>
-      <c r="G536" t="n">
+      <c r="G536" s="1" t="n">
         <v>131.33</v>
       </c>
       <c r="H536" t="n">
@@ -18139,10 +18142,10 @@
       <c r="E537" t="n">
         <v>30</v>
       </c>
-      <c r="F537" t="n">
+      <c r="F537" s="1" t="n">
         <v>1642.69</v>
       </c>
-      <c r="G537" t="n">
+      <c r="G537" s="1" t="n">
         <v>52.99</v>
       </c>
       <c r="H537" t="n">
@@ -18172,10 +18175,10 @@
       <c r="E538" t="n">
         <v>27</v>
       </c>
-      <c r="F538" t="n">
+      <c r="F538" s="1" t="n">
         <v>553.25</v>
       </c>
-      <c r="G538" t="n">
+      <c r="G538" s="1" t="n">
         <v>18.44</v>
       </c>
       <c r="H538" t="n">
@@ -18205,10 +18208,10 @@
       <c r="E539" t="n">
         <v>29</v>
       </c>
-      <c r="F539" t="n">
+      <c r="F539" s="1" t="n">
         <v>27549.71</v>
       </c>
-      <c r="G539" t="n">
+      <c r="G539" s="1" t="n">
         <v>949.99</v>
       </c>
       <c r="H539" t="n">
@@ -18238,10 +18241,10 @@
       <c r="E540" t="n">
         <v>29</v>
       </c>
-      <c r="F540" t="n">
+      <c r="F540" s="1" t="n">
         <v>2319.71</v>
       </c>
-      <c r="G540" t="n">
+      <c r="G540" s="1" t="n">
         <v>79.98999999999999</v>
       </c>
       <c r="H540" t="n">
@@ -18271,10 +18274,10 @@
       <c r="E541" t="n">
         <v>29</v>
       </c>
-      <c r="F541" t="n">
+      <c r="F541" s="1" t="n">
         <v>26594.71</v>
       </c>
-      <c r="G541" t="n">
+      <c r="G541" s="1" t="n">
         <v>917.0599999999999</v>
       </c>
       <c r="H541" t="n">
@@ -18304,10 +18307,10 @@
       <c r="E542" t="n">
         <v>21</v>
       </c>
-      <c r="F542" t="n">
+      <c r="F542" s="1" t="n">
         <v>841.41</v>
       </c>
-      <c r="G542" t="n">
+      <c r="G542" s="1" t="n">
         <v>30.05</v>
       </c>
       <c r="H542" t="n">
@@ -18337,10 +18340,10 @@
       <c r="E543" t="n">
         <v>21</v>
       </c>
-      <c r="F543" t="n">
+      <c r="F543" s="1" t="n">
         <v>910.84</v>
       </c>
-      <c r="G543" t="n">
+      <c r="G543" s="1" t="n">
         <v>32.53</v>
       </c>
       <c r="H543" t="n">
@@ -18370,10 +18373,10 @@
       <c r="E544" t="n">
         <v>28</v>
       </c>
-      <c r="F544" t="n">
+      <c r="F544" s="1" t="n">
         <v>2342.73</v>
       </c>
-      <c r="G544" t="n">
+      <c r="G544" s="1" t="n">
         <v>83.67</v>
       </c>
       <c r="H544" t="n">
@@ -18403,10 +18406,10 @@
       <c r="E545" t="n">
         <v>24</v>
       </c>
-      <c r="F545" t="n">
+      <c r="F545" s="1" t="n">
         <v>784.6799999999999</v>
       </c>
-      <c r="G545" t="n">
+      <c r="G545" s="1" t="n">
         <v>29.06</v>
       </c>
       <c r="H545" t="n">
@@ -18436,10 +18439,10 @@
       <c r="E546" t="n">
         <v>26</v>
       </c>
-      <c r="F546" t="n">
+      <c r="F546" s="1" t="n">
         <v>1682.52</v>
       </c>
-      <c r="G546" t="n">
+      <c r="G546" s="1" t="n">
         <v>64.70999999999999</v>
       </c>
       <c r="H546" t="n">
@@ -18469,10 +18472,10 @@
       <c r="E547" t="n">
         <v>23</v>
       </c>
-      <c r="F547" t="n">
+      <c r="F547" s="1" t="n">
         <v>963.76</v>
       </c>
-      <c r="G547" t="n">
+      <c r="G547" s="1" t="n">
         <v>40.16</v>
       </c>
       <c r="H547" t="n">
@@ -18502,10 +18505,10 @@
       <c r="E548" t="n">
         <v>18</v>
       </c>
-      <c r="F548" t="n">
+      <c r="F548" s="1" t="n">
         <v>755.79</v>
       </c>
-      <c r="G548" t="n">
+      <c r="G548" s="1" t="n">
         <v>32.86</v>
       </c>
       <c r="H548" t="n">
@@ -18535,10 +18538,10 @@
       <c r="E549" t="n">
         <v>19</v>
       </c>
-      <c r="F549" t="n">
+      <c r="F549" s="1" t="n">
         <v>368.21</v>
       </c>
-      <c r="G549" t="n">
+      <c r="G549" s="1" t="n">
         <v>16.01</v>
       </c>
       <c r="H549" t="n">
@@ -18568,10 +18571,10 @@
       <c r="E550" t="n">
         <v>17</v>
       </c>
-      <c r="F550" t="n">
+      <c r="F550" s="1" t="n">
         <v>355.3</v>
       </c>
-      <c r="G550" t="n">
+      <c r="G550" s="1" t="n">
         <v>16.15</v>
       </c>
       <c r="H550" t="n">
@@ -18601,10 +18604,10 @@
       <c r="E551" t="n">
         <v>22</v>
       </c>
-      <c r="F551" t="n">
+      <c r="F551" s="1" t="n">
         <v>1250.79</v>
       </c>
-      <c r="G551" t="n">
+      <c r="G551" s="1" t="n">
         <v>56.85</v>
       </c>
       <c r="H551" t="n">
@@ -18634,10 +18637,10 @@
       <c r="E552" t="n">
         <v>20</v>
       </c>
-      <c r="F552" t="n">
+      <c r="F552" s="1" t="n">
         <v>1277.31</v>
       </c>
-      <c r="G552" t="n">
+      <c r="G552" s="1" t="n">
         <v>63.87</v>
       </c>
       <c r="H552" t="n">
@@ -18667,10 +18670,10 @@
       <c r="E553" t="n">
         <v>19</v>
       </c>
-      <c r="F553" t="n">
+      <c r="F553" s="1" t="n">
         <v>1217.81</v>
       </c>
-      <c r="G553" t="n">
+      <c r="G553" s="1" t="n">
         <v>60.89</v>
       </c>
       <c r="H553" t="n">
@@ -18700,10 +18703,10 @@
       <c r="E554" t="n">
         <v>20</v>
       </c>
-      <c r="F554" t="n">
+      <c r="F554" s="1" t="n">
         <v>1071.62</v>
       </c>
-      <c r="G554" t="n">
+      <c r="G554" s="1" t="n">
         <v>53.58</v>
       </c>
       <c r="H554" t="n">
@@ -18733,10 +18736,10 @@
       <c r="E555" t="n">
         <v>18</v>
       </c>
-      <c r="F555" t="n">
+      <c r="F555" s="1" t="n">
         <v>626.8</v>
       </c>
-      <c r="G555" t="n">
+      <c r="G555" s="1" t="n">
         <v>31.34</v>
       </c>
       <c r="H555" t="n">
@@ -18766,10 +18769,10 @@
       <c r="E556" t="n">
         <v>17</v>
       </c>
-      <c r="F556" t="n">
+      <c r="F556" s="1" t="n">
         <v>8454.82</v>
       </c>
-      <c r="G556" t="n">
+      <c r="G556" s="1" t="n">
         <v>469.71</v>
       </c>
       <c r="H556" t="n">
@@ -18799,10 +18802,10 @@
       <c r="E557" t="n">
         <v>17</v>
       </c>
-      <c r="F557" t="n">
+      <c r="F557" s="1" t="n">
         <v>495.22</v>
       </c>
-      <c r="G557" t="n">
+      <c r="G557" s="1" t="n">
         <v>27.51</v>
       </c>
       <c r="H557" t="n">
@@ -18832,10 +18835,10 @@
       <c r="E558" t="n">
         <v>17</v>
       </c>
-      <c r="F558" t="n">
+      <c r="F558" s="1" t="n">
         <v>1869.83</v>
       </c>
-      <c r="G558" t="n">
+      <c r="G558" s="1" t="n">
         <v>109.99</v>
       </c>
       <c r="H558" t="n">
@@ -18865,10 +18868,10 @@
       <c r="E559" t="n">
         <v>17</v>
       </c>
-      <c r="F559" t="n">
+      <c r="F559" s="1" t="n">
         <v>940.63</v>
       </c>
-      <c r="G559" t="n">
+      <c r="G559" s="1" t="n">
         <v>55.33</v>
       </c>
       <c r="H559" t="n">
@@ -18898,10 +18901,10 @@
       <c r="E560" t="n">
         <v>16</v>
       </c>
-      <c r="F560" t="n">
+      <c r="F560" s="1" t="n">
         <v>229.83</v>
       </c>
-      <c r="G560" t="n">
+      <c r="G560" s="1" t="n">
         <v>13.52</v>
       </c>
       <c r="H560" t="n">
@@ -18931,10 +18934,10 @@
       <c r="E561" t="n">
         <v>17</v>
       </c>
-      <c r="F561" t="n">
+      <c r="F561" s="1" t="n">
         <v>2573.03</v>
       </c>
-      <c r="G561" t="n">
+      <c r="G561" s="1" t="n">
         <v>151.35</v>
       </c>
       <c r="H561" t="n">
@@ -18964,10 +18967,10 @@
       <c r="E562" t="n">
         <v>15</v>
       </c>
-      <c r="F562" t="n">
+      <c r="F562" s="1" t="n">
         <v>720.99</v>
       </c>
-      <c r="G562" t="n">
+      <c r="G562" s="1" t="n">
         <v>45.06</v>
       </c>
       <c r="H562" t="n">
@@ -18997,10 +19000,10 @@
       <c r="E563" t="n">
         <v>12</v>
       </c>
-      <c r="F563" t="n">
+      <c r="F563" s="1" t="n">
         <v>227.16</v>
       </c>
-      <c r="G563" t="n">
+      <c r="G563" s="1" t="n">
         <v>14.2</v>
       </c>
       <c r="H563" t="n">
@@ -19030,10 +19033,10 @@
       <c r="E564" t="n">
         <v>15</v>
       </c>
-      <c r="F564" t="n">
+      <c r="F564" s="1" t="n">
         <v>254.72</v>
       </c>
-      <c r="G564" t="n">
+      <c r="G564" s="1" t="n">
         <v>16.98</v>
       </c>
       <c r="H564" t="n">
@@ -19063,10 +19066,10 @@
       <c r="E565" t="n">
         <v>15</v>
       </c>
-      <c r="F565" t="n">
+      <c r="F565" s="1" t="n">
         <v>538.85</v>
       </c>
-      <c r="G565" t="n">
+      <c r="G565" s="1" t="n">
         <v>35.92</v>
       </c>
       <c r="H565" t="n">
@@ -19096,10 +19099,10 @@
       <c r="E566" t="n">
         <v>15</v>
       </c>
-      <c r="F566" t="n">
+      <c r="F566" s="1" t="n">
         <v>1033.85</v>
       </c>
-      <c r="G566" t="n">
+      <c r="G566" s="1" t="n">
         <v>68.92</v>
       </c>
       <c r="H566" t="n">
@@ -19129,10 +19132,10 @@
       <c r="E567" t="n">
         <v>14</v>
       </c>
-      <c r="F567" t="n">
+      <c r="F567" s="1" t="n">
         <v>232.26</v>
       </c>
-      <c r="G567" t="n">
+      <c r="G567" s="1" t="n">
         <v>16.59</v>
       </c>
       <c r="H567" t="n">
@@ -19162,10 +19165,10 @@
       <c r="E568" t="n">
         <v>14</v>
       </c>
-      <c r="F568" t="n">
+      <c r="F568" s="1" t="n">
         <v>2099.86</v>
       </c>
-      <c r="G568" t="n">
+      <c r="G568" s="1" t="n">
         <v>149.99</v>
       </c>
       <c r="H568" t="n">
@@ -19195,10 +19198,10 @@
       <c r="E569" t="n">
         <v>14</v>
       </c>
-      <c r="F569" t="n">
+      <c r="F569" s="1" t="n">
         <v>2161.86</v>
       </c>
-      <c r="G569" t="n">
+      <c r="G569" s="1" t="n">
         <v>154.42</v>
       </c>
       <c r="H569" t="n">
@@ -19228,10 +19231,10 @@
       <c r="E570" t="n">
         <v>14</v>
       </c>
-      <c r="F570" t="n">
+      <c r="F570" s="1" t="n">
         <v>1159.86</v>
       </c>
-      <c r="G570" t="n">
+      <c r="G570" s="1" t="n">
         <v>82.84999999999999</v>
       </c>
       <c r="H570" t="n">
@@ -19261,10 +19264,10 @@
       <c r="E571" t="n">
         <v>12</v>
       </c>
-      <c r="F571" t="n">
+      <c r="F571" s="1" t="n">
         <v>402.87</v>
       </c>
-      <c r="G571" t="n">
+      <c r="G571" s="1" t="n">
         <v>30.99</v>
       </c>
       <c r="H571" t="n">
@@ -19294,10 +19297,10 @@
       <c r="E572" t="n">
         <v>12</v>
       </c>
-      <c r="F572" t="n">
+      <c r="F572" s="1" t="n">
         <v>239.88</v>
       </c>
-      <c r="G572" t="n">
+      <c r="G572" s="1" t="n">
         <v>19.99</v>
       </c>
       <c r="H572" t="n">
@@ -19327,10 +19330,10 @@
       <c r="E573" t="n">
         <v>10</v>
       </c>
-      <c r="F573" t="n">
+      <c r="F573" s="1" t="n">
         <v>433.71</v>
       </c>
-      <c r="G573" t="n">
+      <c r="G573" s="1" t="n">
         <v>43.37</v>
       </c>
       <c r="H573" t="n">
@@ -19360,10 +19363,10 @@
       <c r="E574" t="n">
         <v>10</v>
       </c>
-      <c r="F574" t="n">
+      <c r="F574" s="1" t="n">
         <v>179.9</v>
       </c>
-      <c r="G574" t="n">
+      <c r="G574" s="1" t="n">
         <v>17.99</v>
       </c>
       <c r="H574" t="n">
@@ -19393,10 +19396,10 @@
       <c r="E575" t="n">
         <v>8</v>
       </c>
-      <c r="F575" t="n">
+      <c r="F575" s="1" t="n">
         <v>529.87</v>
       </c>
-      <c r="G575" t="n">
+      <c r="G575" s="1" t="n">
         <v>52.99</v>
       </c>
       <c r="H575" t="n">
@@ -19426,10 +19429,10 @@
       <c r="E576" t="n">
         <v>9</v>
       </c>
-      <c r="F576" t="n">
+      <c r="F576" s="1" t="n">
         <v>1349.91</v>
       </c>
-      <c r="G576" t="n">
+      <c r="G576" s="1" t="n">
         <v>149.99</v>
       </c>
       <c r="H576" t="n">
@@ -19459,10 +19462,10 @@
       <c r="E577" t="n">
         <v>6</v>
       </c>
-      <c r="F577" t="n">
+      <c r="F577" s="1" t="n">
         <v>245.91</v>
       </c>
-      <c r="G577" t="n">
+      <c r="G577" s="1" t="n">
         <v>27.32</v>
       </c>
       <c r="H577" t="n">
@@ -19492,10 +19495,10 @@
       <c r="E578" t="n">
         <v>8</v>
       </c>
-      <c r="F578" t="n">
+      <c r="F578" s="1" t="n">
         <v>939.92</v>
       </c>
-      <c r="G578" t="n">
+      <c r="G578" s="1" t="n">
         <v>117.49</v>
       </c>
       <c r="H578" t="n">
@@ -19525,10 +19528,10 @@
       <c r="E579" t="n">
         <v>7</v>
       </c>
-      <c r="F579" t="n">
+      <c r="F579" s="1" t="n">
         <v>179.34</v>
       </c>
-      <c r="G579" t="n">
+      <c r="G579" s="1" t="n">
         <v>25.62</v>
       </c>
       <c r="H579" t="n">
@@ -19558,10 +19561,10 @@
       <c r="E580" t="n">
         <v>7</v>
       </c>
-      <c r="F580" t="n">
+      <c r="F580" s="1" t="n">
         <v>503.93</v>
       </c>
-      <c r="G580" t="n">
+      <c r="G580" s="1" t="n">
         <v>71.98999999999999</v>
       </c>
       <c r="H580" t="n">
@@ -19591,10 +19594,10 @@
       <c r="E581" t="n">
         <v>6</v>
       </c>
-      <c r="F581" t="n">
+      <c r="F581" s="1" t="n">
         <v>90.93000000000001</v>
       </c>
-      <c r="G581" t="n">
+      <c r="G581" s="1" t="n">
         <v>12.99</v>
       </c>
       <c r="H581" t="n">
@@ -19624,10 +19627,10 @@
       <c r="E582" t="n">
         <v>6</v>
       </c>
-      <c r="F582" t="n">
+      <c r="F582" s="1" t="n">
         <v>103.75</v>
       </c>
-      <c r="G582" t="n">
+      <c r="G582" s="1" t="n">
         <v>17.29</v>
       </c>
       <c r="H582" t="n">
@@ -19657,10 +19660,10 @@
       <c r="E583" t="n">
         <v>6</v>
       </c>
-      <c r="F583" t="n">
+      <c r="F583" s="1" t="n">
         <v>398.94</v>
       </c>
-      <c r="G583" t="n">
+      <c r="G583" s="1" t="n">
         <v>66.48999999999999</v>
       </c>
       <c r="H583" t="n">
@@ -19690,10 +19693,10 @@
       <c r="E584" t="n">
         <v>6</v>
       </c>
-      <c r="F584" t="n">
+      <c r="F584" s="1" t="n">
         <v>106.36</v>
       </c>
-      <c r="G584" t="n">
+      <c r="G584" s="1" t="n">
         <v>17.73</v>
       </c>
       <c r="H584" t="n">
@@ -19723,10 +19726,10 @@
       <c r="E585" t="n">
         <v>5</v>
       </c>
-      <c r="F585" t="n">
+      <c r="F585" s="1" t="n">
         <v>2712.93</v>
       </c>
-      <c r="G585" t="n">
+      <c r="G585" s="1" t="n">
         <v>542.59</v>
       </c>
       <c r="H585" t="n">
@@ -19756,10 +19759,10 @@
       <c r="E586" t="n">
         <v>4</v>
       </c>
-      <c r="F586" t="n">
+      <c r="F586" s="1" t="n">
         <v>213.45</v>
       </c>
-      <c r="G586" t="n">
+      <c r="G586" s="1" t="n">
         <v>42.69</v>
       </c>
       <c r="H586" t="n">
@@ -19789,10 +19792,10 @@
       <c r="E587" t="n">
         <v>4</v>
       </c>
-      <c r="F587" t="n">
+      <c r="F587" s="1" t="n">
         <v>147.96</v>
       </c>
-      <c r="G587" t="n">
+      <c r="G587" s="1" t="n">
         <v>36.99</v>
       </c>
       <c r="H587" t="n">
@@ -19822,10 +19825,10 @@
       <c r="E588" t="n">
         <v>4</v>
       </c>
-      <c r="F588" t="n">
+      <c r="F588" s="1" t="n">
         <v>332.03</v>
       </c>
-      <c r="G588" t="n">
+      <c r="G588" s="1" t="n">
         <v>83.01000000000001</v>
       </c>
       <c r="H588" t="n">
@@ -19855,10 +19858,10 @@
       <c r="E589" t="n">
         <v>4</v>
       </c>
-      <c r="F589" t="n">
+      <c r="F589" s="1" t="n">
         <v>344.96</v>
       </c>
-      <c r="G589" t="n">
+      <c r="G589" s="1" t="n">
         <v>86.23999999999999</v>
       </c>
       <c r="H589" t="n">
@@ -19888,10 +19891,10 @@
       <c r="E590" t="n">
         <v>4</v>
       </c>
-      <c r="F590" t="n">
+      <c r="F590" s="1" t="n">
         <v>190.42</v>
       </c>
-      <c r="G590" t="n">
+      <c r="G590" s="1" t="n">
         <v>47.6</v>
       </c>
       <c r="H590" t="n">
@@ -19921,10 +19924,10 @@
       <c r="E591" t="n">
         <v>4</v>
       </c>
-      <c r="F591" t="n">
+      <c r="F591" s="1" t="n">
         <v>131.96</v>
       </c>
-      <c r="G591" t="n">
+      <c r="G591" s="1" t="n">
         <v>32.99</v>
       </c>
       <c r="H591" t="n">
@@ -19954,10 +19957,10 @@
       <c r="E592" t="n">
         <v>3</v>
       </c>
-      <c r="F592" t="n">
+      <c r="F592" s="1" t="n">
         <v>83.97</v>
       </c>
-      <c r="G592" t="n">
+      <c r="G592" s="1" t="n">
         <v>27.99</v>
       </c>
       <c r="H592" t="n">
@@ -19987,10 +19990,10 @@
       <c r="E593" t="n">
         <v>3</v>
       </c>
-      <c r="F593" t="n">
+      <c r="F593" s="1" t="n">
         <v>29.97</v>
       </c>
-      <c r="G593" t="n">
+      <c r="G593" s="1" t="n">
         <v>9.99</v>
       </c>
       <c r="H593" t="n">
@@ -20020,10 +20023,10 @@
       <c r="E594" t="n">
         <v>3</v>
       </c>
-      <c r="F594" t="n">
+      <c r="F594" s="1" t="n">
         <v>51.03</v>
       </c>
-      <c r="G594" t="n">
+      <c r="G594" s="1" t="n">
         <v>17.01</v>
       </c>
       <c r="H594" t="n">
@@ -20053,10 +20056,10 @@
       <c r="E595" t="n">
         <v>3</v>
       </c>
-      <c r="F595" t="n">
+      <c r="F595" s="1" t="n">
         <v>329.97</v>
       </c>
-      <c r="G595" t="n">
+      <c r="G595" s="1" t="n">
         <v>109.99</v>
       </c>
       <c r="H595" t="n">
@@ -20086,10 +20089,10 @@
       <c r="E596" t="n">
         <v>3</v>
       </c>
-      <c r="F596" t="n">
+      <c r="F596" s="1" t="n">
         <v>56.97</v>
       </c>
-      <c r="G596" t="n">
+      <c r="G596" s="1" t="n">
         <v>18.99</v>
       </c>
       <c r="H596" t="n">
@@ -20119,10 +20122,10 @@
       <c r="E597" t="n">
         <v>3</v>
       </c>
-      <c r="F597" t="n">
+      <c r="F597" s="1" t="n">
         <v>350.67</v>
       </c>
-      <c r="G597" t="n">
+      <c r="G597" s="1" t="n">
         <v>116.89</v>
       </c>
       <c r="H597" t="n">
@@ -20152,10 +20155,10 @@
       <c r="E598" t="n">
         <v>3</v>
       </c>
-      <c r="F598" t="n">
+      <c r="F598" s="1" t="n">
         <v>329.97</v>
       </c>
-      <c r="G598" t="n">
+      <c r="G598" s="1" t="n">
         <v>109.99</v>
       </c>
       <c r="H598" t="n">
@@ -20185,10 +20188,10 @@
       <c r="E599" t="n">
         <v>3</v>
       </c>
-      <c r="F599" t="n">
+      <c r="F599" s="1" t="n">
         <v>98.97</v>
       </c>
-      <c r="G599" t="n">
+      <c r="G599" s="1" t="n">
         <v>32.99</v>
       </c>
       <c r="H599" t="n">
@@ -20218,10 +20221,10 @@
       <c r="E600" t="n">
         <v>3</v>
       </c>
-      <c r="F600" t="n">
+      <c r="F600" s="1" t="n">
         <v>89.97</v>
       </c>
-      <c r="G600" t="n">
+      <c r="G600" s="1" t="n">
         <v>29.99</v>
       </c>
       <c r="H600" t="n">
@@ -20251,10 +20254,10 @@
       <c r="E601" t="n">
         <v>2</v>
       </c>
-      <c r="F601" t="n">
+      <c r="F601" s="1" t="n">
         <v>195.98</v>
       </c>
-      <c r="G601" t="n">
+      <c r="G601" s="1" t="n">
         <v>97.98999999999999</v>
       </c>
       <c r="H601" t="n">
@@ -20284,10 +20287,10 @@
       <c r="E602" t="n">
         <v>2</v>
       </c>
-      <c r="F602" t="n">
+      <c r="F602" s="1" t="n">
         <v>119.98</v>
       </c>
-      <c r="G602" t="n">
+      <c r="G602" s="1" t="n">
         <v>59.99</v>
       </c>
       <c r="H602" t="n">
@@ -20317,10 +20320,10 @@
       <c r="E603" t="n">
         <v>2</v>
       </c>
-      <c r="F603" t="n">
+      <c r="F603" s="1" t="n">
         <v>56.25</v>
       </c>
-      <c r="G603" t="n">
+      <c r="G603" s="1" t="n">
         <v>28.12</v>
       </c>
       <c r="H603" t="n">
@@ -20350,10 +20353,10 @@
       <c r="E604" t="n">
         <v>2</v>
       </c>
-      <c r="F604" t="n">
+      <c r="F604" s="1" t="n">
         <v>145.53</v>
       </c>
-      <c r="G604" t="n">
+      <c r="G604" s="1" t="n">
         <v>72.76000000000001</v>
       </c>
       <c r="H604" t="n">
@@ -20383,10 +20386,10 @@
       <c r="E605" t="n">
         <v>2</v>
       </c>
-      <c r="F605" t="n">
+      <c r="F605" s="1" t="n">
         <v>148.5</v>
       </c>
-      <c r="G605" t="n">
+      <c r="G605" s="1" t="n">
         <v>74.25</v>
       </c>
       <c r="H605" t="n">
@@ -20416,10 +20419,10 @@
       <c r="E606" t="n">
         <v>2</v>
       </c>
-      <c r="F606" t="n">
+      <c r="F606" s="1" t="n">
         <v>95.98</v>
       </c>
-      <c r="G606" t="n">
+      <c r="G606" s="1" t="n">
         <v>47.99</v>
       </c>
       <c r="H606" t="n">
@@ -20449,10 +20452,10 @@
       <c r="E607" t="n">
         <v>2</v>
       </c>
-      <c r="F607" t="n">
+      <c r="F607" s="1" t="n">
         <v>52.99</v>
       </c>
-      <c r="G607" t="n">
+      <c r="G607" s="1" t="n">
         <v>26.5</v>
       </c>
       <c r="H607" t="n">
@@ -20482,10 +20485,10 @@
       <c r="E608" t="n">
         <v>2</v>
       </c>
-      <c r="F608" t="n">
+      <c r="F608" s="1" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="G608" t="n">
+      <c r="G608" s="1" t="n">
         <v>35.7</v>
       </c>
       <c r="H608" t="n">
@@ -20515,10 +20518,10 @@
       <c r="E609" t="n">
         <v>2</v>
       </c>
-      <c r="F609" t="n">
+      <c r="F609" s="1" t="n">
         <v>239.98</v>
       </c>
-      <c r="G609" t="n">
+      <c r="G609" s="1" t="n">
         <v>119.99</v>
       </c>
       <c r="H609" t="n">
@@ -20548,10 +20551,10 @@
       <c r="E610" t="n">
         <v>2</v>
       </c>
-      <c r="F610" t="n">
+      <c r="F610" s="1" t="n">
         <v>120.77</v>
       </c>
-      <c r="G610" t="n">
+      <c r="G610" s="1" t="n">
         <v>60.38</v>
       </c>
       <c r="H610" t="n">
@@ -20581,10 +20584,10 @@
       <c r="E611" t="n">
         <v>1</v>
       </c>
-      <c r="F611" t="n">
+      <c r="F611" s="1" t="n">
         <v>26.7</v>
       </c>
-      <c r="G611" t="n">
+      <c r="G611" s="1" t="n">
         <v>26.7</v>
       </c>
       <c r="H611" t="n">
@@ -20614,10 +20617,10 @@
       <c r="E612" t="n">
         <v>1</v>
       </c>
-      <c r="F612" t="n">
+      <c r="F612" s="1" t="n">
         <v>83.08</v>
       </c>
-      <c r="G612" t="n">
+      <c r="G612" s="1" t="n">
         <v>83.08</v>
       </c>
       <c r="H612" t="n">
@@ -20647,10 +20650,10 @@
       <c r="E613" t="n">
         <v>1</v>
       </c>
-      <c r="F613" t="n">
+      <c r="F613" s="1" t="n">
         <v>20.77</v>
       </c>
-      <c r="G613" t="n">
+      <c r="G613" s="1" t="n">
         <v>20.77</v>
       </c>
       <c r="H613" t="n">
@@ -20680,10 +20683,10 @@
       <c r="E614" t="n">
         <v>1</v>
       </c>
-      <c r="F614" t="n">
+      <c r="F614" s="1" t="n">
         <v>59.99</v>
       </c>
-      <c r="G614" t="n">
+      <c r="G614" s="1" t="n">
         <v>59.99</v>
       </c>
       <c r="H614" t="n">
@@ -20713,10 +20716,10 @@
       <c r="E615" t="n">
         <v>1</v>
       </c>
-      <c r="F615" t="n">
+      <c r="F615" s="1" t="n">
         <v>62.99</v>
       </c>
-      <c r="G615" t="n">
+      <c r="G615" s="1" t="n">
         <v>62.99</v>
       </c>
       <c r="H615" t="n">
@@ -20746,10 +20749,10 @@
       <c r="E616" t="n">
         <v>1</v>
       </c>
-      <c r="F616" t="n">
+      <c r="F616" s="1" t="n">
         <v>71.86</v>
       </c>
-      <c r="G616" t="n">
+      <c r="G616" s="1" t="n">
         <v>71.86</v>
       </c>
       <c r="H616" t="n">
@@ -20779,10 +20782,10 @@
       <c r="E617" t="n">
         <v>1</v>
       </c>
-      <c r="F617" t="n">
+      <c r="F617" s="1" t="n">
         <v>53.19</v>
       </c>
-      <c r="G617" t="n">
+      <c r="G617" s="1" t="n">
         <v>53.19</v>
       </c>
       <c r="H617" t="n">
@@ -20812,10 +20815,10 @@
       <c r="E618" t="n">
         <v>1</v>
       </c>
-      <c r="F618" t="n">
+      <c r="F618" s="1" t="n">
         <v>117.99</v>
       </c>
-      <c r="G618" t="n">
+      <c r="G618" s="1" t="n">
         <v>117.99</v>
       </c>
       <c r="H618" t="n">
@@ -20845,10 +20848,10 @@
       <c r="E619" t="n">
         <v>1</v>
       </c>
-      <c r="F619" t="n">
+      <c r="F619" s="1" t="n">
         <v>29.99</v>
       </c>
-      <c r="G619" t="n">
+      <c r="G619" s="1" t="n">
         <v>29.99</v>
       </c>
       <c r="H619" t="n">
@@ -20878,10 +20881,10 @@
       <c r="E620" t="n">
         <v>1</v>
       </c>
-      <c r="F620" t="n">
+      <c r="F620" s="1" t="n">
         <v>55.99</v>
       </c>
-      <c r="G620" t="n">
+      <c r="G620" s="1" t="n">
         <v>55.99</v>
       </c>
       <c r="H620" t="n">
@@ -20911,10 +20914,10 @@
       <c r="E621" t="n">
         <v>1</v>
       </c>
-      <c r="F621" t="n">
+      <c r="F621" s="1" t="n">
         <v>39.84</v>
       </c>
-      <c r="G621" t="n">
+      <c r="G621" s="1" t="n">
         <v>39.84</v>
       </c>
       <c r="H621" t="n">
@@ -20944,10 +20947,10 @@
       <c r="E622" t="n">
         <v>1</v>
       </c>
-      <c r="F622" t="n">
+      <c r="F622" s="1" t="n">
         <v>112.02</v>
       </c>
-      <c r="G622" t="n">
+      <c r="G622" s="1" t="n">
         <v>112.02</v>
       </c>
       <c r="H622" t="n">
@@ -20977,10 +20980,10 @@
       <c r="E623" t="n">
         <v>1</v>
       </c>
-      <c r="F623" t="n">
+      <c r="F623" s="1" t="n">
         <v>35.99</v>
       </c>
-      <c r="G623" t="n">
+      <c r="G623" s="1" t="n">
         <v>35.99</v>
       </c>
       <c r="H623" t="n">
@@ -21010,10 +21013,10 @@
       <c r="E624" t="n">
         <v>1</v>
       </c>
-      <c r="F624" t="n">
+      <c r="F624" s="1" t="n">
         <v>119.99</v>
       </c>
-      <c r="G624" t="n">
+      <c r="G624" s="1" t="n">
         <v>119.99</v>
       </c>
       <c r="H624" t="n">
@@ -21043,10 +21046,10 @@
       <c r="E625" t="n">
         <v>1</v>
       </c>
-      <c r="F625" t="n">
+      <c r="F625" s="1" t="n">
         <v>56.88</v>
       </c>
-      <c r="G625" t="n">
+      <c r="G625" s="1" t="n">
         <v>56.88</v>
       </c>
       <c r="H625" t="n">
@@ -21076,10 +21079,10 @@
       <c r="E626" t="n">
         <v>1</v>
       </c>
-      <c r="F626" t="n">
+      <c r="F626" s="1" t="n">
         <v>32.47</v>
       </c>
-      <c r="G626" t="n">
+      <c r="G626" s="1" t="n">
         <v>32.47</v>
       </c>
       <c r="H626" t="n">
@@ -21109,10 +21112,10 @@
       <c r="E627" t="n">
         <v>1</v>
       </c>
-      <c r="F627" t="n">
+      <c r="F627" s="1" t="n">
         <v>23.45</v>
       </c>
-      <c r="G627" t="n">
+      <c r="G627" s="1" t="n">
         <v>23.45</v>
       </c>
       <c r="H627" t="n">
@@ -21159,12 +21162,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>销售额 (USD)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>均价</t>
+          <t>均价 (USD)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -21193,10 +21196,10 @@
       <c r="D2" t="n">
         <v>99141</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="1" t="n">
         <v>3635186.88</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="1" t="n">
         <v>34.71</v>
       </c>
       <c r="G2" t="n">
@@ -21221,10 +21224,10 @@
       <c r="D3" t="n">
         <v>79152</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="1" t="n">
         <v>2687430.6</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="1" t="n">
         <v>30.79</v>
       </c>
       <c r="G3" t="n">
@@ -21249,10 +21252,10 @@
       <c r="D4" t="n">
         <v>79597</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="1" t="n">
         <v>3099927.21</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="1" t="n">
         <v>37.86</v>
       </c>
       <c r="G4" t="n">
@@ -21277,10 +21280,10 @@
       <c r="D5" t="n">
         <v>37376</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="1" t="n">
         <v>3231664.42</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="1" t="n">
         <v>84.33</v>
       </c>
       <c r="G5" t="n">
@@ -21305,10 +21308,10 @@
       <c r="D6" t="n">
         <v>34376</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="1" t="n">
         <v>2296706.79</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="1" t="n">
         <v>64.48</v>
       </c>
       <c r="G6" t="n">
@@ -21333,10 +21336,10 @@
       <c r="D7" t="n">
         <v>18630</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="1" t="n">
         <v>281592.46</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="1" t="n">
         <v>13.97</v>
       </c>
       <c r="G7" t="n">
@@ -21361,10 +21364,10 @@
       <c r="D8" t="n">
         <v>19481</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="1" t="n">
         <v>872184.88</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="1" t="n">
         <v>43.45</v>
       </c>
       <c r="G8" t="n">
@@ -21389,10 +21392,10 @@
       <c r="D9" t="n">
         <v>17128</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="1" t="n">
         <v>685296.89</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="1" t="n">
         <v>36.27</v>
       </c>
       <c r="G9" t="n">
@@ -21417,10 +21420,10 @@
       <c r="D10" t="n">
         <v>15970</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="1" t="n">
         <v>709113.9399999999</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="1" t="n">
         <v>42.95</v>
       </c>
       <c r="G10" t="n">
@@ -21445,10 +21448,10 @@
       <c r="D11" t="n">
         <v>15688</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="1" t="n">
         <v>753084.95</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="1" t="n">
         <v>47.49</v>
       </c>
       <c r="G11" t="n">
@@ -21473,10 +21476,10 @@
       <c r="D12" t="n">
         <v>13692</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="1" t="n">
         <v>1544290.63</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="1" t="n">
         <v>109.93</v>
       </c>
       <c r="G12" t="n">
@@ -21501,10 +21504,10 @@
       <c r="D13" t="n">
         <v>13932</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="1" t="n">
         <v>1608319.15</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="1" t="n">
         <v>114.81</v>
       </c>
       <c r="G13" t="n">
@@ -21529,10 +21532,10 @@
       <c r="D14" t="n">
         <v>9504</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="1" t="n">
         <v>715862.9300000001</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="1" t="n">
         <v>74.09</v>
       </c>
       <c r="G14" t="n">
@@ -21557,10 +21560,10 @@
       <c r="D15" t="n">
         <v>8806</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="1" t="n">
         <v>636079.09</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="1" t="n">
         <v>71.29000000000001</v>
       </c>
       <c r="G15" t="n">
@@ -21585,10 +21588,10 @@
       <c r="D16" t="n">
         <v>8682</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="1" t="n">
         <v>581542.38</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="1" t="n">
         <v>66.02</v>
       </c>
       <c r="G16" t="n">
@@ -21613,10 +21616,10 @@
       <c r="D17" t="n">
         <v>6083</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="1" t="n">
         <v>336765.37</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="1" t="n">
         <v>54.79</v>
       </c>
       <c r="G17" t="n">
@@ -21641,10 +21644,10 @@
       <c r="D18" t="n">
         <v>5549</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="1" t="n">
         <v>363535.36</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="1" t="n">
         <v>62.4</v>
       </c>
       <c r="G18" t="n">
@@ -21669,10 +21672,10 @@
       <c r="D19" t="n">
         <v>5565</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="1" t="n">
         <v>339845.64</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="1" t="n">
         <v>59.03</v>
       </c>
       <c r="G19" t="n">
@@ -21697,10 +21700,10 @@
       <c r="D20" t="n">
         <v>5208</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="1" t="n">
         <v>91708.23</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="1" t="n">
         <v>16.44</v>
       </c>
       <c r="G20" t="n">
@@ -21725,10 +21728,10 @@
       <c r="D21" t="n">
         <v>5280</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="1" t="n">
         <v>262696.16</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="1" t="n">
         <v>47.76</v>
       </c>
       <c r="G21" t="n">
@@ -21753,10 +21756,10 @@
       <c r="D22" t="n">
         <v>5093</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="1" t="n">
         <v>390726.86</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="1" t="n">
         <v>76.03</v>
       </c>
       <c r="G22" t="n">
@@ -21781,10 +21784,10 @@
       <c r="D23" t="n">
         <v>5022</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="1" t="n">
         <v>472996.71</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="1" t="n">
         <v>93.77</v>
       </c>
       <c r="G23" t="n">
@@ -21809,10 +21812,10 @@
       <c r="D24" t="n">
         <v>4780</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="1" t="n">
         <v>238046.17</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="1" t="n">
         <v>49.4</v>
       </c>
       <c r="G24" t="n">
@@ -21837,10 +21840,10 @@
       <c r="D25" t="n">
         <v>4082</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="1" t="n">
         <v>234950.09</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="1" t="n">
         <v>56.44</v>
       </c>
       <c r="G25" t="n">
@@ -21865,10 +21868,10 @@
       <c r="D26" t="n">
         <v>3616</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="1" t="n">
         <v>214682.62</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="1" t="n">
         <v>53.99</v>
       </c>
       <c r="G26" t="n">
@@ -21893,10 +21896,10 @@
       <c r="D27" t="n">
         <v>3787</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="1" t="n">
         <v>330891.93</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="1" t="n">
         <v>84.67</v>
       </c>
       <c r="G27" t="n">
@@ -21921,10 +21924,10 @@
       <c r="D28" t="n">
         <v>3629</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="1" t="n">
         <v>250101.29</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="1" t="n">
         <v>68.54000000000001</v>
       </c>
       <c r="G28" t="n">
@@ -21949,10 +21952,10 @@
       <c r="D29" t="n">
         <v>2861</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="1" t="n">
         <v>62387.71</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="1" t="n">
         <v>19.77</v>
       </c>
       <c r="G29" t="n">
@@ -21977,10 +21980,10 @@
       <c r="D30" t="n">
         <v>2870</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="1" t="n">
         <v>86018.84</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="1" t="n">
         <v>29.2</v>
       </c>
       <c r="G30" t="n">
@@ -22005,10 +22008,10 @@
       <c r="D31" t="n">
         <v>2790</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="1" t="n">
         <v>264394.37</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="1" t="n">
         <v>93.13</v>
       </c>
       <c r="G31" t="n">
@@ -22033,10 +22036,10 @@
       <c r="D32" t="n">
         <v>2730</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="1" t="n">
         <v>277509.57</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="1" t="n">
         <v>98.79000000000001</v>
       </c>
       <c r="G32" t="n">
@@ -22061,10 +22064,10 @@
       <c r="D33" t="n">
         <v>2579</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="1" t="n">
         <v>103763.31</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="1" t="n">
         <v>38.88</v>
       </c>
       <c r="G33" t="n">
@@ -22089,10 +22092,10 @@
       <c r="D34" t="n">
         <v>2407</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="1" t="n">
         <v>78490.37</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="1" t="n">
         <v>30.52</v>
       </c>
       <c r="G34" t="n">
@@ -22117,10 +22120,10 @@
       <c r="D35" t="n">
         <v>2471</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="1" t="n">
         <v>232316.79</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="1" t="n">
         <v>93.79000000000001</v>
       </c>
       <c r="G35" t="n">
@@ -22145,10 +22148,10 @@
       <c r="D36" t="n">
         <v>2354</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="1" t="n">
         <v>178052.78</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="1" t="n">
         <v>75.56999999999999</v>
       </c>
       <c r="G36" t="n">
@@ -22173,10 +22176,10 @@
       <c r="D37" t="n">
         <v>2005</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="1" t="n">
         <v>101576.87</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="1" t="n">
         <v>50.16</v>
       </c>
       <c r="G37" t="n">
@@ -22201,10 +22204,10 @@
       <c r="D38" t="n">
         <v>1867</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="1" t="n">
         <v>101255.89</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="1" t="n">
         <v>52.93</v>
       </c>
       <c r="G38" t="n">
@@ -22229,10 +22232,10 @@
       <c r="D39" t="n">
         <v>1734</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="1" t="n">
         <v>179565.79</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="1" t="n">
         <v>101.22</v>
       </c>
       <c r="G39" t="n">
@@ -22257,10 +22260,10 @@
       <c r="D40" t="n">
         <v>1651</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="1" t="n">
         <v>147270.93</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="1" t="n">
         <v>87.92</v>
       </c>
       <c r="G40" t="n">
@@ -22285,10 +22288,10 @@
       <c r="D41" t="n">
         <v>1591</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="1" t="n">
         <v>62866</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="1" t="n">
         <v>39.39</v>
       </c>
       <c r="G41" t="n">
@@ -22313,10 +22316,10 @@
       <c r="D42" t="n">
         <v>1410</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="1" t="n">
         <v>28832.66</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="1" t="n">
         <v>18.6</v>
       </c>
       <c r="G42" t="n">
@@ -22341,10 +22344,10 @@
       <c r="D43" t="n">
         <v>1497</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="1" t="n">
         <v>117321.78</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="1" t="n">
         <v>76.83</v>
       </c>
       <c r="G43" t="n">
@@ -22369,10 +22372,10 @@
       <c r="D44" t="n">
         <v>1426</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="1" t="n">
         <v>49614.3</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="1" t="n">
         <v>34.31</v>
       </c>
       <c r="G44" t="n">
@@ -22397,10 +22400,10 @@
       <c r="D45" t="n">
         <v>1307</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="1" t="n">
         <v>89166.03999999999</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="1" t="n">
         <v>64.47</v>
       </c>
       <c r="G45" t="n">
@@ -22425,10 +22428,10 @@
       <c r="D46" t="n">
         <v>1374</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="1" t="n">
         <v>136191.43</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="1" t="n">
         <v>98.69</v>
       </c>
       <c r="G46" t="n">
@@ -22453,10 +22456,10 @@
       <c r="D47" t="n">
         <v>1282</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="1" t="n">
         <v>125548.46</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="1" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="G47" t="n">
@@ -22481,10 +22484,10 @@
       <c r="D48" t="n">
         <v>1276</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="1" t="n">
         <v>162459.71</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="1" t="n">
         <v>125.94</v>
       </c>
       <c r="G48" t="n">
@@ -22509,10 +22512,10 @@
       <c r="D49" t="n">
         <v>1127</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="1" t="n">
         <v>68079.56</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="1" t="n">
         <v>59.41</v>
       </c>
       <c r="G49" t="n">
@@ -22537,10 +22540,10 @@
       <c r="D50" t="n">
         <v>1051</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="1" t="n">
         <v>68859.59</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="1" t="n">
         <v>64.66</v>
       </c>
       <c r="G50" t="n">
@@ -22565,10 +22568,10 @@
       <c r="D51" t="n">
         <v>908</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="1" t="n">
         <v>42042.52</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="1" t="n">
         <v>45.11</v>
       </c>
       <c r="G51" t="n">
@@ -22593,10 +22596,10 @@
       <c r="D52" t="n">
         <v>893</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="1" t="n">
         <v>132995.27</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="1" t="n">
         <v>148.27</v>
       </c>
       <c r="G52" t="n">
@@ -22621,10 +22624,10 @@
       <c r="D53" t="n">
         <v>859</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="1" t="n">
         <v>48445.66</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="1" t="n">
         <v>55.81</v>
       </c>
       <c r="G53" t="n">
@@ -22649,10 +22652,10 @@
       <c r="D54" t="n">
         <v>781</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="1" t="n">
         <v>105852.86</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="1" t="n">
         <v>130.68</v>
       </c>
       <c r="G54" t="n">
@@ -22677,10 +22680,10 @@
       <c r="D55" t="n">
         <v>781</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="1" t="n">
         <v>54286.61</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="1" t="n">
         <v>68.63</v>
       </c>
       <c r="G55" t="n">
@@ -22705,10 +22708,10 @@
       <c r="D56" t="n">
         <v>715</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="1" t="n">
         <v>26750.73</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="1" t="n">
         <v>34.79</v>
       </c>
       <c r="G56" t="n">
@@ -22733,10 +22736,10 @@
       <c r="D57" t="n">
         <v>717</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="1" t="n">
         <v>44357.98</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="1" t="n">
         <v>59.46</v>
       </c>
       <c r="G57" t="n">
@@ -22761,10 +22764,10 @@
       <c r="D58" t="n">
         <v>714</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="1" t="n">
         <v>53607.83</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="1" t="n">
         <v>74.15000000000001</v>
       </c>
       <c r="G58" t="n">
@@ -22789,10 +22792,10 @@
       <c r="D59" t="n">
         <v>688</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="1" t="n">
         <v>24566.45</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="1" t="n">
         <v>35.25</v>
       </c>
       <c r="G59" t="n">
@@ -22817,10 +22820,10 @@
       <c r="D60" t="n">
         <v>565</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="1" t="n">
         <v>65409</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="1" t="n">
         <v>115.56</v>
       </c>
       <c r="G60" t="n">
@@ -22845,10 +22848,10 @@
       <c r="D61" t="n">
         <v>554</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="1" t="n">
         <v>41541.36</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="1" t="n">
         <v>74.18000000000001</v>
       </c>
       <c r="G61" t="n">
@@ -22873,10 +22876,10 @@
       <c r="D62" t="n">
         <v>515</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="1" t="n">
         <v>35804.05</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="1" t="n">
         <v>68.72</v>
       </c>
       <c r="G62" t="n">
@@ -22901,10 +22904,10 @@
       <c r="D63" t="n">
         <v>503</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="1" t="n">
         <v>35973.44</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="1" t="n">
         <v>70.67</v>
       </c>
       <c r="G63" t="n">
@@ -22929,10 +22932,10 @@
       <c r="D64" t="n">
         <v>447</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="1" t="n">
         <v>9517.15</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="1" t="n">
         <v>20.47</v>
       </c>
       <c r="G64" t="n">
@@ -22957,10 +22960,10 @@
       <c r="D65" t="n">
         <v>454</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="1" t="n">
         <v>12635.32</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="1" t="n">
         <v>27.35</v>
       </c>
       <c r="G65" t="n">
@@ -22985,10 +22988,10 @@
       <c r="D66" t="n">
         <v>441</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="1" t="n">
         <v>29885.26</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="1" t="n">
         <v>66.41</v>
       </c>
       <c r="G66" t="n">
@@ -23013,10 +23016,10 @@
       <c r="D67" t="n">
         <v>364</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="1" t="n">
         <v>32155.82</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="1" t="n">
         <v>86.44</v>
       </c>
       <c r="G67" t="n">
@@ -23041,10 +23044,10 @@
       <c r="D68" t="n">
         <v>218</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="1" t="n">
         <v>206882.82</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="1" t="n">
         <v>949</v>
       </c>
       <c r="G68" t="n">
@@ -23069,10 +23072,10 @@
       <c r="D69" t="n">
         <v>171</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="1" t="n">
         <v>3214.26</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="1" t="n">
         <v>16.07</v>
       </c>
       <c r="G69" t="n">
@@ -23097,10 +23100,10 @@
       <c r="D70" t="n">
         <v>184</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="1" t="n">
         <v>12666.62</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="1" t="n">
         <v>67.38</v>
       </c>
       <c r="G70" t="n">
@@ -23125,10 +23128,10 @@
       <c r="D71" t="n">
         <v>174</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="1" t="n">
         <v>15297.97</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="1" t="n">
         <v>83.14</v>
       </c>
       <c r="G71" t="n">
@@ -23153,10 +23156,10 @@
       <c r="D72" t="n">
         <v>117</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="1" t="n">
         <v>1965.25</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="1" t="n">
         <v>14.78</v>
       </c>
       <c r="G72" t="n">
@@ -23181,10 +23184,10 @@
       <c r="D73" t="n">
         <v>114</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="1" t="n">
         <v>15732.12</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="1" t="n">
         <v>136.8</v>
       </c>
       <c r="G73" t="n">
@@ -23209,10 +23212,10 @@
       <c r="D74" t="n">
         <v>112</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="1" t="n">
         <v>2565.12</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="1" t="n">
         <v>22.5</v>
       </c>
       <c r="G74" t="n">
@@ -23237,10 +23240,10 @@
       <c r="D75" t="n">
         <v>30</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="1" t="n">
         <v>1642.69</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="1" t="n">
         <v>52.99</v>
       </c>
       <c r="G75" t="n">
@@ -23265,10 +23268,10 @@
       <c r="D76" t="n">
         <v>22</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="1" t="n">
         <v>11167.75</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" s="1" t="n">
         <v>485.55</v>
       </c>
       <c r="G76" t="n">
@@ -23293,10 +23296,10 @@
       <c r="D77" t="n">
         <v>17</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="1" t="n">
         <v>543.53</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="1" t="n">
         <v>30.2</v>
       </c>
       <c r="G77" t="n">
@@ -23321,10 +23324,10 @@
       <c r="D78" t="n">
         <v>2</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="1" t="n">
         <v>55.92</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" s="1" t="n">
         <v>27.96</v>
       </c>
       <c r="G78" t="n">
@@ -23349,10 +23352,10 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="1" t="n">
         <v>92.25</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" s="1" t="n">
         <v>92.25</v>
       </c>
       <c r="G79" t="n">
@@ -23377,10 +23380,10 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="1" t="n">
         <v>71.41</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" s="1" t="n">
         <v>71.41</v>
       </c>
       <c r="G80" t="n">
